--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03832078128406491</v>
+        <v>0.04699997533857858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.04454914300289459</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0284087536412827</v>
+        <v>0.03309849682298149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02638195953805722</v>
+        <v>0.03145466027826771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02269890243601469</v>
+        <v>0.02651990440202479</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02004580404065126</v>
+        <v>0.02318440190254289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01928671849305919</v>
+        <v>0.02301962100605737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01792027001313068</v>
+        <v>0.02262720834981313</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01619892410736012</v>
+        <v>0.02234705201576581</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01407164547855211</v>
+        <v>0.01333332061767578</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01296130133714413</v>
+        <v>0.01307393392431955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01277587303594796</v>
+        <v>0.01275215373563698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01248996525817536</v>
+        <v>0.01124268070553902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>FXGB.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01232138778024661</v>
+        <v>0.008891454965358037</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>FEDF.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01221777277792335</v>
+        <v>0.008167379826360399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>Amundi USD Fed Funds Rate UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4104444715711806</v>
+        <v>0.426398148395476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,195 +713,195 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1149448793737018</v>
+        <v>0.09576136433814519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07911114162868915</v>
+        <v>0.09532354685469158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0773548255976515</v>
+        <v>0.0847419338352664</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07554796999905911</v>
+        <v>0.07928567239520512</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07518178766424</v>
+        <v>0.07191429261324167</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0707756511679023</v>
+        <v>0.07048895726118953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06969325527823034</v>
+        <v>0.06583592110921543</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06923076923076921</v>
+        <v>0.06581150502463484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06491503936157095</v>
+        <v>0.06246959902924187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06376841484038631</v>
+        <v>0.06179173319141396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06297494705199336</v>
+        <v>0.06061924863274792</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05712818379197038</v>
+        <v>0.05929137377785909</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05093257321023592</v>
+        <v>0.05688416021126352</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05005672908571435</v>
+        <v>0.05205331133022484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.319540605734423</v>
+        <v>0.2826124765015132</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,15 +969,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.162301647138247</v>
+        <v>0.1893813027801381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1553064654730978</v>
+        <v>0.1668006897502106</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,75 +999,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1481274568729807</v>
+        <v>0.1643582640812558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1474115481948497</v>
+        <v>0.123560928936052</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1316870175140916</v>
+        <v>0.1210844040186392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1238850958023381</v>
+        <v>0.1197053620471857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1228046630151924</v>
+        <v>0.1175933847308479</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1137622698617693</v>
+        <v>0.1117942592625405</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1089,45 +1089,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1086758497521361</v>
+        <v>0.1015400936261959</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1025912453011912</v>
+        <v>0.09572548528545699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08680147578091013</v>
+        <v>0.08323022108260414</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08483517394439999</v>
+        <v>0.08094631813405684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07862949595032798</v>
+        <v>0.08038128968361535</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPN.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0785932497260029</v>
+        <v>0.07666233567765079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6772474210357222</v>
+        <v>0.6860397513927279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5083768612610933</v>
+        <v>0.4502568505362172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,60 +1240,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4912954805483689</v>
+        <v>0.383055463025386</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.48582807398179</v>
+        <v>0.3553255189348292</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4303020833835212</v>
+        <v>0.3444419565625301</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3773099972820062</v>
+        <v>0.3421051467608343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3476214664533273</v>
+        <v>0.3232142722016049</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,30 +1315,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3302989903802247</v>
+        <v>0.3135866045908395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3234536077195183</v>
+        <v>0.3080632048197007</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3209116946217929</v>
+        <v>0.2778744574210099</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3198873524335386</v>
+        <v>0.270590594342772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2967413973388064</v>
+        <v>0.2571161696049151</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2876008193003239</v>
+        <v>0.2433280727375513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2789506119074534</v>
+        <v>0.2382847315628891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2766478687282095</v>
+        <v>0.2348501981169457</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.585415843714573</v>
+        <v>1.417145184288866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.563662681207206</v>
+        <v>1.398000656437471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7683846616377978</v>
+        <v>0.793804328025671</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7647487630947125</v>
+        <v>0.7367839278259507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.759380986398646</v>
+        <v>0.6718569501737623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,150 +1541,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6555295513124362</v>
+        <v>0.6100088758920184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6356498941494806</v>
+        <v>0.6038907667446951</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6245948754684805</v>
+        <v>0.5877046432754649</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5727204309946585</v>
+        <v>0.5656816014096742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>COMH.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5670279486408001</v>
+        <v>0.5480734093899533</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5636947424380803</v>
+        <v>0.525775994386255</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5486506795053567</v>
+        <v>0.5150481701702978</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5426305900417037</v>
+        <v>0.5094621623717321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5163087913028996</v>
+        <v>0.5068596700050658</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5129032284527903</v>
+        <v>0.4869590326220838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.578463737736245</v>
+        <v>2.39626849978836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.457976474616103</v>
+        <v>2.367817008723167</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.077000088355379</v>
+        <v>1.804706196541569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.043113814419916</v>
+        <v>1.779873862119433</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.865857918694148</v>
+        <v>1.749083038480807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.613298625067221</v>
+        <v>1.54774083784014</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.545741249726172</v>
+        <v>1.501950114687115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.387941248276654</v>
+        <v>1.322747634657341</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,45 +1842,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.353056085809162</v>
+        <v>1.220583170715141</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.278008100077423</v>
+        <v>1.199150943128896</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.223806226426214</v>
+        <v>1.194964888611999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.178633262711191</v>
+        <v>1.15854771963838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,30 +1902,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.161151736014856</v>
+        <v>1.081284816675812</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.151483369397445</v>
+        <v>1.066798104630462</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.096042125432263</v>
+        <v>1.042977787796712</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.979268404218667</v>
+        <v>0.8590687475680512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9676875184448273</v>
+        <v>0.8487312814752055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5633301142576221</v>
+        <v>0.5819026158542877</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5361724518046913</v>
+        <v>0.5023203991529144</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,120 +2038,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4961797067439928</v>
+        <v>0.4868528759783533</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4759432030635702</v>
+        <v>0.479699579837199</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4679652453420586</v>
+        <v>0.4523226981940347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4307561219978349</v>
+        <v>0.4000000838395026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4016589751006419</v>
+        <v>0.3791219704949</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3956043787136534</v>
+        <v>0.3553175566773152</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3779488713109476</v>
+        <v>0.3356613228017047</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3448276902743739</v>
+        <v>0.3344922043105225</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3360010340872068</v>
+        <v>0.3247422957812305</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3194632025788802</v>
+        <v>0.3205185273624149</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2958454400583692</v>
+        <v>0.2759706388387229</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04699997533857858</v>
+        <v>0.05430429140764592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04454914300289459</v>
+        <v>0.04499678253684758</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03309849682298149</v>
+        <v>0.04212060879910728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -487,135 +487,135 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03145466027826771</v>
+        <v>0.03220137999554851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02651990440202479</v>
+        <v>0.03036854311591042</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02318440190254289</v>
+        <v>0.02725122535172231</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02301962100605737</v>
+        <v>0.02722017868050686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02262720834981313</v>
+        <v>0.02689260687816808</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02234705201576581</v>
+        <v>0.02603015530052799</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01333332061767578</v>
+        <v>0.02567570724131985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>JPXU.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01307393392431955</v>
+        <v>0.01498853882195572</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - USD Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01275215373563698</v>
+        <v>0.0140733882941424</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01124268070553902</v>
+        <v>0.01207442483026266</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -637,30 +637,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FXGB.L</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.008891454965358037</v>
+        <v>0.01159341094899813</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FEDF.MI</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.008167379826360399</v>
+        <v>0.008320700034446293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi USD Fed Funds Rate UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.426398148395476</v>
+        <v>0.3959731646719442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,210 +713,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09576136433814519</v>
+        <v>0.1032538292127201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09532354685469158</v>
+        <v>0.1023024360240365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0847419338352664</v>
+        <v>0.08942532215967325</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07928567239520512</v>
+        <v>0.0847419338352664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07191429261324167</v>
+        <v>0.08428575701251306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07048895726118953</v>
+        <v>0.07501390353943482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06583592110921543</v>
+        <v>0.07272276591204019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06581150502463484</v>
+        <v>0.07140959531974578</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06246959902924187</v>
+        <v>0.06958541353634917</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06179173319141396</v>
+        <v>0.06689112001886177</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06061924863274792</v>
+        <v>0.06670940563069538</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05929137377785909</v>
+        <v>0.0610885506441905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05688416021126352</v>
+        <v>0.06061924863274792</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05205331133022484</v>
+        <v>0.05136185430498963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2826124765015132</v>
+        <v>0.346927990938747</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1893813027801381</v>
+        <v>0.2098418006906249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,45 +984,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1668006897502106</v>
+        <v>0.1882069391756869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1643582640812558</v>
+        <v>0.1524292399667937</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.123560928936052</v>
+        <v>0.1197053620471857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1210844040186392</v>
+        <v>0.1155254584952619</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,135 +1044,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1197053620471857</v>
+        <v>0.1116878999494739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1175933847308479</v>
+        <v>0.09336053052281557</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1117942592625405</v>
+        <v>0.09053311222916638</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1015400936261959</v>
+        <v>0.0895272384815502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09572548528545699</v>
+        <v>0.08710658148899419</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08323022108260414</v>
+        <v>0.07920815232060519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWF.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08094631813405684</v>
+        <v>0.07518794604887424</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08038128968361535</v>
+        <v>0.07470037992047041</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>FXGB.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07666233567765079</v>
+        <v>0.07084201495281284</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6860397513927279</v>
+        <v>0.7227051788701873</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4502568505362172</v>
+        <v>0.4423480631364389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.383055463025386</v>
+        <v>0.3454573141273045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3553255189348292</v>
+        <v>0.3366605794164905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,30 +1270,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3444419565625301</v>
+        <v>0.3049903064901631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3421051467608343</v>
+        <v>0.3008969103695776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3232142722016049</v>
+        <v>0.2990294651075465</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,45 +1315,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3135866045908395</v>
+        <v>0.297443356374032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3080632048197007</v>
+        <v>0.2723608563716293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2778744574210099</v>
+        <v>0.2712572113846725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.270590594342772</v>
+        <v>0.2559086611656682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2571161696049151</v>
+        <v>0.2327586662512153</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2433280727375513</v>
+        <v>0.2264890872549246</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,15 +1405,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2382847315628891</v>
+        <v>0.2135017397996208</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2348501981169457</v>
+        <v>0.2114208169399179</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.417145184288866</v>
+        <v>1.384061986580881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.398000656437471</v>
+        <v>1.364928591834413</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.793804328025671</v>
+        <v>0.8918786320773959</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7367839278259507</v>
+        <v>0.714908882802284</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6718569501737623</v>
+        <v>0.6276413265255549</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6100088758920184</v>
+        <v>0.622542951066984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,75 +1556,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6038907667446951</v>
+        <v>0.5920496591129658</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5877046432754649</v>
+        <v>0.5799632171144369</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5656816014096742</v>
+        <v>0.5587649221371802</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5480734093899533</v>
+        <v>0.5561313034098323</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.525775994386255</v>
+        <v>0.5000187085628451</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5150481701702978</v>
+        <v>0.495780360530754</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,15 +1646,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5094621623717321</v>
+        <v>0.473191897883521</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5068596700050658</v>
+        <v>0.4671479354948405</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4869590326220838</v>
+        <v>0.4469499723533712</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.39626849978836</v>
+        <v>2.380468963159628</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.367817008723167</v>
+        <v>2.341388002287532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.804706196541569</v>
+        <v>1.780883920247871</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.779873862119433</v>
+        <v>1.75710842536454</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.749083038480807</v>
+        <v>1.689062929594667</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.54774083784014</v>
+        <v>1.543045014461854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.501950114687115</v>
+        <v>1.490912119542445</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.322747634657341</v>
+        <v>1.301480271452534</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.220583170715141</v>
+        <v>1.216014258479965</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.199150943128896</v>
+        <v>1.180403197436826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.194964888611999</v>
+        <v>1.157864774727079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.15854771963838</v>
+        <v>1.154853399931751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.066798104630462</v>
+        <v>1.048558078272662</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.042977787796712</v>
+        <v>1.037953397114105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8590687475680512</v>
+        <v>0.8432784129482775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8487312814752055</v>
+        <v>0.8335913229185508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5819026158542877</v>
+        <v>0.6475543571724116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,45 +2023,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5023203991529144</v>
+        <v>0.5038722802489106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4868528759783533</v>
+        <v>0.5025935098077707</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.479699579837199</v>
+        <v>0.5009309344164257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4523226981940347</v>
+        <v>0.4349021702735296</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4000000838395026</v>
+        <v>0.4120879236043273</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3791219704949</v>
+        <v>0.374053505050415</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3553175566773152</v>
+        <v>0.3506162774938364</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3356613228017047</v>
+        <v>0.3297687100315845</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3344922043105225</v>
+        <v>0.3282841090247477</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3247422957812305</v>
+        <v>0.3223006204937207</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COMH.MI</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3205185273624149</v>
+        <v>0.2759706388387229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF EUR Hedged Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2759706388387229</v>
+        <v>0.2518663215959489</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05430429140764592</v>
+        <v>0.06352652756985422</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04499678253684758</v>
+        <v>0.03454950455924366</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>TPXY.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04212060879910728</v>
+        <v>0.0262012588936833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Japan Topix UCITS ETF JPY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>JPXU.L</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03220137999554851</v>
+        <v>0.02592137689980145</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - USD Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03036854311591042</v>
+        <v>0.02504763052072101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02725122535172231</v>
+        <v>0.02501947040498442</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>TPXH.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02722017868050686</v>
+        <v>0.02416318606830536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Japan Topix UCITS ETF Daily Hedged EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02689260687816808</v>
+        <v>0.02343188400485441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02603015530052799</v>
+        <v>0.02296009776875674</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02567570724131985</v>
+        <v>0.02281579569129555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPXU.L</t>
+          <t>JPNH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01498853882195572</v>
+        <v>0.02276149386529536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - USD Hedged (C)</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0140733882941424</v>
+        <v>0.02257528939869458</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>JPNY.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01207442483026266</v>
+        <v>0.02216667503243852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi JPX Nikkei 400 UCITS ETF JPY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01159341094899813</v>
+        <v>0.02212051635755174</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>LJPN.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.008320700034446293</v>
+        <v>0.0217814747150924</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3959731646719442</v>
+        <v>0.3064043483398322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1032538292127201</v>
+        <v>0.1168924001807834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1023024360240365</v>
+        <v>0.09174067524614182</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08942532215967325</v>
+        <v>0.07013387306486352</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,165 +758,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0847419338352664</v>
+        <v>0.0671373009072791</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08428575701251306</v>
+        <v>0.06534214973291719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07501390353943482</v>
+        <v>0.06482625309092027</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07272276591204019</v>
+        <v>0.06419403054397854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07140959531974578</v>
+        <v>0.05819817633296731</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06958541353634917</v>
+        <v>0.05792166255817688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06689112001886177</v>
+        <v>0.05425374704771024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06670940563069538</v>
+        <v>0.04918030089041414</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0610885506441905</v>
+        <v>0.04558186410541509</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06061924863274792</v>
+        <v>0.04490192887050659</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05136185430498963</v>
+        <v>0.04438378929429732</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.346927990938747</v>
+        <v>0.3349804215649992</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2098418006906249</v>
+        <v>0.1862323790972906</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1882069391756869</v>
+        <v>0.1822946409121071</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1524292399667937</v>
+        <v>0.1430188526426908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,75 +1014,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1197053620471857</v>
+        <v>0.1158125573326478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1155254584952619</v>
+        <v>0.1100071954696005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1116878999494739</v>
+        <v>0.1031979864212698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09336053052281557</v>
+        <v>0.08805566959565292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09053311222916638</v>
+        <v>0.08137091516034123</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0895272384815502</v>
+        <v>0.07840956782327457</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,75 +1104,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08710658148899419</v>
+        <v>0.07646716004712428</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07920815232060519</v>
+        <v>0.07465697898482637</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07518794604887424</v>
+        <v>0.07414853565873014</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>FXGB.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07470037992047041</v>
+        <v>0.0683708414872799</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FXGB.L</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07084201495281284</v>
+        <v>0.06761429396681895</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7227051788701873</v>
+        <v>0.784941288578102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4423480631364389</v>
+        <v>0.4563259431977924</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3454573141273045</v>
+        <v>0.3765325199642031</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,75 +1255,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3366605794164905</v>
+        <v>0.3318193425530214</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3049903064901631</v>
+        <v>0.3276182251652473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3008969103695776</v>
+        <v>0.3228574099574264</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2990294651075465</v>
+        <v>0.3193875177464247</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.297443356374032</v>
+        <v>0.2930554646778178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2723608563716293</v>
+        <v>0.290165638123471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,60 +1345,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2712572113846725</v>
+        <v>0.2801812570582507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2559086611656682</v>
+        <v>0.2749473976513166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2327586662512153</v>
+        <v>0.2398023528349484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2264890872549246</v>
+        <v>0.2336147484917162</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2135017397996208</v>
+        <v>0.228917426604077</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2114208169399179</v>
+        <v>0.2224449679122875</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.384061986580881</v>
+        <v>1.40474458014602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.364928591834413</v>
+        <v>1.385833936702455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8918786320773959</v>
+        <v>0.915647859619146</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.714908882802284</v>
+        <v>0.7301070631439048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6276413265255549</v>
+        <v>0.6830254117868861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.622542951066984</v>
+        <v>0.622332459550025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,60 +1556,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5920496591129658</v>
+        <v>0.5885157565410009</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5799632171144369</v>
+        <v>0.5788333892822266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5587649221371802</v>
+        <v>0.5647758065537876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5561313034098323</v>
+        <v>0.5279804640307568</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5000187085628451</v>
+        <v>0.5241489759462776</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.495780360530754</v>
+        <v>0.5162398045902887</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,30 +1646,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.473191897883521</v>
+        <v>0.514955610199304</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4671479354948405</v>
+        <v>0.4848580300631797</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4469499723533712</v>
+        <v>0.4580384325384923</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.380468963159628</v>
+        <v>2.4341872912646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.341388002287532</v>
+        <v>2.351456317142956</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.780883920247871</v>
+        <v>1.832093481007806</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.75710842536454</v>
+        <v>1.806891928878146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.689062929594667</v>
+        <v>1.665388401755676</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.543045014461854</v>
+        <v>1.53313149897736</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.490912119542445</v>
+        <v>1.501132543176655</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.301480271452534</v>
+        <v>1.309814829026564</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.216014258479965</v>
+        <v>1.248648776773242</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,30 +1857,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.180403197436826</v>
+        <v>1.207079205618746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.157864774727079</v>
+        <v>1.198089790712515</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.154853399931751</v>
+        <v>1.170158352434073</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.081284816675812</v>
+        <v>1.103489319664314</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.048558078272662</v>
+        <v>1.070495455554969</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.037953397114105</v>
+        <v>1.057277817887916</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8432784129482775</v>
+        <v>0.8772221087631455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8335913229185508</v>
+        <v>0.8666994151601408</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6475543571724116</v>
+        <v>0.6920419629071035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5038722802489106</v>
+        <v>0.5225225166587086</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5025935098077707</v>
+        <v>0.4825158487643102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5009309344164257</v>
+        <v>0.4690838502612629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4349021702735296</v>
+        <v>0.4475855718641371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4120879236043273</v>
+        <v>0.4119047342909574</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.374053505050415</v>
+        <v>0.3923946886771947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3506162774938364</v>
+        <v>0.3712683436355824</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,30 +2128,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3297687100315845</v>
+        <v>0.349391595105176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3282841090247477</v>
+        <v>0.335224863801689</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3223006204937207</v>
+        <v>0.3171459151692479</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2518663215959489</v>
+        <v>0.2651712664150694</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06352652756985422</v>
+        <v>0.1565933837405216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,75 +457,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03454950455924366</v>
+        <v>0.05074355244797246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TPXY.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0262012588936833</v>
+        <v>0.03091770581751629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF JPY</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JPXU.L</t>
+          <t>JPNH.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02592137689980145</v>
+        <v>0.03052744723346201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - USD Hedged (C)</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>JPNY.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02504763052072101</v>
+        <v>0.030266986211402</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi JPX Nikkei 400 UCITS ETF JPY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02501947040498442</v>
+        <v>0.0302614610101164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02416318606830536</v>
+        <v>0.02987752766473761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -547,120 +547,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02343188400485441</v>
+        <v>0.02956847584658528</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>JPN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02296009776875674</v>
+        <v>0.02939979242690871</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>JPXX.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02281579569129555</v>
+        <v>0.02906182952993963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JPNH.PA</t>
+          <t>TPXY.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02276149386529536</v>
+        <v>0.02883407075469635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
+          <t>Amundi Japan Topix UCITS ETF JPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02257528939869458</v>
+        <v>0.02857986850279959</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPNY.PA</t>
+          <t>SRIJC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02216667503243852</v>
+        <v>0.02825990179913873</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi JPX Nikkei 400 UCITS ETF JPY</t>
+          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02212051635755174</v>
+        <v>0.02822647308099802</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LJPN.AS</t>
+          <t>JPXY.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0217814747150924</v>
+        <v>0.02754088447597947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Japan UCITS ETF Dist</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3064043483398322</v>
+        <v>0.3547579434386727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1168924001807834</v>
+        <v>0.2150072561130973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,30 +728,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09174067524614182</v>
+        <v>0.1098349570556982</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07013387306486352</v>
+        <v>0.09284090885844454</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0671373009072791</v>
+        <v>0.0759739853819823</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,75 +773,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06534214973291719</v>
+        <v>0.07486366996381721</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06482625309092027</v>
+        <v>0.06647534193169635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06419403054397854</v>
+        <v>0.06590440804253617</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05819817633296731</v>
+        <v>0.06406689084587058</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05792166255817688</v>
+        <v>0.05923347842253612</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05425374704771024</v>
+        <v>0.05231722111803871</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04918030089041414</v>
+        <v>0.05037533312265419</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04558186410541509</v>
+        <v>0.05015354144322548</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04490192887050659</v>
+        <v>0.04823402064852855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04438378929429732</v>
+        <v>0.04512714611070212</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3349804215649992</v>
+        <v>0.4213369986367801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,30 +969,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1862323790972906</v>
+        <v>0.2121270687334575</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1822946409121071</v>
+        <v>0.2087117252786577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1430188526426908</v>
+        <v>0.1682360551224864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,45 +1014,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1158125573326478</v>
+        <v>0.1269057284044219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1100071954696005</v>
+        <v>0.1243643383462008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1031979864212698</v>
+        <v>0.1162684987860236</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08805566959565292</v>
+        <v>0.1096976600089281</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08137091516034123</v>
+        <v>0.1041166366119184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1089,75 +1089,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07840956782327457</v>
+        <v>0.1003926354621678</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07646716004712428</v>
+        <v>0.1002360720601652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07465697898482637</v>
+        <v>0.08881816336749315</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07414853565873014</v>
+        <v>0.08652428519450117</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FXGB.L</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0683708414872799</v>
+        <v>0.08599406034253509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06761429396681895</v>
+        <v>0.0809733285655958</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.784941288578102</v>
+        <v>0.9524637858072917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4563259431977924</v>
+        <v>0.4993374137265025</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3765325199642031</v>
+        <v>0.4674317341580472</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,15 +1255,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3318193425530214</v>
+        <v>0.3821474589269902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3276182251652473</v>
+        <v>0.3751049167555192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,75 +1285,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3228574099574264</v>
+        <v>0.3709262083202152</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3193875177464247</v>
+        <v>0.3503282239621868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2930554646778178</v>
+        <v>0.3401902539165829</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.290165638123471</v>
+        <v>0.3380042993502379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2801812570582507</v>
+        <v>0.318119049252767</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2749473976513166</v>
+        <v>0.3103633326068698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1375,60 +1375,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2398023528349484</v>
+        <v>0.3080752338779777</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2336147484917162</v>
+        <v>0.2896953523274326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.228917426604077</v>
+        <v>0.2827390609284424</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2224449679122875</v>
+        <v>0.2786836994472712</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.40474458014602</v>
+        <v>1.467121202513582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.385833936702455</v>
+        <v>1.44717673144374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.915647859619146</v>
+        <v>1.00547809042086</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7301070631439048</v>
+        <v>0.7601120374455148</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6830254117868861</v>
+        <v>0.7374031979497464</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.622332459550025</v>
+        <v>0.6451162194583042</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5885157565410009</v>
+        <v>0.6381355821968255</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,75 +1571,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5788333892822266</v>
+        <v>0.5932264275497854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5647758065537876</v>
+        <v>0.5846437820560926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5279804640307568</v>
+        <v>0.5769307839758722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5241489759462776</v>
+        <v>0.5396203271828697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5162398045902887</v>
+        <v>0.5381186269357647</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.514955610199304</v>
+        <v>0.5127799866817875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4848580300631797</v>
+        <v>0.4906856524948959</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4580384325384923</v>
+        <v>0.4800230044111891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.4341872912646</v>
+        <v>2.561970969888691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.351456317142956</v>
+        <v>2.450733083508396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.832093481007806</v>
+        <v>1.914842135764308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.806891928878146</v>
+        <v>1.887962616032296</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.665388401755676</v>
+        <v>1.746462215346856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.53313149897736</v>
+        <v>1.590832236930241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.501132543176655</v>
+        <v>1.474424807178545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.309814829026564</v>
+        <v>1.370262532365149</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,30 +1842,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.248648776773242</v>
+        <v>1.279800659040489</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.207079205618746</v>
+        <v>1.252991789641499</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.198089790712515</v>
+        <v>1.244035116578254</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.170158352434073</v>
+        <v>1.197579049798432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.103489319664314</v>
+        <v>1.181463927366084</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.070495455554969</v>
+        <v>1.158313453981343</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.057277817887916</v>
+        <v>1.091798964307086</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8772221087631455</v>
+        <v>0.9163219459393543</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8666994151601408</v>
+        <v>0.9077934433200372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6920419629071035</v>
+        <v>0.8183782243018178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5225225166587086</v>
+        <v>0.5443625170336173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4825158487643102</v>
+        <v>0.477822114966254</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4690838502612629</v>
+        <v>0.4692470791835339</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4119047342909574</v>
+        <v>0.4214286223311265</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3923946886771947</v>
+        <v>0.4045114251564155</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3712683436355824</v>
+        <v>0.3902415278978006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.349391595105176</v>
+        <v>0.3717407760251727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,45 +2143,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.335224863801689</v>
+        <v>0.3309821096289747</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3171459151692479</v>
+        <v>0.3223483866939323</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2759706388387229</v>
+        <v>0.2867962398651125</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2651712664150694</v>
+        <v>0.2850500390152404</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1565933837405216</v>
+        <v>0.1662201862211719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05074355244797246</v>
+        <v>0.1357922778990419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03091770581751629</v>
+        <v>0.05542473983846063</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JPNH.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03052744723346201</v>
+        <v>0.03549486957619363</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JPNY.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.030266986211402</v>
+        <v>0.03212421411292521</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi JPX Nikkei 400 UCITS ETF JPY</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0302614610101164</v>
+        <v>0.02891857507607032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TPXH.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02987752766473761</v>
+        <v>0.02878046642379473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF Daily Hedged EUR (C)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02956847584658528</v>
+        <v>0.0284923578373717</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JPN.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02939979242690871</v>
+        <v>0.02573844374025458</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPXX.L</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02906182952993963</v>
+        <v>0.02506566586094117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - GBP Hedged (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TPXY.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02883407075469635</v>
+        <v>0.02221404548110706</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF JPY</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02857986850279959</v>
+        <v>0.02177779728804174</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SRIJC.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02825990179913873</v>
+        <v>0.02114864932084637</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02822647308099802</v>
+        <v>0.01869389218942108</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPXY.AS</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02754088447597947</v>
+        <v>0.01636885527931198</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR (C)</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3547579434386727</v>
+        <v>0.5789248070945556</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,45 +713,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2150072561130973</v>
+        <v>0.1179466960840216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1098349570556982</v>
+        <v>0.09655907750263504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09284090885844454</v>
+        <v>0.08295164622566098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0759739853819823</v>
+        <v>0.0754509646725301</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07486366996381721</v>
+        <v>0.07437592373156043</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06647534193169635</v>
+        <v>0.0692575319936608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06590440804253617</v>
+        <v>0.05938015212324532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06406689084587058</v>
+        <v>0.05636222103442612</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05923347842253612</v>
+        <v>0.04548592369126525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05231722111803871</v>
+        <v>0.04483016453334177</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05037533312265419</v>
+        <v>0.04400193673443353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05015354144322548</v>
+        <v>0.04392766959200722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04823402064852855</v>
+        <v>0.04319562241212282</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04512714611070212</v>
+        <v>0.04173135228687785</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4213369986367801</v>
+        <v>0.3478688935431322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,30 +969,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2121270687334575</v>
+        <v>0.2142933433889962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2087117252786577</v>
+        <v>0.1905033006514125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1682360551224864</v>
+        <v>0.1725546997681087</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1269057284044219</v>
+        <v>0.1338365699287341</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1243643383462008</v>
+        <v>0.118855238715698</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,75 +1044,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1162684987860236</v>
+        <v>0.1073621477568285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1096976600089281</v>
+        <v>0.1060051277019172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1041166366119184</v>
+        <v>0.1054545837366323</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1003926354621678</v>
+        <v>0.1049811778417624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1002360720601652</v>
+        <v>0.1049153145841715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08881816336749315</v>
+        <v>0.06786286210369052</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1134,45 +1134,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08652428519450117</v>
+        <v>0.06763472608356724</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>FXGB.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08599406034253509</v>
+        <v>0.06603541564190851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0809733285655958</v>
+        <v>0.06265923605585599</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9524637858072917</v>
+        <v>0.8979687308403803</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4993374137265025</v>
+        <v>0.5074946138844358</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4674317341580472</v>
+        <v>0.4709449546223916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,15 +1255,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3821474589269902</v>
+        <v>0.3926557666245505</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3751049167555192</v>
+        <v>0.3925209865220223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,30 +1285,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3709262083202152</v>
+        <v>0.3739894669752777</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3503282239621868</v>
+        <v>0.361596605997478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3401902539165829</v>
+        <v>0.3526645277683969</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1330,15 +1330,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3380042993502379</v>
+        <v>0.3501400266996011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.318119049252767</v>
+        <v>0.3329963696435516</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,60 +1360,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3103633326068698</v>
+        <v>0.3268901222977678</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3080752338779777</v>
+        <v>0.3254901960784313</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2896953523274326</v>
+        <v>0.3057651566651611</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2827390609284424</v>
+        <v>0.3036662636668019</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2786836994472712</v>
+        <v>0.292451376117157</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.467121202513582</v>
+        <v>1.387510428781565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.44717673144374</v>
+        <v>1.372175683228768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.00547809042086</v>
+        <v>0.9076566661780285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7601120374455148</v>
+        <v>0.7310233514806357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7374031979497464</v>
+        <v>0.7092564003267094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6451162194583042</v>
+        <v>0.6597254718136574</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6381355821968255</v>
+        <v>0.6151502062243546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,120 +1571,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5932264275497854</v>
+        <v>0.6051839312446101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5846437820560926</v>
+        <v>0.5599801066094938</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5769307839758722</v>
+        <v>0.5314311435531391</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5396203271828697</v>
+        <v>0.5246897359240259</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5381186269357647</v>
+        <v>0.5180081665344127</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5127799866817875</v>
+        <v>0.5164213160989519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4906856524948959</v>
+        <v>0.4804933116955596</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4800230044111891</v>
+        <v>0.4786726455732113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.561970969888691</v>
+        <v>2.406330652017598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.450733083508396</v>
+        <v>2.332574000659519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.914842135764308</v>
+        <v>1.890154473046646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1767,30 +1767,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.887962616032296</v>
+        <v>1.870244513149594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.746462215346856</v>
+        <v>1.867568126188137</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.590832236930241</v>
+        <v>1.586446201317699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.474424807178545</v>
+        <v>1.526648545140758</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.370262532365149</v>
+        <v>1.313277463889482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,45 +1842,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.279800659040489</v>
+        <v>1.279710484528673</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.252991789641499</v>
+        <v>1.273867020164409</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.244035116578254</v>
+        <v>1.245147659976802</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.197579049798432</v>
+        <v>1.219849585812543</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.181463927366084</v>
+        <v>1.124631913530533</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.158313453981343</v>
+        <v>1.100948708658672</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.091798964307086</v>
+        <v>1.043428462522633</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9163219459393543</v>
+        <v>0.880874416537154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9077934433200372</v>
+        <v>0.872855243408255</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8183782243018178</v>
+        <v>0.775618271580834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5443625170336173</v>
+        <v>0.5375374843722907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.477822114966254</v>
+        <v>0.4845990708287051</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4692470791835339</v>
+        <v>0.4710161436625175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4475855718641371</v>
+        <v>0.466839765932423</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4214286223311265</v>
+        <v>0.4305861317445561</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4045114251564155</v>
+        <v>0.39393116403113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3902415278978006</v>
+        <v>0.3841969894903994</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3717407760251727</v>
+        <v>0.3250558729523001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,60 +2143,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3309821096289747</v>
+        <v>0.3184199434913597</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3223483866939323</v>
+        <v>0.3149755946311914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2867962398651125</v>
+        <v>0.2819578042234534</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2850500390152404</v>
+        <v>0.2717733709505992</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1662201862211719</v>
+        <v>0.1844416347414111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1357922778990419</v>
+        <v>0.1557678940227598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05542473983846063</v>
+        <v>0.1554062219894656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03549486957619363</v>
+        <v>0.09428569025346056</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03212421411292521</v>
+        <v>0.08440713862892935</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02891857507607032</v>
+        <v>0.07154424722588226</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02878046642379473</v>
+        <v>0.07066502114735651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0284923578373717</v>
+        <v>0.06901573730933563</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02573844374025458</v>
+        <v>0.06232971570782064</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02506566586094117</v>
+        <v>0.05487354484870788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02221404548110706</v>
+        <v>0.05240331595106751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02177779728804174</v>
+        <v>0.05125501327677995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02114864932084637</v>
+        <v>0.04792108451984256</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>AASU.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01869389218942108</v>
+        <v>0.04652231795817108</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>E127.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01636885527931198</v>
+        <v>0.04494908492633587</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Core MSCI Emerging Markets Swap UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -698,225 +698,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5789248070945556</v>
+        <v>0.2894067563361487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1179466960840216</v>
+        <v>0.2229958970537069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09655907750263504</v>
+        <v>0.09675213373352531</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08295164622566098</v>
+        <v>0.09013647023341198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0754509646725301</v>
+        <v>0.07942277572147938</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07437592373156043</v>
+        <v>0.07940200263420238</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0692575319936608</v>
+        <v>0.07607436896443764</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05938015212324532</v>
+        <v>0.07077340793673859</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05636222103442612</v>
+        <v>0.06368274988597467</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04548592369126525</v>
+        <v>0.05842723747776568</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04483016453334177</v>
+        <v>0.05423175748183406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04400193673443353</v>
+        <v>0.05262457208063909</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04392766959200722</v>
+        <v>0.04857414861407472</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04319562241212282</v>
+        <v>0.04791027161657624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04173135228687785</v>
+        <v>0.04622602997290381</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -954,225 +954,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3478688935431322</v>
+        <v>0.8412698586395342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2142933433889962</v>
+        <v>0.4091211298945554</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1905033006514125</v>
+        <v>0.1765346973870849</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1725546997681087</v>
+        <v>0.1642383874985218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1338365699287341</v>
+        <v>0.1511498173561483</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.118855238715698</v>
+        <v>0.148051632646834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1073621477568285</v>
+        <v>0.1295283994611274</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1060051277019172</v>
+        <v>0.1176556009639622</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1054545837366323</v>
+        <v>0.1022349716379245</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1049811778417624</v>
+        <v>0.0978627166038073</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1049153145841715</v>
+        <v>0.09445543553436542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06786286210369052</v>
+        <v>0.07380291797917971</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06763472608356724</v>
+        <v>0.07046073881615222</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FXGB.L</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06603541564190851</v>
+        <v>0.07024077016833497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>XUCM.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06265923605585599</v>
+        <v>0.06965924650604438</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8979687308403803</v>
+        <v>0.9540680070495957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5074946138844358</v>
+        <v>0.5576872267167552</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4709449546223916</v>
+        <v>0.4973392818525972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3926557666245505</v>
+        <v>0.4545997153642742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3925209865220223</v>
+        <v>0.4528881596555536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,60 +1285,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3739894669752777</v>
+        <v>0.3947425893073566</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.361596605997478</v>
+        <v>0.3807543655422825</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3526645277683969</v>
+        <v>0.3789918596552098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3501400266996011</v>
+        <v>0.3645446282343539</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3329963696435516</v>
+        <v>0.3620427468849707</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3268901222977678</v>
+        <v>0.3585356784004696</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3254901960784313</v>
+        <v>0.3452231908974583</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3057651566651611</v>
+        <v>0.328699813390684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3036662636668019</v>
+        <v>0.3266199989770131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.292451376117157</v>
+        <v>0.3225290104236842</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.387510428781565</v>
+        <v>1.545050083358745</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.372175683228768</v>
+        <v>1.525279586240195</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9076566661780285</v>
+        <v>0.9201632472427208</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7310233514806357</v>
+        <v>0.7793334671467114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7092564003267094</v>
+        <v>0.7237792197428712</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6597254718136574</v>
+        <v>0.637267809676006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,135 +1556,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6151502062243546</v>
+        <v>0.6366827811738285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6051839312446101</v>
+        <v>0.6086101047216479</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5599801066094938</v>
+        <v>0.5684427995773844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5314311435531391</v>
+        <v>0.5667946531981876</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5246897359240259</v>
+        <v>0.5548063480342644</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5180081665344127</v>
+        <v>0.5469126425140787</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5164213160989519</v>
+        <v>0.5271283230468229</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4804933116955596</v>
+        <v>0.4978674998297241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4786726455732113</v>
+        <v>0.462695034846988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.406330652017598</v>
+        <v>2.558762225271023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.332574000659519</v>
+        <v>2.369379405543236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.890154473046646</v>
+        <v>2.116275897897606</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1767,30 +1767,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.870244513149594</v>
+        <v>2.083636953513313</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.867568126188137</v>
+        <v>2.077876774288821</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.586446201317699</v>
+        <v>1.649652762627953</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.526648545140758</v>
+        <v>1.54003012362438</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1827,75 +1827,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.313277463889482</v>
+        <v>1.405127133355601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.279710484528673</v>
+        <v>1.350206787846857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.273867020164409</v>
+        <v>1.345886508779605</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.245147659976802</v>
+        <v>1.305096997673608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.219849585812543</v>
+        <v>1.249546360190954</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.124631913530533</v>
+        <v>1.198211646658088</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.100948708658672</v>
+        <v>1.189241309650376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.043428462522633</v>
+        <v>1.089509505003172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.880874416537154</v>
+        <v>0.990439879929337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.872855243408255</v>
+        <v>0.9809973693312897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.775618271580834</v>
+        <v>0.8283122548750048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5375374843722907</v>
+        <v>0.5959596025341753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,90 +2038,90 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4845990708287051</v>
+        <v>0.4958740179952974</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4710161436625175</v>
+        <v>0.4454678648666379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.466839765932423</v>
+        <v>0.4440271743236948</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4305861317445561</v>
+        <v>0.4396098875179806</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.39393116403113</v>
+        <v>0.4263406908139054</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3841969894903994</v>
+        <v>0.4109890671891172</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3250558729523001</v>
+        <v>0.3695058579331729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,30 +2143,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3184199434913597</v>
+        <v>0.3449538779719141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3149755946311914</v>
+        <v>0.3263356837304101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2819578042234534</v>
+        <v>0.3228196226984863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2717733709505992</v>
+        <v>0.3225666161939402</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1844416347414111</v>
+        <v>0.2233973472938209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,150 +457,150 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1557678940227598</v>
+        <v>0.1814387065806573</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1554062219894656</v>
+        <v>0.1355354429882094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09428569025346056</v>
+        <v>0.1249728987347491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08440713862892935</v>
+        <v>0.1113864647254532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07154424722588226</v>
+        <v>0.1035402870741335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07066502114735651</v>
+        <v>0.0946375137629889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06901573730933563</v>
+        <v>0.09201627461835682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06232971570782064</v>
+        <v>0.07284214622096008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05487354484870788</v>
+        <v>0.0692223889939334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05240331595106751</v>
+        <v>0.06868456120312194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05125501327677995</v>
+        <v>0.06680803564806848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -622,45 +622,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04792108451984256</v>
+        <v>0.06521746126324657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASU.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04652231795817108</v>
+        <v>0.06456140886273309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF USD</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E127.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04494908492633587</v>
+        <v>0.06215812839690149</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Emerging Markets Swap UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2894067563361487</v>
+        <v>0.2888709770736286</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2229958970537069</v>
+        <v>0.2362752443383098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,30 +728,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09675213373352531</v>
+        <v>0.1155035200358188</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09013647023341198</v>
+        <v>0.1074539829597532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07942277572147938</v>
+        <v>0.1065741040150354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07940200263420238</v>
+        <v>0.09913000738890143</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07607436896443764</v>
+        <v>0.08821139785485532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07077340793673859</v>
+        <v>0.08489211061579516</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,105 +818,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06368274988597467</v>
+        <v>0.07295513453595293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05842723747776568</v>
+        <v>0.0707788262430844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05423175748183406</v>
+        <v>0.06766831494864967</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05262457208063909</v>
+        <v>0.06125755286333812</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04857414861407472</v>
+        <v>0.06031273889197863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>FUJI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04791027161657624</v>
+        <v>0.05602104256486529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04622602997290381</v>
+        <v>0.05518692797530722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8412698586395342</v>
+        <v>0.840504767094826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4091211298945554</v>
+        <v>0.4447965938747735</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,15 +984,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1765346973870849</v>
+        <v>0.1942484463114447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1642383874985218</v>
+        <v>0.1655303492690579</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1511498173561483</v>
+        <v>0.15976988571314</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,45 +1029,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.148051632646834</v>
+        <v>0.1524543294573817</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1295283994611274</v>
+        <v>0.1449061577665898</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1176556009639622</v>
+        <v>0.1309332493592603</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1022349716379245</v>
+        <v>0.1237990789583456</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1089,15 +1089,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0978627166038073</v>
+        <v>0.1103384924233064</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09445543553436542</v>
+        <v>0.1065468263177731</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,60 +1119,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07380291797917971</v>
+        <v>0.09567838517984795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07046073881615222</v>
+        <v>0.0904746905159739</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07024077016833497</v>
+        <v>0.08928926959660366</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XUCM.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06965924650604438</v>
+        <v>0.08888896339744146</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Communication Services UCITS ETF 1D</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9540680070495957</v>
+        <v>0.9995384062203558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5576872267167552</v>
+        <v>0.5693333943684895</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,105 +1240,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4973392818525972</v>
+        <v>0.4878362681073034</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4545997153642742</v>
+        <v>0.4874729350922908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4528881596555536</v>
+        <v>0.4688809309533883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3947425893073566</v>
+        <v>0.4235835738267033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3807543655422825</v>
+        <v>0.4099206375860642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3789918596552098</v>
+        <v>0.395562209624343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3645446282343539</v>
+        <v>0.3801806291692906</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3620427468849707</v>
+        <v>0.3760966336885747</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3585356784004696</v>
+        <v>0.3649671171081843</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3452231908974583</v>
+        <v>0.3373969260614571</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.328699813390684</v>
+        <v>0.3373226524066433</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3266199989770131</v>
+        <v>0.3322528115874468</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3225290104236842</v>
+        <v>0.3300130338963314</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.545050083358745</v>
+        <v>1.54177746557231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.525279586240195</v>
+        <v>1.524991949979612</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9201632472427208</v>
+        <v>0.9511261250376557</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7793334671467114</v>
+        <v>0.7693927458673695</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7237792197428712</v>
+        <v>0.7317351232798208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.637267809676006</v>
+        <v>0.6470964277764826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6366827811738285</v>
+        <v>0.6411154791276881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6086101047216479</v>
+        <v>0.6017192879416911</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5684427995773844</v>
+        <v>0.5774898344816326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,45 +1601,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5667946531981876</v>
+        <v>0.545596989365829</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5548063480342644</v>
+        <v>0.5418922427912238</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5469126425140787</v>
+        <v>0.5405183523685291</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5271283230468229</v>
+        <v>0.5306546494381421</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4978674998297241</v>
+        <v>0.4982688835937195</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.462695034846988</v>
+        <v>0.4872304995552654</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.558762225271023</v>
+        <v>2.527143015562955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.369379405543236</v>
+        <v>2.342994011976048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.116275897897606</v>
+        <v>2.151424333446436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.083636953513313</v>
+        <v>2.124296305897397</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.077876774288821</v>
+        <v>2.107909971546635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.649652762627953</v>
+        <v>1.636023629512342</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.54003012362438</v>
+        <v>1.529132294915719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.405127133355601</v>
+        <v>1.439682499522868</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.350206787846857</v>
+        <v>1.390388014893023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,30 +1857,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.345886508779605</v>
+        <v>1.329446656001242</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.305096997673608</v>
+        <v>1.320104150516548</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.249546360190954</v>
+        <v>1.239756643317366</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.198211646658088</v>
+        <v>1.201109527988217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.189241309650376</v>
+        <v>1.192579279978701</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.089509505003172</v>
+        <v>1.08248724326074</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.990439879929337</v>
+        <v>1.012890025592216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9809973693312897</v>
+        <v>1.007117846976952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8283122548750048</v>
+        <v>0.8708563668189291</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5959596025341753</v>
+        <v>0.6066066222434439</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4958740179952974</v>
+        <v>0.5016808217734332</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,45 +2053,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4454678648666379</v>
+        <v>0.4442619469584304</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4440271743236948</v>
+        <v>0.443316188713371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4396098875179806</v>
+        <v>0.4417442518031656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4263406908139054</v>
+        <v>0.4345680574852435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4109890671891172</v>
+        <v>0.4181319133529919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3695058579331729</v>
+        <v>0.3573379494927267</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,30 +2143,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3449538779719141</v>
+        <v>0.3392777552104347</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3263356837304101</v>
+        <v>0.3380357807420507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3228196226984863</v>
+        <v>0.3332007688626955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3225666161939402</v>
+        <v>0.3168922329238277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2233973472938209</v>
+        <v>0.2053828912350453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1814387065806573</v>
+        <v>0.1889952082728306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,15 +472,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1355354429882094</v>
+        <v>0.1106524237299136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1249728987347491</v>
+        <v>0.1017348231949355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1113864647254532</v>
+        <v>0.09621783581362697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,30 +517,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1035402870741335</v>
+        <v>0.07083603094749225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0946375137629889</v>
+        <v>0.07047821810809451</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09201627461835682</v>
+        <v>0.06036852473891074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -562,90 +562,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07284214622096008</v>
+        <v>0.05935832302367738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0692223889939334</v>
+        <v>0.05921164250570254</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06868456120312194</v>
+        <v>0.05379230882288932</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06680803564806848</v>
+        <v>0.05358870073644417</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06521746126324657</v>
+        <v>0.04539110237827204</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06456140886273309</v>
+        <v>0.04499032920411516</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06215812839690149</v>
+        <v>0.04016161200973412</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2888709770736286</v>
+        <v>0.1880976213097016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2362752443383098</v>
+        <v>0.1770963707618485</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,45 +728,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1155035200358188</v>
+        <v>0.1193559051127777</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1074539829597532</v>
+        <v>0.1103758714851957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1065741040150354</v>
+        <v>0.1063943607438533</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09913000738890143</v>
+        <v>0.1054789414392532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,45 +788,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08821139785485532</v>
+        <v>0.105365962612064</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08489211061579516</v>
+        <v>0.09939156044520825</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07295513453595293</v>
+        <v>0.09883038296076974</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0707788262430844</v>
+        <v>0.08914009539571133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06766831494864967</v>
+        <v>0.07896151778170357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06125755286333812</v>
+        <v>0.07057339107507921</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06031273889197863</v>
+        <v>0.06548043158751193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FUJI.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05602104256486529</v>
+        <v>0.06334256204660593</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05518692797530722</v>
+        <v>0.05863515790017781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.840504767094826</v>
+        <v>0.8058901653181358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4447965938747735</v>
+        <v>0.3292142921517602</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,195 +984,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1942484463114447</v>
+        <v>0.2199999762970266</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1655303492690579</v>
+        <v>0.1857913345693929</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.15976988571314</v>
+        <v>0.17916773906581</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1524543294573817</v>
+        <v>0.1770486723999787</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1449061577665898</v>
+        <v>0.1539221263927684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1309332493592603</v>
+        <v>0.1374928894924947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1237990789583456</v>
+        <v>0.1359935151920897</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1103384924233064</v>
+        <v>0.1352486134049935</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1065468263177731</v>
+        <v>0.1065979589360495</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09567838517984795</v>
+        <v>0.08537029293998288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>LAFRI.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0904746905159739</v>
+        <v>0.08362909693693577</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi Pan Africa UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08928926959660366</v>
+        <v>0.08094137120950573</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08888896339744146</v>
+        <v>0.0781385400592336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9995384062203558</v>
+        <v>0.8969026929818689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5693333943684895</v>
+        <v>0.5588859110808735</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,30 +1240,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4878362681073034</v>
+        <v>0.4694392232822167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4874729350922908</v>
+        <v>0.4688257462095826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4688809309533883</v>
+        <v>0.4255809113409286</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,75 +1285,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4235835738267033</v>
+        <v>0.3944621971632141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4099206375860642</v>
+        <v>0.3881435218880906</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.395562209624343</v>
+        <v>0.3687774478123225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3801806291692906</v>
+        <v>0.3685832437239207</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3760966336885747</v>
+        <v>0.3542234006346385</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3649671171081843</v>
+        <v>0.3278165418478569</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3373969260614571</v>
+        <v>0.3110533415651746</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3373226524066433</v>
+        <v>0.3077086317325941</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3322528115874468</v>
+        <v>0.2981919694386055</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3300130338963314</v>
+        <v>0.2954495739766714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.54177746557231</v>
+        <v>1.48965498084195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.524991949979612</v>
+        <v>1.466785082516361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9511261250376557</v>
+        <v>0.8885762807411031</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7693927458673695</v>
+        <v>0.7452115036484237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7317351232798208</v>
+        <v>0.7025262651601194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6470964277764826</v>
+        <v>0.6352292824638675</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6411154791276881</v>
+        <v>0.627500025431315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6017192879416911</v>
+        <v>0.5754903366179707</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,60 +1586,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5774898344816326</v>
+        <v>0.54715581962541</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.545596989365829</v>
+        <v>0.5470769838701037</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5418922427912238</v>
+        <v>0.5298397705069757</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5405183523685291</v>
+        <v>0.5267355053728426</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5306546494381421</v>
+        <v>0.4953391817104531</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4982688835937195</v>
+        <v>0.4828892485560854</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4872304995552654</v>
+        <v>0.4618668677144599</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.527143015562955</v>
+        <v>2.515527815764706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.342994011976048</v>
+        <v>2.327916461633829</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.151424333446436</v>
+        <v>2.116443980143969</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1767,30 +1767,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.124296305897397</v>
+        <v>2.100401539014188</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.107909971546635</v>
+        <v>2.078198464063884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.636023629512342</v>
+        <v>1.609567244899499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.529132294915719</v>
+        <v>1.493923909867366</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.439682499522868</v>
+        <v>1.432622712661586</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.390388014893023</v>
+        <v>1.36281264531934</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.329446656001242</v>
+        <v>1.325117942528697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.320104150516548</v>
+        <v>1.300115888556472</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.239756643317366</v>
+        <v>1.214564534165369</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,30 +1902,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.201109527988217</v>
+        <v>1.179740661313455</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.192579279978701</v>
+        <v>1.171303217838356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.08248724326074</v>
+        <v>1.077415576708789</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.012890025592216</v>
+        <v>0.9905472380764435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.007117846976952</v>
+        <v>0.9775035620333261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8708563668189291</v>
+        <v>0.8118994997560465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6066066222434439</v>
+        <v>0.6044225180646166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5016808217734332</v>
+        <v>0.4922065691136379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4442619469584304</v>
+        <v>0.4745364440110598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2068,30 +2068,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.443316188713371</v>
+        <v>0.457847470297476</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4417442518031656</v>
+        <v>0.4286811552324976</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4345680574852435</v>
+        <v>0.4263406908139054</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4181319133529919</v>
+        <v>0.4258241877244715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3573379494927267</v>
+        <v>0.3528681133087275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3392777552104347</v>
+        <v>0.3360421799333941</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3380357807420507</v>
+        <v>0.324606618406504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3332007688626955</v>
+        <v>0.3225987848949639</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3168922329238277</v>
+        <v>0.3073082832857461</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,60 +442,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2053828912350453</v>
+        <v>0.1535840431728839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1889952082728306</v>
+        <v>0.1395564609292019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1106524237299136</v>
+        <v>0.06613480085316104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1017348231949355</v>
+        <v>0.06465073068662952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09621783581362697</v>
+        <v>0.0472225921565701</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -517,75 +517,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07083603094749225</v>
+        <v>0.04247261956212389</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07047821810809451</v>
+        <v>0.03874213369470381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06036852473891074</v>
+        <v>0.03800922495126446</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05935832302367738</v>
+        <v>0.02991162426302063</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05921164250570254</v>
+        <v>0.02951438879948709</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05379230882288932</v>
+        <v>0.02704611564004789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -607,60 +607,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05358870073644417</v>
+        <v>0.02406738913025186</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04539110237827204</v>
+        <v>0.0223423826921465</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04499032920411516</v>
+        <v>0.02207100949997853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04016161200973412</v>
+        <v>0.0216404027205519</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1880976213097016</v>
+        <v>0.1848750114440918</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1770963707618485</v>
+        <v>0.1395564609292019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1193559051127777</v>
+        <v>0.09640512227015474</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,90 +743,90 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1103758714851957</v>
+        <v>0.08627493097633288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1063943607438533</v>
+        <v>0.08518112091276375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1054789414392532</v>
+        <v>0.08329910959036568</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.105365962612064</v>
+        <v>0.07672937219662002</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09939156044520825</v>
+        <v>0.06792373609176106</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09883038296076974</v>
+        <v>0.06766912336677788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08914009539571133</v>
+        <v>0.06605507268135957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -848,75 +848,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07896151778170357</v>
+        <v>0.06090724376439183</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07057339107507921</v>
+        <v>0.06035802269811263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06548043158751193</v>
+        <v>0.05171014261180185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06334256204660593</v>
+        <v>0.05034611440360082</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05863515790017781</v>
+        <v>0.04923719719737019</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8058901653181358</v>
+        <v>0.8127748949298597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,75 +969,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3292142921517602</v>
+        <v>0.2469375909282032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2199999762970266</v>
+        <v>0.2463009665591129</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1857913345693929</v>
+        <v>0.1875938347893507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.17916773906581</v>
+        <v>0.1830155667579518</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1770486723999787</v>
+        <v>0.17732009998659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1539221263927684</v>
+        <v>0.1523525393879634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,60 +1059,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1374928894924947</v>
+        <v>0.1237149026478854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1359935151920897</v>
+        <v>0.1234145178317736</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1352486134049935</v>
+        <v>0.1213102828070332</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1065979589360495</v>
+        <v>0.09063609044060916</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08537029293998288</v>
+        <v>0.08552029550778073</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1134,45 +1134,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LAFRI.MI</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08362909693693577</v>
+        <v>0.08513963460845986</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Pan Africa UCITS ETF Acc</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08094137120950573</v>
+        <v>0.08133328755696612</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0781385400592336</v>
+        <v>0.07547265502028888</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8969026929818689</v>
+        <v>0.9006268058679827</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5588859110808735</v>
+        <v>0.5794481560945941</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4694392232822167</v>
+        <v>0.5340879844847468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4688257462095826</v>
+        <v>0.5331481459887195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4255809113409286</v>
+        <v>0.422001277988449</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,60 +1285,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3944621971632141</v>
+        <v>0.4099935874413128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3881435218880906</v>
+        <v>0.4064599122297141</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3687774478123225</v>
+        <v>0.3897830744853472</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3685832437239207</v>
+        <v>0.3785770714447796</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3542234006346385</v>
+        <v>0.3593862073912699</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3278165418478569</v>
+        <v>0.347459290903364</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1375,60 +1375,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3110533415651746</v>
+        <v>0.3244513783593876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3077086317325941</v>
+        <v>0.3211785720125477</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2981919694386055</v>
+        <v>0.3157658043969163</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2954495739766714</v>
+        <v>0.3135178933013441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.48965498084195</v>
+        <v>1.475694431801667</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.466785082516361</v>
+        <v>1.457608847245611</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8885762807411031</v>
+        <v>0.909767534099345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7452115036484237</v>
+        <v>0.7418677677880954</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,120 +1526,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7025262651601194</v>
+        <v>0.6423645322538971</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6352292824638675</v>
+        <v>0.6281965177537774</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.627500025431315</v>
+        <v>0.6030493275778106</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5754903366179707</v>
+        <v>0.5588235228664864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.54715581962541</v>
+        <v>0.5288653648065658</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5470769838701037</v>
+        <v>0.5221855126624266</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5298397705069757</v>
+        <v>0.5164457749865043</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5267355053728426</v>
+        <v>0.5048652406627163</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4953391817104531</v>
+        <v>0.4912177943403786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4828892485560854</v>
+        <v>0.4771448691922031</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4618668677144599</v>
+        <v>0.4486394278225887</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.515527815764706</v>
+        <v>2.505353807524917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.327916461633829</v>
+        <v>2.331165344763281</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.116443980143969</v>
+        <v>2.064148694718499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.100401539014188</v>
+        <v>2.044553805199109</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.078198464063884</v>
+        <v>2.032126421054758</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.609567244899499</v>
+        <v>1.616460408305985</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.493923909867366</v>
+        <v>1.459290031439346</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.432622712661586</v>
+        <v>1.405933784382503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.36281264531934</v>
+        <v>1.343482629576726</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.325117942528697</v>
+        <v>1.317301605603459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.300115888556472</v>
+        <v>1.306098562114057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.214564534165369</v>
+        <v>1.208521298442205</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.179740661313455</v>
+        <v>1.202355905056381</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.171303217838356</v>
+        <v>1.189722213699904</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.077415576708789</v>
+        <v>1.071292343040347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9905472380764435</v>
+        <v>0.9502658056597904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9775035620333261</v>
+        <v>0.9437299645541983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8118994997560465</v>
+        <v>0.8008854414778008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6044225180646166</v>
+        <v>0.586131524259464</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4922065691136379</v>
+        <v>0.5050457136984245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4745364440110598</v>
+        <v>0.4789119066117375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.457847470297476</v>
+        <v>0.4756491417990207</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,45 +2083,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4286811552324976</v>
+        <v>0.4481685330504401</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4263406908139054</v>
+        <v>0.4103875521932612</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4258241877244715</v>
+        <v>0.409550334815624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3528681133087275</v>
+        <v>0.3282841090247477</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,45 +2143,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3360421799333941</v>
+        <v>0.3195875904567578</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.324606618406504</v>
+        <v>0.3089044818783666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3225987848949639</v>
+        <v>0.3060196786721616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3073082832857461</v>
+        <v>0.2955270543378012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1535840431728839</v>
+        <v>0.08909027986920726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,60 +457,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1395564609292019</v>
+        <v>0.08044775103862611</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06613480085316104</v>
+        <v>0.05082806160053965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06465073068662952</v>
+        <v>0.05072398596386596</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0472225921565701</v>
+        <v>0.05007103451312145</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04247261956212389</v>
+        <v>0.04895103180519556</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03874213369470381</v>
+        <v>0.0474235613181262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -547,120 +547,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03800922495126446</v>
+        <v>0.04597424638619851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02991162426302063</v>
+        <v>0.04382050531965853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02951438879948709</v>
+        <v>0.03697471895344862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02704611564004789</v>
+        <v>0.03517669464796347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02406738913025186</v>
+        <v>0.02946242345794281</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0223423826921465</v>
+        <v>0.02777778806053477</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02207100949997853</v>
+        <v>0.02739807803586403</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0216404027205519</v>
+        <v>0.02583437781293152</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1848750114440918</v>
+        <v>0.2530840381988837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1395564609292019</v>
+        <v>0.1336801141071806</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09640512227015474</v>
+        <v>0.1143720824078363</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,180 +743,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08627493097633288</v>
+        <v>0.101857856581187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08518112091276375</v>
+        <v>0.09596642953621104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08329910959036568</v>
+        <v>0.09009291724855029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07672937219662002</v>
+        <v>0.08473952333602686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06792373609176106</v>
+        <v>0.07568760582037726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06766912336677788</v>
+        <v>0.07459074190536086</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06605507268135957</v>
+        <v>0.06753239520116838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06090724376439183</v>
+        <v>0.06502280288375406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06035802269811263</v>
+        <v>0.05960268624993703</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05171014261180185</v>
+        <v>0.05900256239449719</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05034611440360082</v>
+        <v>0.05702393493765956</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04923719719737019</v>
+        <v>0.05701615847568831</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8127748949298597</v>
+        <v>0.8842990083538147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2469375909282032</v>
+        <v>0.2447689853700563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2463009665591129</v>
+        <v>0.227169022240902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1875938347893507</v>
+        <v>0.1765857029727509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1830155667579518</v>
+        <v>0.1677082655394619</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.17732009998659</v>
+        <v>0.1649403956666899</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1523525393879634</v>
+        <v>0.1477382535120384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1237149026478854</v>
+        <v>0.1349686243133257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,75 +1074,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1234145178317736</v>
+        <v>0.1277282163151328</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1213102828070332</v>
+        <v>0.1181758495197651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09063609044060916</v>
+        <v>0.1043317907541939</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08552029550778073</v>
+        <v>0.09574787460508749</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08513963460845986</v>
+        <v>0.09361760128086249</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08133328755696612</v>
+        <v>0.08992331210938564</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07547265502028888</v>
+        <v>0.08731240347556013</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9006268058679827</v>
+        <v>1.076041168342571</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5794481560945941</v>
+        <v>0.6514939643349518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5340879844847468</v>
+        <v>0.561699548439524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5331481459887195</v>
+        <v>0.5509103249039156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,75 +1270,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.422001277988449</v>
+        <v>0.4910219942835556</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4099935874413128</v>
+        <v>0.4628303191729708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4064599122297141</v>
+        <v>0.4548981128677989</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3897830744853472</v>
+        <v>0.435527326530448</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3785770714447796</v>
+        <v>0.418994820676756</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3593862073912699</v>
+        <v>0.4130216000461178</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.347459290903364</v>
+        <v>0.3822146131141775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1375,30 +1375,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3244513783593876</v>
+        <v>0.3758706874556599</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3211785720125477</v>
+        <v>0.3487168603804243</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3157658043969163</v>
+        <v>0.3425241349231829</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3135178933013441</v>
+        <v>0.342015155879152</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.475694431801667</v>
+        <v>1.500373802920898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.457608847245611</v>
+        <v>1.48238367306157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.909767534099345</v>
+        <v>1.016885671803625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7418677677880954</v>
+        <v>0.7850890730525906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,120 +1526,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6423645322538971</v>
+        <v>0.640690540138646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6281965177537774</v>
+        <v>0.6219462506163025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6030493275778106</v>
+        <v>0.6002048680071732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5588235228664864</v>
+        <v>0.543070544388772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5288653648065658</v>
+        <v>0.5393215003641756</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5221855126624266</v>
+        <v>0.5391769948557217</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5164457749865043</v>
+        <v>0.5276162651007679</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5048652406627163</v>
+        <v>0.5211423692384696</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4912177943403786</v>
+        <v>0.5094211104326258</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,30 +1661,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4771448691922031</v>
+        <v>0.4865722424461485</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4486394278225887</v>
+        <v>0.4453056667190589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.505353807524917</v>
+        <v>2.601681922513381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.331165344763281</v>
+        <v>2.393582634807495</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.064148694718499</v>
+        <v>2.183721564188286</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1767,30 +1767,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.044553805199109</v>
+        <v>2.154104103243673</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.032126421054758</v>
+        <v>2.075420980069676</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.616460408305985</v>
+        <v>1.631252614610813</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.459290031439346</v>
+        <v>1.509956038944156</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.405933784382503</v>
+        <v>1.468077201577212</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,30 +1842,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.343482629576726</v>
+        <v>1.388575637074866</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.317301605603459</v>
+        <v>1.383951855075476</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.306098562114057</v>
+        <v>1.329686212087587</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,45 +1887,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.208521298442205</v>
+        <v>1.269246280937221</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.202355905056381</v>
+        <v>1.256728866767681</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.189722213699904</v>
+        <v>1.240786804249637</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.071292343040347</v>
+        <v>1.102537906077942</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9502658056597904</v>
+        <v>0.9764756172437836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9437299645541983</v>
+        <v>0.9678539264872481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8008854414778008</v>
+        <v>0.8572509834863269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.586131524259464</v>
+        <v>0.6145235768175137</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5050457136984245</v>
+        <v>0.4960268623696451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4789119066117375</v>
+        <v>0.4799342092305467</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4756491417990207</v>
+        <v>0.446447861411418</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4481685330504401</v>
+        <v>0.4302197531178165</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4103875521932612</v>
+        <v>0.427604172409694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.409550334815624</v>
+        <v>0.4226469200984937</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3282841090247477</v>
+        <v>0.3409485817274014</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3195875904567578</v>
+        <v>0.3243352636570507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3089044818783666</v>
+        <v>0.3197273879066995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,15 +2173,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3060196786721616</v>
+        <v>0.3075077400186281</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2955270543378012</v>
+        <v>0.304512768418939</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08909027986920726</v>
+        <v>0.03786768772179561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08044775103862611</v>
+        <v>0.03147038949100245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05082806160053965</v>
+        <v>0.02350583131431327</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05072398596386596</v>
+        <v>0.0204220974586673</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05007103451312145</v>
+        <v>0.01534837451268833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04895103180519556</v>
+        <v>0.01474555779827735</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0474235613181262</v>
+        <v>0.01248783770424411</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04597424638619851</v>
+        <v>0.01182739081937911</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04382050531965853</v>
+        <v>0.01121644835385505</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>SMARTU.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03697471895344862</v>
+        <v>0.009687198677771125</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Smart Overnight Return UCITS ETF USD Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>FEDF.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03517669464796347</v>
+        <v>0.00958413383917267</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi USD Fed Funds Rate UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02946242345794281</v>
+        <v>0.009163525621242785</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02777778806053477</v>
+        <v>0.007511730194512012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02739807803586403</v>
+        <v>0.007434578279956083</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02583437781293152</v>
+        <v>0.007374334988495157</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2530840381988837</v>
+        <v>0.1117607042672772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,45 +713,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1336801141071806</v>
+        <v>0.0980864514069022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1143720824078363</v>
+        <v>0.09625307835864549</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.101857856581187</v>
+        <v>0.08679374084238911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09596642953621104</v>
+        <v>0.06378594386572844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09009291724855029</v>
+        <v>0.05995888414458128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08473952333602686</v>
+        <v>0.04950286665251036</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07568760582037726</v>
+        <v>0.04298949638016736</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07459074190536086</v>
+        <v>0.04159915981860496</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06753239520116838</v>
+        <v>0.04020585541941024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06502280288375406</v>
+        <v>0.04001941240153806</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05960268624993703</v>
+        <v>0.03802697350290662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05900256239449719</v>
+        <v>0.03399342739987632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05702393493765956</v>
+        <v>0.03221717247596145</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05701615847568831</v>
+        <v>0.03215798655913837</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8842990083538147</v>
+        <v>0.8548479993813609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2447689853700563</v>
+        <v>0.2521568148743873</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.227169022240902</v>
+        <v>0.2460454366704505</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,30 +999,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1765857029727509</v>
+        <v>0.1822328776130575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1677082655394619</v>
+        <v>0.1731062557439513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1649403956666899</v>
+        <v>0.1446990867493982</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1477382535120384</v>
+        <v>0.1376652260559468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,120 +1059,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1349686243133257</v>
+        <v>0.1295577992097598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1277282163151328</v>
+        <v>0.1246218149897624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1181758495197651</v>
+        <v>0.1100365259002194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1043317907541939</v>
+        <v>0.09861762757585146</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09574787460508749</v>
+        <v>0.0941096057630566</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09361760128086249</v>
+        <v>0.09042890159200945</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08992331210938564</v>
+        <v>0.08203635475852278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08731240347556013</v>
+        <v>0.07823641443853413</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.076041168342571</v>
+        <v>1.092237104873664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6514939643349518</v>
+        <v>0.6372896788192355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.561699548439524</v>
+        <v>0.5559012453321908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5509103249039156</v>
+        <v>0.5542822952290449</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4910219942835556</v>
+        <v>0.4778879297177152</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4628303191729708</v>
+        <v>0.4472922662643453</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,60 +1300,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4548981128677989</v>
+        <v>0.4386137818832572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.435527326530448</v>
+        <v>0.4267237052065826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.418994820676756</v>
+        <v>0.3909365107706182</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4130216000461178</v>
+        <v>0.377422263627013</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3822146131141775</v>
+        <v>0.3755889869634468</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1375,60 +1375,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3758706874556599</v>
+        <v>0.3737579538818345</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3487168603804243</v>
+        <v>0.3572134756918468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3425241349231829</v>
+        <v>0.3443982412927296</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.342015155879152</v>
+        <v>0.3357393808096869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.500373802920898</v>
+        <v>1.500207838872266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.48238367306157</v>
+        <v>1.48392116102109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.016885671803625</v>
+        <v>1.045320523729642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7850890730525906</v>
+        <v>0.7499244983783282</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.640690540138646</v>
+        <v>0.6402294920910045</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,90 +1541,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6219462506163025</v>
+        <v>0.5702244825995306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6002048680071732</v>
+        <v>0.5662229266528687</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.543070544388772</v>
+        <v>0.5270204613714753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5393215003641756</v>
+        <v>0.5197595552747969</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5391769948557217</v>
+        <v>0.5086379258245297</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5276162651007679</v>
+        <v>0.5032353367885045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5211423692384696</v>
+        <v>0.4963716673695477</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,15 +1646,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5094211104326258</v>
+        <v>0.4961300899193848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4865722424461485</v>
+        <v>0.492481161794863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4453056667190589</v>
+        <v>0.4262589276158191</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.601681922513381</v>
+        <v>2.559762145426994</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.393582634807495</v>
+        <v>2.316832940460801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.183721564188286</v>
+        <v>2.095920584216252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.154104103243673</v>
+        <v>2.067472820149414</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.075420980069676</v>
+        <v>1.960127456721134</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.631252614610813</v>
+        <v>1.613857555686623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.509956038944156</v>
+        <v>1.584505297364537</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.468077201577212</v>
+        <v>1.414126519045444</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.388575637074866</v>
+        <v>1.326971222106518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,30 +1857,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.383951855075476</v>
+        <v>1.313697198931707</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.329686212087587</v>
+        <v>1.289308194019038</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.269246280937221</v>
+        <v>1.218362299691028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.256728866767681</v>
+        <v>1.217045155686765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.240786804249637</v>
+        <v>1.215892889848687</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.102537906077942</v>
+        <v>1.094824296258812</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9764756172437836</v>
+        <v>0.9376980184144628</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9678539264872481</v>
+        <v>0.9307529297525776</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8572509834863269</v>
+        <v>0.8712882543279885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6145235768175137</v>
+        <v>0.5798525827311793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4960268623696451</v>
+        <v>0.4987091444227711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4799342092305467</v>
+        <v>0.4853299713011661</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.446447861411418</v>
+        <v>0.4562143088591502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4302197531178165</v>
+        <v>0.4124543022310669</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.427604172409694</v>
+        <v>0.4023097278737806</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4226469200984937</v>
+        <v>0.4011551568164833</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,75 +2128,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3409485817274014</v>
+        <v>0.3653914692935782</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3243352636570507</v>
+        <v>0.342190181838953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3197273879066995</v>
+        <v>0.3275863109640291</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3075077400186281</v>
+        <v>0.3110417786962305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.304512768418939</v>
+        <v>0.3029409343553942</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,45 +442,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03786768772179561</v>
+        <v>0.03436421920275379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03147038949100245</v>
+        <v>0.02309723250888185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02350583131431327</v>
+        <v>0.0197587288788903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0204220974586673</v>
+        <v>0.01551952866482575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,75 +502,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01534837451268833</v>
+        <v>0.01413706666677239</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01474555779827735</v>
+        <v>0.01391772132464442</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01248783770424411</v>
+        <v>0.01309247551112414</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>FEDF.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01182739081937911</v>
+        <v>0.01072937311982303</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi USD Fed Funds Rate UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01121644835385505</v>
+        <v>0.01027354809334491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009687198677771125</v>
+        <v>0.009882952756163244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -592,75 +592,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FEDF.MI</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.00958413383917267</v>
+        <v>0.008084999578229057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi USD Fed Funds Rate UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.009163525621242785</v>
+        <v>0.007793097058463649</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.007511730194512012</v>
+        <v>0.005393369561377703</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.007434578279956083</v>
+        <v>0.004385707195194488</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.007374334988495157</v>
+        <v>0.002686211750047685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0980864514069022</v>
+        <v>0.1091116567623198</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09625307835864549</v>
+        <v>0.1000673343938334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,180 +743,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08679374084238911</v>
+        <v>0.06717505441033977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06378594386572844</v>
+        <v>0.06211708903425883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05995888414458128</v>
+        <v>0.05944484224769253</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04950286665251036</v>
+        <v>0.05661352353647287</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04298949638016736</v>
+        <v>0.05142403625410963</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04159915981860496</v>
+        <v>0.05130049534615466</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04020585541941024</v>
+        <v>0.0486880840796915</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04001941240153806</v>
+        <v>0.0477776222568338</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03802697350290662</v>
+        <v>0.04731772874902007</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03399342739987632</v>
+        <v>0.04663883727597806</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03221717247596145</v>
+        <v>0.0407669096612342</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03215798655913837</v>
+        <v>0.03783620189230619</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
@@ -969,30 +969,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2521568148743873</v>
+        <v>0.2563881358590232</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2460454366704505</v>
+        <v>0.2182314863496533</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1822328776130575</v>
+        <v>0.1730257452525084</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1731062557439513</v>
+        <v>0.1439735752816793</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1446990867493982</v>
+        <v>0.1325626926030152</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,60 +1044,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1376652260559468</v>
+        <v>0.1173459511419295</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1295577992097598</v>
+        <v>0.116657662912242</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1246218149897624</v>
+        <v>0.1139336174698238</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1100365259002194</v>
+        <v>0.1109952740359084</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09861762757585146</v>
+        <v>0.08540417908756437</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,60 +1119,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>BITC.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0941096057630566</v>
+        <v>0.07885513079111872</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>CoinShares Physical Bitcoin</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09042890159200945</v>
+        <v>0.07444945066708186</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>SEL.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08203635475852278</v>
+        <v>0.07229437440328268</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07823641443853413</v>
+        <v>0.07212392452523586</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.092237104873664</v>
+        <v>1.065612433014058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6372896788192355</v>
+        <v>0.6521494670479302</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,30 +1240,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5559012453321908</v>
+        <v>0.6378313245381035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5542822952290449</v>
+        <v>0.6369459033339251</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4778879297177152</v>
+        <v>0.4651047199508807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4472922662643453</v>
+        <v>0.4509804188228106</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4386137818832572</v>
+        <v>0.4335623291139754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,120 +1315,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4267237052065826</v>
+        <v>0.4078339394352928</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3909365107706182</v>
+        <v>0.3992015758818397</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.377422263627013</v>
+        <v>0.3909365107706182</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3755889869634468</v>
+        <v>0.3670957193995761</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3737579538818345</v>
+        <v>0.3582993043236025</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3572134756918468</v>
+        <v>0.3500441874728304</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3443982412927296</v>
+        <v>0.3453964610041214</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3357393808096869</v>
+        <v>0.3399924070786511</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.500207838872266</v>
+        <v>1.524022095069106</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.48392116102109</v>
+        <v>1.512294360522028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.045320523729642</v>
+        <v>1.039142644086597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7499244983783282</v>
+        <v>0.7545277224663665</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6402294920910045</v>
+        <v>0.6485900642190565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,30 +1541,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5702244825995306</v>
+        <v>0.5589892998367629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5662229266528687</v>
+        <v>0.5549292187943315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5270204613714753</v>
+        <v>0.5192307549445832</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,15 +1586,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5197595552747969</v>
+        <v>0.5173660590535847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5086379258245297</v>
+        <v>0.5104768900295948</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5032353367885045</v>
+        <v>0.4998577468757452</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,45 +1631,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4963716673695477</v>
+        <v>0.4866666572038518</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4961300899193848</v>
+        <v>0.4730213015245344</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.492481161794863</v>
+        <v>0.4680800458037095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4262589276158191</v>
+        <v>0.4501379074949703</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.559762145426994</v>
+        <v>2.554493432857926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.316832940460801</v>
+        <v>2.302298177578384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.095920584216252</v>
+        <v>2.182762153320627</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.067472820149414</v>
+        <v>2.161571876277092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.960127456721134</v>
+        <v>1.968102154658359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.613857555686623</v>
+        <v>1.59725138752559</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.584505297364537</v>
+        <v>1.593303626097785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.414126519045444</v>
+        <v>1.420817980299286</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.326971222106518</v>
+        <v>1.337814559469384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,75 +1857,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.313697198931707</v>
+        <v>1.309748313207332</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.289308194019038</v>
+        <v>1.30354031811875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.218362299691028</v>
+        <v>1.230676309256866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.217045155686765</v>
+        <v>1.229332605832317</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.215892889848687</v>
+        <v>1.210267637012232</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.094824296258812</v>
+        <v>1.092060687935156</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9376980184144628</v>
+        <v>0.9920510716637758</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9307529297525776</v>
+        <v>0.98998149963983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8712882543279885</v>
+        <v>0.890076699679184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5798525827311793</v>
+        <v>0.600054570060303</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4987091444227711</v>
+        <v>0.5097799414084907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4853299713011661</v>
+        <v>0.4646795743868641</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4562143088591502</v>
+        <v>0.4420381884654843</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,15 +2083,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4124543022310669</v>
+        <v>0.4213036608745711</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4023097278737806</v>
+        <v>0.4122406272662142</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2113,15 +2113,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4011551568164833</v>
+        <v>0.3941392834042079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3653914692935782</v>
+        <v>0.346085729342968</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.342190181838953</v>
+        <v>0.3402036406060736</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3275863109640291</v>
+        <v>0.3341336122341727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3110417786962305</v>
+        <v>0.3175186728431598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3029409343553942</v>
+        <v>0.307240994793589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03436421920275379</v>
+        <v>0.08092966305516991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02309723250888185</v>
+        <v>0.03411765969276948</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0197587288788903</v>
+        <v>0.02933394386803978</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01551952866482575</v>
+        <v>0.02749141675880851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01413706666677239</v>
+        <v>0.02689985297253616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01391772132464442</v>
+        <v>0.02020252302504666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01309247551112414</v>
+        <v>0.01903973755007926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FEDF.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01072937311982303</v>
+        <v>0.01887174706894923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi USD Fed Funds Rate UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01027354809334491</v>
+        <v>0.01790928676783876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMARTU.MI</t>
+          <t>JPXU.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009882952756163244</v>
+        <v>0.0159441517034189</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Smart Overnight Return UCITS ETF USD Hedged Acc</t>
+          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - USD Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.008084999578229057</v>
+        <v>0.01564216452751133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.007793097058463649</v>
+        <v>0.01512677897873704</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>JPN.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.005393369561377703</v>
+        <v>0.0137185736754184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004385707195194488</v>
+        <v>0.01327513982793449</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002686211750047685</v>
+        <v>0.01324977789336534</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -698,45 +698,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1117607042672772</v>
+        <v>0.2176423603490694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1091116567623198</v>
+        <v>0.1519318065200674</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1000673343938334</v>
+        <v>0.1050169979674613</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06717505441033977</v>
+        <v>0.09791518357758067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,165 +758,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06211708903425883</v>
+        <v>0.08925436092612293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05944484224769253</v>
+        <v>0.0775956531905011</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05661352353647287</v>
+        <v>0.07010290155085097</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05142403625410963</v>
+        <v>0.05386027066015053</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05130049534615466</v>
+        <v>0.05322211964218648</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0486880840796915</v>
+        <v>0.05153619292940603</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0477776222568338</v>
+        <v>0.04964715268034259</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04731772874902007</v>
+        <v>0.04876374097320757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04663883727597806</v>
+        <v>0.04867628836643445</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0407669096612342</v>
+        <v>0.04754808518002696</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03783620189230619</v>
+        <v>0.04654507227698068</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8548479993813609</v>
+        <v>0.8588640460594228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2563881358590232</v>
+        <v>0.277323995205033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2182314863496533</v>
+        <v>0.2309679592123566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1730257452525084</v>
+        <v>0.1883311344479239</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1439735752816793</v>
+        <v>0.149886797059257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,60 +1029,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1325626926030152</v>
+        <v>0.1333332970028831</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1173459511419295</v>
+        <v>0.1280120655314936</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.116657662912242</v>
+        <v>0.1131358969238101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1139336174698238</v>
+        <v>0.1106498051078728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1109952740359084</v>
+        <v>0.1071222778310925</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,60 +1104,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08540417908756437</v>
+        <v>0.1036677082608353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BITC.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07885513079111872</v>
+        <v>0.08994266722870004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CoinShares Physical Bitcoin</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07444945066708186</v>
+        <v>0.07069212407372572</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL.PA</t>
+          <t>FXGB.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07229437440328268</v>
+        <v>0.0667241167056507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Stoxx Europe Select Dividend 30 UCITS ETF Dist</t>
+          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07212392452523586</v>
+        <v>0.06451611219192133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.065612433014058</v>
+        <v>1.034320294222848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6521494670479302</v>
+        <v>0.581606718782846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6378313245381035</v>
+        <v>0.4838594671679524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6369459033339251</v>
+        <v>0.4724860541994587</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,30 +1270,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4651047199508807</v>
+        <v>0.4141196350173779</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4509804188228106</v>
+        <v>0.4022824695947345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4335623291139754</v>
+        <v>0.397242239632952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,120 +1315,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4078339394352928</v>
+        <v>0.3939481138536409</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3992015758818397</v>
+        <v>0.3310827202712412</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3909365107706182</v>
+        <v>0.3019466983616415</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3670957193995761</v>
+        <v>0.3007289789977494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3582993043236025</v>
+        <v>0.2921840781389702</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3500441874728304</v>
+        <v>0.284915454383164</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3453964610041214</v>
+        <v>0.2744085292913025</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3399924070786511</v>
+        <v>0.2742101303069853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.524022095069106</v>
+        <v>1.515643000136636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.512294360522028</v>
+        <v>1.471313652283122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.039142644086597</v>
+        <v>1.096636277920825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7545277224663665</v>
+        <v>0.7803189800994026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,15 +1526,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6485900642190565</v>
+        <v>0.5612575789297738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5589892998367629</v>
+        <v>0.5470389193775469</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,135 +1556,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5549292187943315</v>
+        <v>0.539015897580458</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5192307549445832</v>
+        <v>0.5248991443888886</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5173660590535847</v>
+        <v>0.4959577375191728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5104768900295948</v>
+        <v>0.4936499232939717</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4998577468757452</v>
+        <v>0.4859335073018822</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4866666572038518</v>
+        <v>0.4812735179446412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4730213015245344</v>
+        <v>0.4806400580927928</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4680800458037095</v>
+        <v>0.4768439235522091</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>BNK.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4501379074949703</v>
+        <v>0.4087560342898278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.554493432857926</v>
+        <v>2.495218846218274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.302298177578384</v>
+        <v>2.267414645274124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.182762153320627</v>
+        <v>2.153242849578352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.161571876277092</v>
+        <v>2.094433715427068</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.968102154658359</v>
+        <v>1.934609342689065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.59725138752559</v>
+        <v>1.614246309470628</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.593303626097785</v>
+        <v>1.602228383116664</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.420817980299286</v>
+        <v>1.442379103343341</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.337814559469384</v>
+        <v>1.364922799466819</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.309748313207332</v>
+        <v>1.30503137415994</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.30354031811875</v>
+        <v>1.284968077647135</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.230676309256866</v>
+        <v>1.234609434741263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.229332605832317</v>
+        <v>1.194070793647346</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.210267637012232</v>
+        <v>1.181463893619198</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.092060687935156</v>
+        <v>1.075873774637154</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9920510716637758</v>
+        <v>0.9735753082162255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1993,30 +1993,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.98998149963983</v>
+        <v>0.9585359157611344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.890076699679184</v>
+        <v>0.947722869047279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.600054570060303</v>
+        <v>0.6150695377738853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,150 +2038,150 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5097799414084907</v>
+        <v>0.4534146419198071</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4646795743868641</v>
+        <v>0.4476563784473777</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4420381884654843</v>
+        <v>0.407031883896082</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4213036608745711</v>
+        <v>0.4043212538557268</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4122406272662142</v>
+        <v>0.395238139819418</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3941392834042079</v>
+        <v>0.3428634166393489</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.346085729342968</v>
+        <v>0.3178544596860771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3402036406060736</v>
+        <v>0.3119008495623001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3341336122341727</v>
+        <v>0.3053704872224561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3175186728431598</v>
+        <v>0.3052088934811523</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.307240994793589</v>
+        <v>0.2978230448473806</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08092966305516991</v>
+        <v>0.08406286542601715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,165 +457,165 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03411765969276948</v>
+        <v>0.05214521147009732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02933394386803978</v>
+        <v>0.03616136498566203</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02749141675880851</v>
+        <v>0.03266872889479422</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02689985297253616</v>
+        <v>0.03259559416999713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02020252302504666</v>
+        <v>0.03185895492677138</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01903973755007926</v>
+        <v>0.028701545088333</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>PRAJ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01887174706894923</v>
+        <v>0.02860185683451477</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>FUJI.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01790928676783876</v>
+        <v>0.02858053656247694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPXU.L</t>
+          <t>ETFJAP.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0159441517034189</v>
+        <v>0.02682436823499468</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Japan SRI Climate Paris Aligned UCITS ETF DR - USD Hedged (C)</t>
+          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01564216452751133</v>
+        <v>0.02662681465718286</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01512677897873704</v>
+        <v>0.02542464111703535</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0137185736754184</v>
+        <v>0.02515131375743485</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -637,30 +637,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01327513982793449</v>
+        <v>0.02420687690863743</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01324977789336534</v>
+        <v>0.02346756496882052</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2176423603490694</v>
+        <v>0.1992570753195213</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1519318065200674</v>
+        <v>0.1691123545098965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1050169979674613</v>
+        <v>0.1080093999480056</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09791518357758067</v>
+        <v>0.1062663064398854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,165 +758,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08925436092612293</v>
+        <v>0.09063708115313873</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0775956531905011</v>
+        <v>0.08260224211934886</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07010290155085097</v>
+        <v>0.07839178330880858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05386027066015053</v>
+        <v>0.06693444207018828</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05322211964218648</v>
+        <v>0.06503895513051394</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05153619292940603</v>
+        <v>0.06305638004063852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04964715268034259</v>
+        <v>0.06064643916658241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04876374097320757</v>
+        <v>0.06016957825266855</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04867628836643445</v>
+        <v>0.05788766239466292</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04754808518002696</v>
+        <v>0.05560518225585764</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04654507227698068</v>
+        <v>0.05529661617154491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8588640460594228</v>
+        <v>0.4839694632036788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.277323995205033</v>
+        <v>0.2929061539885294</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2309679592123566</v>
+        <v>0.2175444936956434</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1883311344479239</v>
+        <v>0.2074036373326773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.149886797059257</v>
+        <v>0.1623218935975876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1280120655314936</v>
+        <v>0.1250589925190986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,90 +1059,90 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1131358969238101</v>
+        <v>0.1175434185251174</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1106498051078728</v>
+        <v>0.1028795348950493</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1071222778310925</v>
+        <v>0.09354613393385236</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1036677082608353</v>
+        <v>0.08959153445961077</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08994266722870004</v>
+        <v>0.08782615014420703</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07069212407372572</v>
+        <v>0.08583109655191379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0667241167056507</v>
+        <v>0.07120781307949064</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VMIG.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06451611219192133</v>
+        <v>0.07043860371510324</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.034320294222848</v>
+        <v>1.024409407451196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.581606718782846</v>
+        <v>0.5820091513435268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4838594671679524</v>
+        <v>0.5367249935411127</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4724860541994587</v>
+        <v>0.5352806136717814</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,30 +1270,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4141196350173779</v>
+        <v>0.4142379980220257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4022824695947345</v>
+        <v>0.405781594290207</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.397242239632952</v>
+        <v>0.4005392773947714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3310827202712412</v>
+        <v>0.341366051052034</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,90 +1345,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3019466983616415</v>
+        <v>0.2973332406526998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3007289789977494</v>
+        <v>0.285624383639745</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2921840781389702</v>
+        <v>0.2833392162553512</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.284915454383164</v>
+        <v>0.2684707871958312</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2744085292913025</v>
+        <v>0.2682979165056072</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2742101303069853</v>
+        <v>0.2622226081415455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.515643000136636</v>
+        <v>1.445771355794062</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.471313652283122</v>
+        <v>1.42933247178884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.096636277920825</v>
+        <v>0.9785511976920622</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7803189800994026</v>
+        <v>0.7443206996386871</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5612575789297738</v>
+        <v>0.5662527845365308</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5470389193775469</v>
+        <v>0.5323199650966428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.539015897580458</v>
+        <v>0.5214092713997509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,45 +1571,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5248991443888886</v>
+        <v>0.4994843477624169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4959577375191728</v>
+        <v>0.4829695587359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4936499232939717</v>
+        <v>0.4813202834511257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4859335073018822</v>
+        <v>0.4526374993369848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4812735179446412</v>
+        <v>0.4404966030252377</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,15 +1646,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4806400580927928</v>
+        <v>0.4350099653901758</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4768439235522091</v>
+        <v>0.3883163520230015</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BNK.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4087560342898278</v>
+        <v>0.3758123230904005</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Banks UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.495218846218274</v>
+        <v>2.451474356529682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1737,30 +1737,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.267414645274124</v>
+        <v>2.181589076920568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.153242849578352</v>
+        <v>2.165816816479077</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.094433715427068</v>
+        <v>2.14637835421096</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.934609342689065</v>
+        <v>1.858927493548012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.614246309470628</v>
+        <v>1.583612769010013</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.602228383116664</v>
+        <v>1.544735442002814</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.442379103343341</v>
+        <v>1.435992566507016</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.364922799466819</v>
+        <v>1.348770637026111</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.30503137415994</v>
+        <v>1.334274240748321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,60 +1872,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.284968077647135</v>
+        <v>1.264686827450952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.234609434741263</v>
+        <v>1.256621581464837</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.194070793647346</v>
+        <v>1.184315050638146</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.181463893619198</v>
+        <v>1.168018062283969</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.075873774637154</v>
+        <v>1.057219745990455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9735753082162255</v>
+        <v>0.9669154971731206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1993,30 +1993,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9585359157611344</v>
+        <v>0.9580380098308947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.947722869047279</v>
+        <v>0.9522730319924224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6150695377738853</v>
+        <v>0.6036035766300591</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,30 +2038,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4534146419198071</v>
+        <v>0.4723501731379147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4476563784473777</v>
+        <v>0.4592818091673772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.407031883896082</v>
+        <v>0.4082072036919517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,120 +2083,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4043212538557268</v>
+        <v>0.4045788385462175</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.395238139819418</v>
+        <v>0.3942796351913276</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3428634166393489</v>
+        <v>0.3499823487481968</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3178544596860771</v>
+        <v>0.3109025384493744</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3119008495623001</v>
+        <v>0.3078001243465969</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3053704872224561</v>
+        <v>0.3049251234853898</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3052088934811523</v>
+        <v>0.3009603346810072</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2978230448473806</v>
+        <v>0.2832367630751755</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08406286542601715</v>
+        <v>0.05403604251811123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05214521147009732</v>
+        <v>0.04023252353080387</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03616136498566203</v>
+        <v>0.0399053201675319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03266872889479422</v>
+        <v>0.03663046463676123</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03259559416999713</v>
+        <v>0.03020916659410378</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03185895492677138</v>
+        <v>0.02713083243976455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.028701545088333</v>
+        <v>0.02551796199297574</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRAJ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02860185683451477</v>
+        <v>0.02546891233606363</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FUJI.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02858053656247694</v>
+        <v>0.02449102141859316</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ETFJAP.MI</t>
+          <t>FUJI.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02682436823499468</v>
+        <v>0.02445135700528334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
+          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02662681465718286</v>
+        <v>0.02244081118359387</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02542464111703535</v>
+        <v>0.02204454898359498</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPN.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02515131375743485</v>
+        <v>0.02192930478195043</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>PRAJ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02420687690863743</v>
+        <v>0.02156301095484192</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02346756496882052</v>
+        <v>0.02058823941900667</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -698,30 +698,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1992570753195213</v>
+        <v>0.21770313858955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1691123545098965</v>
+        <v>0.2035517279140135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1080093999480056</v>
+        <v>0.1458109040320827</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1062663064398854</v>
+        <v>0.1327612410571968</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09063708115313873</v>
+        <v>0.1257705352477914</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08260224211934886</v>
+        <v>0.1173525937589672</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07839178330880858</v>
+        <v>0.1119146352019096</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06693444207018828</v>
+        <v>0.1062522185290127</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06503895513051394</v>
+        <v>0.1020030040299424</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06305638004063852</v>
+        <v>0.07905707572197374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06064643916658241</v>
+        <v>0.07135947634375572</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06016957825266855</v>
+        <v>0.07036624998840879</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05788766239466292</v>
+        <v>0.0668651510613425</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>FUJI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05560518225585764</v>
+        <v>0.0584614693194101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05529661617154491</v>
+        <v>0.05799006426680142</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4839694632036788</v>
+        <v>0.5038168083418981</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2929061539885294</v>
+        <v>0.2649886970310078</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2175444936956434</v>
+        <v>0.2157246047845214</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2074036373326773</v>
+        <v>0.2106564012558301</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1623218935975876</v>
+        <v>0.131815385571828</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,60 +1029,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1333332970028831</v>
+        <v>0.1304785601343599</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1250589925190986</v>
+        <v>0.1299999782017298</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1175434185251174</v>
+        <v>0.1068115910680523</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1028795348950493</v>
+        <v>0.1007323363030368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09354613393385236</v>
+        <v>0.09873479053943757</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08959153445961077</v>
+        <v>0.0940392072067695</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,45 +1119,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08782615014420703</v>
+        <v>0.09266945330052456</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08583109655191379</v>
+        <v>0.08397947886908819</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FXGB.L</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07120781307949064</v>
+        <v>0.08302115515829933</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Trust FactorFX UCITS ETF GBP Hedged Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07043860371510324</v>
+        <v>0.08300972704606191</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.024409407451196</v>
+        <v>1.00335916330373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5820091513435268</v>
+        <v>0.6232156893163885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,60 +1240,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5367249935411127</v>
+        <v>0.6045501874778678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5352806136717814</v>
+        <v>0.6007587391867661</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4142379980220257</v>
+        <v>0.4331905612791898</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.405781594290207</v>
+        <v>0.4295270123056494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4005392773947714</v>
+        <v>0.423356660665501</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3939481138536409</v>
+        <v>0.4125914687247687</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.341366051052034</v>
+        <v>0.3717333141858288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2973332406526998</v>
+        <v>0.3278058540565616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.285624383639745</v>
+        <v>0.3115786963066296</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2833392162553512</v>
+        <v>0.3076288435824555</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2684707871958312</v>
+        <v>0.2903404013545767</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2682979165056072</v>
+        <v>0.2862222175325704</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2622226081415455</v>
+        <v>0.2856293696796135</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.445771355794062</v>
+        <v>1.498330061275389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.42933247178884</v>
+        <v>1.485934921182808</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9785511976920622</v>
+        <v>0.9271864965310663</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7443206996386871</v>
+        <v>0.762023060906972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,30 +1526,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5662527845365308</v>
+        <v>0.5619199398066623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5323199650966428</v>
+        <v>0.5431115094308314</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5214092713997509</v>
+        <v>0.535193837876061</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,120 +1571,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4994843477624169</v>
+        <v>0.5076529929559475</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4829695587359</v>
+        <v>0.5012155862316725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4813202834511257</v>
+        <v>0.5006392185169972</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4526374993369848</v>
+        <v>0.4780645883211525</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4404966030252377</v>
+        <v>0.4282209678706523</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4350099653901758</v>
+        <v>0.4012710139799649</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3883163520230015</v>
+        <v>0.3963913056493114</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3758123230904005</v>
+        <v>0.3937816020539593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.451474356529682</v>
+        <v>2.583390456461909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.181589076920568</v>
+        <v>2.321260743158553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,30 +1752,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.165816816479077</v>
+        <v>2.303389600602246</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.14637835421096</v>
+        <v>2.197958185965639</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.858927493548012</v>
+        <v>2.040786969087734</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.583612769010013</v>
+        <v>1.621085168371209</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.544735442002814</v>
+        <v>1.579501570154822</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.435992566507016</v>
+        <v>1.546158478803173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,75 +1842,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.348770637026111</v>
+        <v>1.44164423302639</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.334274240748321</v>
+        <v>1.438470271479903</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.264686827450952</v>
+        <v>1.285459356800999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.256621581464837</v>
+        <v>1.274091183383594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.184315050638146</v>
+        <v>1.264788084762309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.168018062283969</v>
+        <v>1.260350324572906</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.057219745990455</v>
+        <v>1.091287851095589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9669154971731206</v>
+        <v>1.048874837446653</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9580380098308947</v>
+        <v>1.046381767466657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9522730319924224</v>
+        <v>0.931972877382049</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6036035766300591</v>
+        <v>0.6453725838559059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4723501731379147</v>
+        <v>0.4724808808779624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4592818091673772</v>
+        <v>0.4588124071392941</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4082072036919517</v>
+        <v>0.4412840974043559</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,30 +2083,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4045788385462175</v>
+        <v>0.4253391853931523</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3942796351913276</v>
+        <v>0.383882777843064</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3499823487481968</v>
+        <v>0.3526390732839435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3109025384493744</v>
+        <v>0.3364616185711156</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3078001243465969</v>
+        <v>0.3351886461227125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3049251234853898</v>
+        <v>0.3221656471105596</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3009603346810072</v>
+        <v>0.3041430707544881</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>HEMA.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2832367630751755</v>
+        <v>0.2985305892689294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>HSBC MSCI Emerging Markets UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,30 +442,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05403604251811123</v>
+        <v>0.1311126623431631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04023252353080387</v>
+        <v>0.1121960854216351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0399053201675319</v>
+        <v>0.06859111482248337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -487,180 +487,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03663046463676123</v>
+        <v>0.06689537401973022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03020916659410378</v>
+        <v>0.06458226030213576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02713083243976455</v>
+        <v>0.06335111599376986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02551796199297574</v>
+        <v>0.06174262547806153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02546891233606363</v>
+        <v>0.0586825665677968</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02449102141859316</v>
+        <v>0.05272620355645907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FUJI.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02445135700528334</v>
+        <v>0.0500461946075903</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02244081118359387</v>
+        <v>0.0474457607877834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02204454898359498</v>
+        <v>0.04479555604810859</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>HEMA.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02192930478195043</v>
+        <v>0.04435002978059699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>HSBC MSCI Emerging Markets UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PRAJ.PA</t>
+          <t>LEMA.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02156301095484192</v>
+        <v>0.04344372296705568</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
+          <t>Amundi Core MSCI Emerging Markets Swap UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>E127.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02058823941900667</v>
+        <v>0.04303341332756294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Core MSCI Emerging Markets Swap UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -698,15 +698,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.21770313858955</v>
+        <v>0.2519797837713071</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2035517279140135</v>
+        <v>0.2130801259317863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,30 +728,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1458109040320827</v>
+        <v>0.1822232268555959</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1327612410571968</v>
+        <v>0.1388712898470472</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1257705352477914</v>
+        <v>0.1189873748805392</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1173525937589672</v>
+        <v>0.1133148226637488</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1119146352019096</v>
+        <v>0.09942554221070155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1062522185290127</v>
+        <v>0.09590301151542668</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1020030040299424</v>
+        <v>0.08568862712869607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07905707572197374</v>
+        <v>0.08548237460473063</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07135947634375572</v>
+        <v>0.0761954224031407</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07036624998840879</v>
+        <v>0.07503894592616223</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0668651510613425</v>
+        <v>0.07183119522640147</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FUJI.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0584614693194101</v>
+        <v>0.06754490287004122</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05799006426680142</v>
+        <v>0.06652314501559542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5038168083418981</v>
+        <v>0.4986259082291609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,195 +969,195 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2649886970310078</v>
+        <v>0.360147723865424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2157246047845214</v>
+        <v>0.2724757655594174</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2106564012558301</v>
+        <v>0.2292521578032396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.131815385571828</v>
+        <v>0.2247813759146498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1304785601343599</v>
+        <v>0.1570807112667882</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1299999782017298</v>
+        <v>0.140943605843169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1068115910680523</v>
+        <v>0.1350720727840358</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1007323363030368</v>
+        <v>0.1348619082725717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09873479053943757</v>
+        <v>0.1235996781580739</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0940392072067695</v>
+        <v>0.1230478222780675</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09266945330052456</v>
+        <v>0.1174438673168343</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08397947886908819</v>
+        <v>0.1085184394336798</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08302115515829933</v>
+        <v>0.09940795975052219</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08300972704606191</v>
+        <v>0.0898194466036879</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.00335916330373</v>
+        <v>1.060239628431135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6232156893163885</v>
+        <v>0.6242930356283909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6045501874778678</v>
+        <v>0.6177257900554423</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6007587391867661</v>
+        <v>0.611668704377605</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,30 +1270,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4331905612791898</v>
+        <v>0.4661571290498789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4295270123056494</v>
+        <v>0.4601713346334888</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.423356660665501</v>
+        <v>0.4323550377089005</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4125914687247687</v>
+        <v>0.4077154617712753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3717333141858288</v>
+        <v>0.3788162345165158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,90 +1345,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3278058540565616</v>
+        <v>0.360147723865424</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3115786963066296</v>
+        <v>0.358897334916457</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3076288435824555</v>
+        <v>0.3365251444945192</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2903404013545767</v>
+        <v>0.3262587213522408</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2862222175325704</v>
+        <v>0.3127659909052185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2856293696796135</v>
+        <v>0.3068612944359175</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.498330061275389</v>
+        <v>1.489370531413102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.485934921182808</v>
+        <v>1.487500166427751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9271864965310663</v>
+        <v>0.9186652060234826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.762023060906972</v>
+        <v>0.7448285965992192</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5619199398066623</v>
+        <v>0.5867712049741824</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5431115094308314</v>
+        <v>0.5565482977078047</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.535193837876061</v>
+        <v>0.5455438715111769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,45 +1571,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5076529929559475</v>
+        <v>0.5331019625107474</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5012155862316725</v>
+        <v>0.5092410820015594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5006392185169972</v>
+        <v>0.4899727956074029</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4780645883211525</v>
+        <v>0.4738867009093066</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,60 +1631,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4282209678706523</v>
+        <v>0.4594535230147163</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4012710139799649</v>
+        <v>0.4459212167683977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3963913056493114</v>
+        <v>0.4090751576029634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3937816020539593</v>
+        <v>0.4058399096583531</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.583390456461909</v>
+        <v>2.544778793960293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.321260743158553</v>
+        <v>2.352829091147401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.303389600602246</v>
+        <v>2.343106851149811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.197958185965639</v>
+        <v>2.187297403523235</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.040786969087734</v>
+        <v>2.005501423183368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.621085168371209</v>
+        <v>1.626220096790578</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,30 +1812,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.579501570154822</v>
+        <v>1.585565608025789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.546158478803173</v>
+        <v>1.579862686285962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.44164423302639</v>
+        <v>1.488833728107692</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.438470271479903</v>
+        <v>1.405461441151187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.285459356800999</v>
+        <v>1.268011051528572</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,30 +1887,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.274091183383594</v>
+        <v>1.249615850651107</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.264788084762309</v>
+        <v>1.237777327762253</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.260350324572906</v>
+        <v>1.20901849055569</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.091287851095589</v>
+        <v>1.085307010480725</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,30 +1978,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.048874837446653</v>
+        <v>1.063185425651083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.046381767466657</v>
+        <v>1.062838936226638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.931972877382049</v>
+        <v>0.9868265041764572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6453725838559059</v>
+        <v>0.6464646359453194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4724808808779624</v>
+        <v>0.5007022893230155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4588124071392941</v>
+        <v>0.4773527129381709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4412840974043559</v>
+        <v>0.4750327488289716</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4253391853931523</v>
+        <v>0.4501109987135115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.383882777843064</v>
+        <v>0.4040294103386124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3526390732839435</v>
+        <v>0.37513284889515</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3364616185711156</v>
+        <v>0.3616214047165134</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,45 +2143,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3351886461227125</v>
+        <v>0.360147723865424</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3221656471105596</v>
+        <v>0.3566134518616981</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3041430707544881</v>
+        <v>0.3459420619900584</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2985305892689294</v>
+        <v>0.3294663672340821</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1311126623431631</v>
+        <v>0.1293225705023258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1121960854216351</v>
+        <v>0.1222012981943768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06859111482248337</v>
+        <v>0.07370485801532078</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06689537401973022</v>
+        <v>0.06616335855558408</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06458226030213576</v>
+        <v>0.05958226489205143</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06335111599376986</v>
+        <v>0.05696382697898139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06174262547806153</v>
+        <v>0.0521326524198702</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>FUJI.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0586825665677968</v>
+        <v>0.04648223836189347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05272620355645907</v>
+        <v>0.04568648584187285</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0500461946075903</v>
+        <v>0.04483071888718348</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0474457607877834</v>
+        <v>0.04330645624797236</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04479555604810859</v>
+        <v>0.04322792312389256</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HEMA.PA</t>
+          <t>ETFJAP.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04435002978059699</v>
+        <v>0.04242584970846663</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HSBC MSCI Emerging Markets UCITS ETF USD (Acc)</t>
+          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEMA.MI</t>
+          <t>JPJY.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04344372296705568</v>
+        <v>0.04201074213302136</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Emerging Markets Swap UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E127.MI</t>
+          <t>PRAJ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04303341332756294</v>
+        <v>0.04076799627560335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Emerging Markets Swap UCITS ETF Dist</t>
+          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2519797837713071</v>
+        <v>0.2543782184512264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,45 +713,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2130801259317863</v>
+        <v>0.2001685670662268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1822232268555959</v>
+        <v>0.1608539769590187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1388712898470472</v>
+        <v>0.1537447089089641</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1189873748805392</v>
+        <v>0.1320676022332881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1133148226637488</v>
+        <v>0.1064215877079928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -788,135 +788,135 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09942554221070155</v>
+        <v>0.0983763186118729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09590301151542668</v>
+        <v>0.09522957671194199</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08568862712869607</v>
+        <v>0.09323909099960681</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08548237460473063</v>
+        <v>0.09132528733996326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0761954224031407</v>
+        <v>0.08226505752735602</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07503894592616223</v>
+        <v>0.08000000365479987</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07183119522640147</v>
+        <v>0.06013507466205215</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06754490287004122</v>
+        <v>0.05944080629632631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06652314501559542</v>
+        <v>0.05901236851742331</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4986259082291609</v>
+        <v>0.5213740247952403</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.360147723865424</v>
+        <v>0.3627533773376435</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2724757655594174</v>
+        <v>0.2624440493772393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2292521578032396</v>
+        <v>0.2060571161292972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2247813759146498</v>
+        <v>0.2057448429354565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,150 +1029,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1570807112667882</v>
+        <v>0.1739894553154504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.140943605843169</v>
+        <v>0.1600973740959586</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1350720727840358</v>
+        <v>0.1600101522118365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1348619082725717</v>
+        <v>0.14802930622939</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1235996781580739</v>
+        <v>0.1417926266622398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1230478222780675</v>
+        <v>0.1320676022332881</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1174438673168343</v>
+        <v>0.1305447544392275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1085184394336798</v>
+        <v>0.1208548527185471</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09940795975052219</v>
+        <v>0.1194029961588152</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0898194466036879</v>
+        <v>0.1152771523346188</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.060239628431135</v>
+        <v>1.016826081327305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6242930356283909</v>
+        <v>0.6357037248423374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,60 +1240,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6177257900554423</v>
+        <v>0.5686177689214795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.611668704377605</v>
+        <v>0.5659526957382617</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4661571290498789</v>
+        <v>0.4944769923428438</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4601713346334888</v>
+        <v>0.4797024159826127</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4323550377089005</v>
+        <v>0.4591146142264277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4077154617712753</v>
+        <v>0.4290836199222878</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3788162345165158</v>
+        <v>0.3852140405102542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,60 +1345,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.360147723865424</v>
+        <v>0.3676564526573083</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.358897334916457</v>
+        <v>0.3627533773376435</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3365251444945192</v>
+        <v>0.3598476301396978</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3262587213522408</v>
+        <v>0.342259106106932</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3127659909052185</v>
+        <v>0.3080804086495312</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3068612944359175</v>
+        <v>0.3067073700241301</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.489370531413102</v>
+        <v>1.430255954472324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.487500166427751</v>
+        <v>1.418423954903266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9186652060234826</v>
+        <v>0.7911974595757292</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7448285965992192</v>
+        <v>0.7301294233545117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5867712049741824</v>
+        <v>0.5753920186531838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5565482977078047</v>
+        <v>0.5288456621046642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5455438715111769</v>
+        <v>0.5216445277074517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5331019625107474</v>
+        <v>0.5154248226098308</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5092410820015594</v>
+        <v>0.5046899684237656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,60 +1601,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4899727956074029</v>
+        <v>0.4860918610997607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4738867009093066</v>
+        <v>0.4764242910021861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4594535230147163</v>
+        <v>0.4657881094107013</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4459212167683977</v>
+        <v>0.4586838775212252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4090751576029634</v>
+        <v>0.4375515116356734</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4058399096583531</v>
+        <v>0.4133551911372753</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.544778793960293</v>
+        <v>2.602184130168746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.352829091147401</v>
+        <v>2.314070323311192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.343106851149811</v>
+        <v>2.289729198752123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.187297403523235</v>
+        <v>2.237803449277565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.005501423183368</v>
+        <v>2.032475767701922</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.626220096790578</v>
+        <v>1.672957919807005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,30 +1812,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.585565608025789</v>
+        <v>1.635739142830614</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.579862686285962</v>
+        <v>1.616278348238468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.488833728107692</v>
+        <v>1.486352281766347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.405461441151187</v>
+        <v>1.433526082369408</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.268011051528572</v>
+        <v>1.292269471150175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,30 +1887,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.249615850651107</v>
+        <v>1.274185200376761</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.237777327762253</v>
+        <v>1.262375052022405</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.20901849055569</v>
+        <v>1.22864708070938</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.085307010480725</v>
+        <v>1.10255407082172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,30 +1978,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.063185425651083</v>
+        <v>1.038992479029102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.062838936226638</v>
+        <v>1.030243614519768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9868265041764572</v>
+        <v>0.8896448121701246</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6464646359453194</v>
+        <v>0.6609336427025301</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5007022893230155</v>
+        <v>0.4986444834823234</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4773527129381709</v>
+        <v>0.4766486815167401</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4750327488289716</v>
+        <v>0.4644548706661444</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4501109987135115</v>
+        <v>0.4502692985730203</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4040294103386124</v>
+        <v>0.3910256240069385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2113,30 +2113,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.37513284889515</v>
+        <v>0.3777954767807734</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3616214047165134</v>
+        <v>0.3726532280676862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.360147723865424</v>
+        <v>0.3627533773376435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3566134518616981</v>
+        <v>0.3451280324227979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3459420619900584</v>
+        <v>0.3353404584468718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HEMA.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3294663672340821</v>
+        <v>0.3276994816837013</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HSBC MSCI Emerging Markets UCITS ETF USD (Acc)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1293225705023258</v>
+        <v>0.1075519856181366</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1222012981943768</v>
+        <v>0.09040360925654811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07370485801532078</v>
+        <v>0.05304510631055859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06616335855558408</v>
+        <v>0.04931515439363721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05958226489205143</v>
+        <v>0.04520972212080432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05696382697898139</v>
+        <v>0.04499499628171</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0521326524198702</v>
+        <v>0.04176465202780322</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FUJI.PA</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04648223836189347</v>
+        <v>0.03514056278735178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04568648584187285</v>
+        <v>0.03495035643147459</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04483071888718348</v>
+        <v>0.03193277683727747</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04330645624797236</v>
+        <v>0.03098192485002493</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04322792312389256</v>
+        <v>0.02722302658735698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L&amp;G Battery Value-Chain UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETFJAP.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04242584970846663</v>
+        <v>0.02696890721400202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (D)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPJY.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04201074213302136</v>
+        <v>0.02612718694744554</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Japan UCITS ETF JPY Unhedged</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRAJ.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04076799627560335</v>
+        <v>0.02577473782918527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Prime Japan UCITS ETF DR (C)</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2543782184512264</v>
+        <v>0.1485359384557132</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,45 +713,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2001685670662268</v>
+        <v>0.141746343279858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1608539769590187</v>
+        <v>0.1281574376614008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1537447089089641</v>
+        <v>0.1172123169117019</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1320676022332881</v>
+        <v>0.1067491549366832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1064215877079928</v>
+        <v>0.101102088633555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0983763186118729</v>
+        <v>0.0914745913923205</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09522957671194199</v>
+        <v>0.08869328718311453</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09323909099960681</v>
+        <v>0.07761331156282081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09132528733996326</v>
+        <v>0.07721573551736416</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08226505752735602</v>
+        <v>0.07449999340623625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08000000365479987</v>
+        <v>0.07432006150167969</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06013507466205215</v>
+        <v>0.07271430902378828</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05944080629632631</v>
+        <v>0.06860044004709209</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05901236851742331</v>
+        <v>0.06223177624735099</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5213740247952403</v>
+        <v>0.4537404634391125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3627533773376435</v>
+        <v>0.2957372022623748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2624440493772393</v>
+        <v>0.2643027705717016</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,60 +999,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2060571161292972</v>
+        <v>0.1981189666109087</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2057448429354565</v>
+        <v>0.1683077069954138</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1739894553154504</v>
+        <v>0.1647406212094551</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1600973740959586</v>
+        <v>0.1630955488943744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1600101522118365</v>
+        <v>0.1591442483429659</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.14802930622939</v>
+        <v>0.1443700073284728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1417926266622398</v>
+        <v>0.1389200826017101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1320676022332881</v>
+        <v>0.1315286491223895</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1305447544392275</v>
+        <v>0.1306025552662742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1208548527185471</v>
+        <v>0.1294233520214334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1194029961588152</v>
+        <v>0.1154559220772426</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1152771523346188</v>
+        <v>0.112756270881992</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.016826081327305</v>
+        <v>0.8809709150993081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6357037248423374</v>
+        <v>0.531747015050434</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,15 +1240,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5686177689214795</v>
+        <v>0.4279205506311792</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5659526957382617</v>
+        <v>0.3973284201321519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,15 +1270,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4944769923428438</v>
+        <v>0.3936371896955611</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4797024159826127</v>
+        <v>0.3798136025794816</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4591146142264277</v>
+        <v>0.3741742874594534</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4290836199222878</v>
+        <v>0.3655528818422422</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1330,15 +1330,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3852140405102542</v>
+        <v>0.2957372022623748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3676564526573083</v>
+        <v>0.2824129792497545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3627533773376435</v>
+        <v>0.2712297598548283</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3598476301396978</v>
+        <v>0.2620235095614101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.342259106106932</v>
+        <v>0.2617178264053996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3080804086495312</v>
+        <v>0.2508350334298464</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3067073700241301</v>
+        <v>0.2483679993519143</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.430255954472324</v>
+        <v>1.387944404102733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.418423954903266</v>
+        <v>1.380543372781945</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7911974595757292</v>
+        <v>0.774200308294215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7301294233545117</v>
+        <v>0.7330837798618752</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5753920186531838</v>
+        <v>0.5384890053479277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5288456621046642</v>
+        <v>0.5345784671231446</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,30 +1556,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5216445277074517</v>
+        <v>0.5243428296152153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5154248226098308</v>
+        <v>0.5135981333671782</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5046899684237656</v>
+        <v>0.4748798880763498</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,90 +1601,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4860918610997607</v>
+        <v>0.4524169323868075</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4764242910021861</v>
+        <v>0.4438510212318107</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4657881094107013</v>
+        <v>0.4421065804023405</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4586838775212252</v>
+        <v>0.4417167918731304</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4375515116356734</v>
+        <v>0.4150246451987119</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4133551911372753</v>
+        <v>0.3923878387748092</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.602184130168746</v>
+        <v>2.426551190005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.314070323311192</v>
+        <v>2.239694749628068</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.289729198752123</v>
+        <v>2.226107441851282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.237803449277565</v>
+        <v>2.125939208525804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.032475767701922</v>
+        <v>1.919787102653743</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,45 +1797,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.672957919807005</v>
+        <v>1.614003416158816</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.635739142830614</v>
+        <v>1.611976162545005</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.616278348238468</v>
+        <v>1.579317432453354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.486352281766347</v>
+        <v>1.423490394314745</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.433526082369408</v>
+        <v>1.404382008118086</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.292269471150175</v>
+        <v>1.235277013469454</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,30 +1887,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.274185200376761</v>
+        <v>1.229310783731663</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.262375052022405</v>
+        <v>1.207004202119168</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.22864708070938</v>
+        <v>1.16578249001374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.10255407082172</v>
+        <v>1.051213614162722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.038992479029102</v>
+        <v>0.9932326669042204</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.030243614519768</v>
+        <v>0.9909796940300639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8896448121701246</v>
+        <v>0.8326315418754793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6609336427025301</v>
+        <v>0.6431886098537491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4986444834823234</v>
+        <v>0.4982524848644112</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4766486815167401</v>
+        <v>0.4759446500953093</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4644548706661444</v>
+        <v>0.4449779962200178</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4502692985730203</v>
+        <v>0.4210311030524534</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3910256240069385</v>
+        <v>0.408608165045327</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3777954767807734</v>
+        <v>0.3765974425076088</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3726532280676862</v>
+        <v>0.363443159590964</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,60 +2143,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3627533773376435</v>
+        <v>0.3309919695420771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3451280324227979</v>
+        <v>0.3191292807614081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3353404584468718</v>
+        <v>0.3117988621842971</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3276994816837013</v>
+        <v>0.3109174244421236</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1075519856181366</v>
+        <v>0.1198396297286859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09040360925654811</v>
+        <v>0.1125523253971934</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05304510631055859</v>
+        <v>0.04689924615369834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04931515439363721</v>
+        <v>0.04615634089813958</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04520972212080432</v>
+        <v>0.04612207285076519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04499499628171</v>
+        <v>0.04478285976661844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04176465202780322</v>
+        <v>0.03638641047762903</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03514056278735178</v>
+        <v>0.03279978914564263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03495035643147459</v>
+        <v>0.0325125586945334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03193277683727747</v>
+        <v>0.02866595733998456</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03098192485002493</v>
+        <v>0.0268521365612211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02722302658735698</v>
+        <v>0.02607686563459688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>R1GR.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02696890721400202</v>
+        <v>0.02394695148434289</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>500E.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02612718694744554</v>
+        <v>0.02375889639838502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi S&amp;P 500 Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>ETFUSA.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02577473782918527</v>
+        <v>0.02351129764989945</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi Core MSCI USA UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -698,180 +698,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1485359384557132</v>
+        <v>0.1334452756801232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.141746343279858</v>
+        <v>0.1162161683235148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1281574376614008</v>
+        <v>0.1028218382975972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1172123169117019</v>
+        <v>0.09835015692676041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1067491549366832</v>
+        <v>0.09814276886439899</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.101102088633555</v>
+        <v>0.09592756152399518</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0914745913923205</v>
+        <v>0.09396529672981724</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08869328718311453</v>
+        <v>0.09234237677698021</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07761331156282081</v>
+        <v>0.07592933748684594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07721573551736416</v>
+        <v>0.07464266241240747</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07449999340623625</v>
+        <v>0.07307713905995539</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07432006150167969</v>
+        <v>0.06352997170454833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07271430902378828</v>
+        <v>0.05946901946837468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -893,30 +893,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06860044004709209</v>
+        <v>0.05892183633026193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06223177624735099</v>
+        <v>0.05789555077650332</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4537404634391125</v>
+        <v>0.3638166947745782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2957372022623748</v>
+        <v>0.2262336678153791</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,195 +984,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2643027705717016</v>
+        <v>0.2220552600369468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1981189666109087</v>
+        <v>0.2219486549065122</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1683077069954138</v>
+        <v>0.1485603464221223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1647406212094551</v>
+        <v>0.1395611434324602</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1630955488943744</v>
+        <v>0.1390689867909638</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1591442483429659</v>
+        <v>0.1278896836511709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1443700073284728</v>
+        <v>0.1231757522131776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1389200826017101</v>
+        <v>0.1230455015208098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1315286491223895</v>
+        <v>0.1067008808236658</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1306025552662742</v>
+        <v>0.1032652140587029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1294233520214334</v>
+        <v>0.1012871401657136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1154559220772426</v>
+        <v>0.1009195261988147</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.112756270881992</v>
+        <v>0.09778338667930186</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8809709150993081</v>
+        <v>0.8503712794039138</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.531747015050434</v>
+        <v>0.5217999193249969</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4279205506311792</v>
+        <v>0.4159784946829308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,180 +1255,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3973284201321519</v>
+        <v>0.3811976442686662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3936371896955611</v>
+        <v>0.3798757566307009</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3798136025794816</v>
+        <v>0.3602367909384698</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3741742874594534</v>
+        <v>0.3493473933236104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3655528818422422</v>
+        <v>0.3186508377055408</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2957372022623748</v>
+        <v>0.2810841169325331</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2824129792497545</v>
+        <v>0.2623840533920829</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2712297598548283</v>
+        <v>0.2529096085143396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2620235095614101</v>
+        <v>0.2468135897869026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2617178264053996</v>
+        <v>0.2306370024282818</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2508350334298464</v>
+        <v>0.2262336678153791</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2483679993519143</v>
+        <v>0.2229103995114201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.387944404102733</v>
+        <v>1.292082176666077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.380543372781945</v>
+        <v>1.28253901852063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,90 +1496,90 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.774200308294215</v>
+        <v>0.7027449705922166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7330837798618752</v>
+        <v>0.6007906073256324</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5384890053479277</v>
+        <v>0.5652069067534533</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5345784671231446</v>
+        <v>0.5527857854290574</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5243428296152153</v>
+        <v>0.5273990987663084</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5135981333671782</v>
+        <v>0.5111373162133637</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4748798880763498</v>
+        <v>0.4455407847796338</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4524169323868075</v>
+        <v>0.4426729428393652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4438510212318107</v>
+        <v>0.4155176039700137</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,15 +1631,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4421065804023405</v>
+        <v>0.4059653955380851</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4417167918731304</v>
+        <v>0.4041404603637249</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,30 +1661,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4150246451987119</v>
+        <v>0.3934743845157895</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3923878387748092</v>
+        <v>0.3795252343905844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.426551190005</v>
+        <v>2.368380525611139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.239694749628068</v>
+        <v>2.150042213462964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.226107441851282</v>
+        <v>2.122669734947555</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.125939208525804</v>
+        <v>2.10101186850757</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.919787102653743</v>
+        <v>1.811038844870228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.614003416158816</v>
+        <v>1.630240227336254</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.611976162545005</v>
+        <v>1.556466512595361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.579317432453354</v>
+        <v>1.525686803297407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,30 +1842,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.423490394314745</v>
+        <v>1.397363434025523</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.404382008118086</v>
+        <v>1.362185491395387</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.235277013469454</v>
+        <v>1.223631855102055</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.229310783731663</v>
+        <v>1.213908376192277</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.207004202119168</v>
+        <v>1.191070537233296</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.16578249001374</v>
+        <v>1.162869113243588</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1932,15 +1932,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>EJAH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.051213614162722</v>
+        <v>1.033269093509699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9932326669042204</v>
+        <v>0.9254524695160229</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9909796940300639</v>
+        <v>0.9184412732563489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8326315418754793</v>
+        <v>0.7492712799337484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6431886098537491</v>
+        <v>0.6341796031902658</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4982524848644112</v>
+        <v>0.5402580150852183</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4759446500953093</v>
+        <v>0.5266369178177603</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4449779962200178</v>
+        <v>0.4192887720386873</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,120 +2083,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4210311030524534</v>
+        <v>0.4161172501034369</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.408608165045327</v>
+        <v>0.3975898846389774</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3765974425076088</v>
+        <v>0.3942614851374771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.363443159590964</v>
+        <v>0.3696085029964569</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3309919695420771</v>
+        <v>0.3136848879391059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3191292807614081</v>
+        <v>0.3112099378703383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3117988621842971</v>
+        <v>0.3049288116154112</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3109174244421236</v>
+        <v>0.2942205696426188</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1198396297286859</v>
+        <v>0.1287453146732254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1125523253971934</v>
+        <v>0.1223681213781451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,15 +472,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04689924615369834</v>
+        <v>0.05947204185809252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04615634089813958</v>
+        <v>0.05212359344692907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,165 +502,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04612207285076519</v>
+        <v>0.04146182066145654</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04478285976661844</v>
+        <v>0.03941339726959692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03638641047762903</v>
+        <v>0.0337480563016217</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03279978914564263</v>
+        <v>0.03287011711057852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0325125586945334</v>
+        <v>0.02784809983324843</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02866595733998456</v>
+        <v>0.02679852132699678</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0268521365612211</v>
+        <v>0.02646569970348067</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02607686563459688</v>
+        <v>0.02520185900798033</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R1GR.AS</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02394695148434289</v>
+        <v>0.02375904190081668</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Russell 1000 Growth UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>500E.AS</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02375889639838502</v>
+        <v>0.02363634976473716</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Swap UCITS ETF USD Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETFUSA.MI</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02351129764989945</v>
+        <v>0.0227662699168607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI USA UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -698,225 +698,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1334452756801232</v>
+        <v>0.140219831829951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1162161683235148</v>
+        <v>0.1339702838325072</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1028218382975972</v>
+        <v>0.1218759891546706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09835015692676041</v>
+        <v>0.108376338276867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09814276886439899</v>
+        <v>0.1078184158362856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09592756152399518</v>
+        <v>0.1044434582965603</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09396529672981724</v>
+        <v>0.09248050348917158</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09234237677698021</v>
+        <v>0.08338894345799774</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07592933748684594</v>
+        <v>0.07194651097090121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07464266241240747</v>
+        <v>0.06993088985629781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07307713905995539</v>
+        <v>0.06874301198951316</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>MGT.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06352997170454833</v>
+        <v>0.06455526881177809</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05946901946837468</v>
+        <v>0.06359921250529688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05892183633026193</v>
+        <v>0.06277685241043618</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>500E.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05789555077650332</v>
+        <v>0.06193490259326739</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi S&amp;P 500 Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
@@ -954,225 +954,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3638166947745782</v>
+        <v>0.4369532240039535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2262336678153791</v>
+        <v>0.3711449900868833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2220552600369468</v>
+        <v>0.2642065623349326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2219486549065122</v>
+        <v>0.2548550807485361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1485603464221223</v>
+        <v>0.246080079683773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1395611434324602</v>
+        <v>0.2307112720235944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1390689867909638</v>
+        <v>0.180504577735243</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1278896836511709</v>
+        <v>0.1630434239303058</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1231757522131776</v>
+        <v>0.1483686423721002</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1230455015208098</v>
+        <v>0.1462994373157489</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1067008808236658</v>
+        <v>0.1358150983416961</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1032652140587029</v>
+        <v>0.129582439801327</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1012871401657136</v>
+        <v>0.1230705401520771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1009195261988147</v>
+        <v>0.1167698964133634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09778338667930186</v>
+        <v>0.1153846193208898</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8503712794039138</v>
+        <v>0.9424209632364016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5217999193249969</v>
+        <v>0.4973585619982488</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4159784946829308</v>
+        <v>0.4154381047796736</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,105 +1255,105 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3811976442686662</v>
+        <v>0.4019964751374487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3798757566307009</v>
+        <v>0.3691309041702822</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3602367909384698</v>
+        <v>0.3506290693512624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3493473933236104</v>
+        <v>0.3448582436830121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3186508377055408</v>
+        <v>0.3383368355787673</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2810841169325331</v>
+        <v>0.3139723454647572</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2623840533920829</v>
+        <v>0.2879678592747084</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2529096085143396</v>
+        <v>0.2540229267081524</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2468135897869026</v>
+        <v>0.2501203409344992</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,45 +1390,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2306370024282818</v>
+        <v>0.2459038485908862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2262336678153791</v>
+        <v>0.2401703590520914</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2229103995114201</v>
+        <v>0.2281049713676999</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1466,30 +1466,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.292082176666077</v>
+        <v>1.284845458643718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.28253901852063</v>
+        <v>1.282087145516404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7027449705922166</v>
+        <v>0.6935553580549223</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6007906073256324</v>
+        <v>0.6301183422315795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,30 +1526,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5652069067534533</v>
+        <v>0.5786673512460023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5527857854290574</v>
+        <v>0.5740072202166064</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5273990987663084</v>
+        <v>0.5397201126587718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5111373162133637</v>
+        <v>0.498582634462168</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,105 +1586,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4455407847796338</v>
+        <v>0.4620272731825579</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4426729428393652</v>
+        <v>0.4516562229705925</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4155176039700137</v>
+        <v>0.4479694024538061</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4059653955380851</v>
+        <v>0.4454393496129261</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4041404603637249</v>
+        <v>0.4241120148166841</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3934743845157895</v>
+        <v>0.415014111497944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3795252343905844</v>
+        <v>0.4124263768793255</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.368380525611139</v>
+        <v>2.270634414320517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.150042213462964</v>
+        <v>2.109328893961258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.122669734947555</v>
+        <v>2.096258190754858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.10101186850757</v>
+        <v>2.05049476517121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.811038844870228</v>
+        <v>1.819816741500607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.630240227336254</v>
+        <v>1.521256878429765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.556466512595361</v>
+        <v>1.50907364759588</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.525686803297407</v>
+        <v>1.500262528329576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,60 +1842,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.397363434025523</v>
+        <v>1.403367976871372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.362185491395387</v>
+        <v>1.327057324530843</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.223631855102055</v>
+        <v>1.245215466037507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.213908376192277</v>
+        <v>1.19783069231982</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.191070537233296</v>
+        <v>1.155726640771556</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.162869113243588</v>
+        <v>1.098504378934214</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.033269093509699</v>
+        <v>1.004455947998763</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9254524695160229</v>
+        <v>0.9154627529513657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9184412732563489</v>
+        <v>0.9129510771779177</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7492712799337484</v>
+        <v>0.8140589373013436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6341796031902658</v>
+        <v>0.6248976160485966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5402580150852183</v>
+        <v>0.5600523254607774</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5266369178177603</v>
+        <v>0.5348509519643587</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2068,60 +2068,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4192887720386873</v>
+        <v>0.4305861317445561</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4161172501034369</v>
+        <v>0.4201283410787016</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3975898846389774</v>
+        <v>0.4059511744416631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3942614851374771</v>
+        <v>0.3987460173915356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3696085029964569</v>
+        <v>0.3803912684873416</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3136848879391059</v>
+        <v>0.3344403891107517</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3112099378703383</v>
+        <v>0.3108923591383836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3049288116154112</v>
+        <v>0.3026092521771908</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2942205696426188</v>
+        <v>0.3000207128826042</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,75 +442,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1287453146732254</v>
+        <v>0.04575057631925139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1223681213781451</v>
+        <v>0.04531605261532268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05947204185809252</v>
+        <v>0.04375069371022566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05212359344692907</v>
+        <v>0.03186093895828512</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04146182066145654</v>
+        <v>0.0315059867432177</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03941339726959692</v>
+        <v>0.03104072351502452</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -532,30 +532,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0337480563016217</v>
+        <v>0.03068312975260534</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03287011711057852</v>
+        <v>0.02955427585682036</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02784809983324843</v>
+        <v>0.02943060496524263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -577,90 +577,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02679852132699678</v>
+        <v>0.02751322751322749</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02646569970348067</v>
+        <v>0.02321939335070322</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02520185900798033</v>
+        <v>0.02238710256102894</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02375904190081668</v>
+        <v>0.02111738906666072</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02363634976473716</v>
+        <v>0.02068430742043614</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>DJE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0227662699168607</v>
+        <v>0.01943424720661358</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -698,225 +698,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.140219831829951</v>
+        <v>0.1636735058359864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1339702838325072</v>
+        <v>0.1440806419325693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1218759891546706</v>
+        <v>0.1208280527699765</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.108376338276867</v>
+        <v>0.1172287357757256</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1078184158362856</v>
+        <v>0.1158653133131831</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1044434582965603</v>
+        <v>0.1075949901916402</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09248050348917158</v>
+        <v>0.09829344585930322</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08338894345799774</v>
+        <v>0.09720591428227743</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07194651097090121</v>
+        <v>0.08530697021851741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06993088985629781</v>
+        <v>0.07439648305146784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06874301198951316</v>
+        <v>0.06786402410558923</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MGT.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06455526881177809</v>
+        <v>0.06727582418374967</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi DJ Global Titans 50 UCITS ETF Dist</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06359921250529688</v>
+        <v>0.06563162933899047</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06277685241043618</v>
+        <v>0.06285132786261216</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>500E.AS</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06193490259326739</v>
+        <v>0.0622740115269409</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Swap UCITS ETF USD Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4369532240039535</v>
+        <v>0.4704641699069356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3711449900868833</v>
+        <v>0.4447674783499986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2642065623349326</v>
+        <v>0.3189251763777547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2548550807485361</v>
+        <v>0.2271446879641681</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.246080079683773</v>
+        <v>0.2106683437526145</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2307112720235944</v>
+        <v>0.2004010913316949</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.180504577735243</v>
+        <v>0.1909381790101905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1630434239303058</v>
+        <v>0.1628462158759716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1483686423721002</v>
+        <v>0.1553984849993448</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1462994373157489</v>
+        <v>0.1513867659389254</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,75 +1104,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1358150983416961</v>
+        <v>0.1364587824265244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.129582439801327</v>
+        <v>0.1294193883096018</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1230705401520771</v>
+        <v>0.1202547502980154</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1167698964133634</v>
+        <v>0.110421002555102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1153846193208898</v>
+        <v>0.1068192246432234</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9424209632364016</v>
+        <v>0.8773658916427951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4973585619982488</v>
+        <v>0.4712586034469981</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4154381047796736</v>
+        <v>0.4253838163435224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,30 +1255,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4019964751374487</v>
+        <v>0.3964438194357534</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3691309041702822</v>
+        <v>0.3574752359707969</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3506290693512624</v>
+        <v>0.3359678837970781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3448582436830121</v>
+        <v>0.3036162302786396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3383368355787673</v>
+        <v>0.3030670454189603</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3139723454647572</v>
+        <v>0.2889761991172717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2879678592747084</v>
+        <v>0.2829485208030038</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2540229267081524</v>
+        <v>0.2665107054959426</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2501203409344992</v>
+        <v>0.2467604951868889</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2459038485908862</v>
+        <v>0.2419783479624955</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,15 +1405,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2401703590520914</v>
+        <v>0.2252856571538364</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2281049713676999</v>
+        <v>0.2226579039985954</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1466,90 +1466,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.284845458643718</v>
+        <v>1.2481349904108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.282087145516404</v>
+        <v>1.242483013605332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6935553580549223</v>
+        <v>0.7337240263742757</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6301183422315795</v>
+        <v>0.7083030962035108</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5786673512460023</v>
+        <v>0.6347155893666363</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5740072202166064</v>
+        <v>0.6311517060868019</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5397201126587718</v>
+        <v>0.5886904356283171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.498582634462168</v>
+        <v>0.5218885512154863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4620272731825579</v>
+        <v>0.5217893976455106</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,45 +1601,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4516562229705925</v>
+        <v>0.4907425889533472</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4479694024538061</v>
+        <v>0.4815498040275554</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4454393496129261</v>
+        <v>0.4784220786198372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4241120148166841</v>
+        <v>0.4715073585001088</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,30 +1661,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.415014111497944</v>
+        <v>0.4572174313454684</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4124263768793255</v>
+        <v>0.453349978609509</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.270634414320517</v>
+        <v>2.32611234478287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1737,45 +1737,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BNKE.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.109328893961258</v>
+        <v>2.133110780393431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.096258190754858</v>
+        <v>1.959835078562031</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.05049476517121</v>
+        <v>1.936035157632255</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.819816741500607</v>
+        <v>1.839329864672439</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,45 +1797,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.521256878429765</v>
+        <v>1.536796756395487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.50907364759588</v>
+        <v>1.521984928511368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.500262528329576</v>
+        <v>1.512662436886223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.403367976871372</v>
+        <v>1.451004521331337</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.327057324530843</v>
+        <v>1.326829024943863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,15 +1872,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.245215466037507</v>
+        <v>1.25497891620082</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.19783069231982</v>
+        <v>1.246234778303559</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,30 +1902,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.155726640771556</v>
+        <v>1.19084482842008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.098504378934214</v>
+        <v>1.160435608156397</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.004455947998763</v>
+        <v>1.021698354405436</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9154627529513657</v>
+        <v>0.8483270322569436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9129510771779177</v>
+        <v>0.8430745504222081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8140589373013436</v>
+        <v>0.7885757206723769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6248976160485966</v>
+        <v>0.6036035766300591</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5600523254607774</v>
+        <v>0.5687081932259126</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5348509519643587</v>
+        <v>0.5449424509819019</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4305861317445561</v>
+        <v>0.4366301214932207</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2083,60 +2083,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4201283410787016</v>
+        <v>0.417817967454132</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4059511744416631</v>
+        <v>0.4125726040193247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3987460173915356</v>
+        <v>0.3903752936814051</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3803912684873416</v>
+        <v>0.3888944189783405</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3344403891107517</v>
+        <v>0.3477238971924523</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3108923591383836</v>
+        <v>0.3071079627612694</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3026092521771908</v>
+        <v>0.3022782524306693</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AJEUAS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3000207128826042</v>
+        <v>0.2913385894788092</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04575057631925139</v>
+        <v>0.06214236304412535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04531605261532268</v>
+        <v>0.059959447692437</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,105 +472,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04375069371022566</v>
+        <v>0.04758793530526018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03186093895828512</v>
+        <v>0.04270971975018911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0315059867432177</v>
+        <v>0.04111323530239708</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03104072351502452</v>
+        <v>0.03836375004349257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03068312975260534</v>
+        <v>0.03337337744601765</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02955427585682036</v>
+        <v>0.03255813318684164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02943060496524263</v>
+        <v>0.03054640932250763</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02751322751322749</v>
+        <v>0.02886637486992583</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -592,75 +592,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02321939335070322</v>
+        <v>0.02469774395453439</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02238710256102894</v>
+        <v>0.0234485964588913</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02111738906666072</v>
+        <v>0.02232199602232554</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>MIVO.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02068430742043614</v>
+        <v>0.02115908764883079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DJE.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01943424720661358</v>
+        <v>0.02103049470742735</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Dow Jones Industrial Average UCITS ETF Dist</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1636735058359864</v>
+        <v>0.1467137773024128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1440806419325693</v>
+        <v>0.1098218773736053</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,15 +728,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1208280527699765</v>
+        <v>0.1049678727915868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1172287357757256</v>
+        <v>0.104840552393366</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,45 +758,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1158653133131831</v>
+        <v>0.1001267335205629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1075949901916402</v>
+        <v>0.09692823509535575</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09829344585930322</v>
+        <v>0.09683547105276391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09720591428227743</v>
+        <v>0.07880761806036296</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -818,105 +818,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08530697021851741</v>
+        <v>0.07626253889853984</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07439648305146784</v>
+        <v>0.06993182381206053</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06786402410558923</v>
+        <v>0.06842524027652885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06727582418374967</v>
+        <v>0.06529479970877272</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06563162933899047</v>
+        <v>0.06097028634481427</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06285132786261216</v>
+        <v>0.05966586978457289</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0622740115269409</v>
+        <v>0.05750083286944796</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4704641699069356</v>
+        <v>0.4227326414131258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4447674783499986</v>
+        <v>0.4004130215624158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3189251763777547</v>
+        <v>0.2435946819180648</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,105 +999,105 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2271446879641681</v>
+        <v>0.2257901958799078</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2106683437526145</v>
+        <v>0.2047953363728041</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2004010913316949</v>
+        <v>0.1992835555382191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1909381790101905</v>
+        <v>0.1401514662335637</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1628462158759716</v>
+        <v>0.1336905504800363</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1553984849993448</v>
+        <v>0.1293778793760265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1513867659389254</v>
+        <v>0.1238603464565404</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1364587824265244</v>
+        <v>0.1135470910387986</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,15 +1119,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1294193883096018</v>
+        <v>0.1105735113797188</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1202547502980154</v>
+        <v>0.1104170395393986</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1149,15 +1149,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.110421002555102</v>
+        <v>0.1075932461401907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1068192246432234</v>
+        <v>0.1039064674815682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8773658916427951</v>
+        <v>0.7091799547215196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4712586034469981</v>
+        <v>0.419362744525138</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4253838163435224</v>
+        <v>0.3806567650037189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3964438194357534</v>
+        <v>0.3419411072520102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,60 +1270,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3574752359707969</v>
+        <v>0.2981816750315358</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3359678837970781</v>
+        <v>0.2784437118567888</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3036162302786396</v>
+        <v>0.2721509243386038</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>JSOL.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3030670454189603</v>
+        <v>0.2644486342168031</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>21shares Jito Staked SOL ETP</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2889761991172717</v>
+        <v>0.2514140984948496</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,60 +1345,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2829485208030038</v>
+        <v>0.2236770258819216</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2665107054959426</v>
+        <v>0.2217810588916469</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2467604951868889</v>
+        <v>0.2141023489925802</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2419783479624955</v>
+        <v>0.2056179429324365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2252856571538364</v>
+        <v>0.2038789007635899</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2226579039985954</v>
+        <v>0.2017211889924344</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.2481349904108</v>
+        <v>1.118074635605292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.242483013605332</v>
+        <v>1.108404345401146</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7337240263742757</v>
+        <v>0.6676745129549684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7083030962035108</v>
+        <v>0.6494929381909189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6347155893666363</v>
+        <v>0.6493089034052404</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,15 +1541,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6311517060868019</v>
+        <v>0.6360860025645594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5886904356283171</v>
+        <v>0.5535925959438366</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,15 +1571,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5218885512154863</v>
+        <v>0.4915097818500893</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5217893976455106</v>
+        <v>0.4768475604420697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,15 +1601,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4907425889533472</v>
+        <v>0.4708180934358979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4815498040275554</v>
+        <v>0.4588855500075202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,60 +1631,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4784220786198372</v>
+        <v>0.4448727040210707</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4715073585001088</v>
+        <v>0.4342256112206926</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4572174313454684</v>
+        <v>0.4273505126236525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.453349978609509</v>
+        <v>0.4216144052680812</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.133110780393431</v>
+        <v>2.141537652053626</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.959835078562031</v>
+        <v>1.846822134313175</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.936035157632255</v>
+        <v>1.820215881191338</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.839329864672439</v>
+        <v>1.799470786449954</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,45 +1797,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.536796756395487</v>
+        <v>1.535332974307702</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.521984928511368</v>
+        <v>1.530090284669805</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.512662436886223</v>
+        <v>1.512022626902997</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.451004521331337</v>
+        <v>1.409184083312114</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.326829024943863</v>
+        <v>1.307159748158305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.25497891620082</v>
+        <v>1.258517445421214</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.246234778303559</v>
+        <v>1.2506113412066</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.19084482842008</v>
+        <v>1.167089339669949</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.160435608156397</v>
+        <v>1.157424877547376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1932,15 +1932,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAH.PA</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.021698354405436</v>
+        <v>1.020245018815574</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF EUR Hedged</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8483270322569436</v>
+        <v>0.7777538839882945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8430745504222081</v>
+        <v>0.7703698485382178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7885757206723769</v>
+        <v>0.735017962360087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6036035766300591</v>
+        <v>0.588502378999241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5687081932259126</v>
+        <v>0.5809445046439226</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5449424509819019</v>
+        <v>0.5684111199721826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4366301214932207</v>
+        <v>0.4335164620959513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.417817967454132</v>
+        <v>0.4312788627526494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4125726040193247</v>
+        <v>0.3904093392256032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3903752936814051</v>
+        <v>0.3767970133237133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3888944189783405</v>
+        <v>0.3703314947086611</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3477238971924523</v>
+        <v>0.3327799110125622</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3071079627612694</v>
+        <v>0.3140260599911329</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3022782524306693</v>
+        <v>0.2830621617552231</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJEUAS.MI</t>
+          <t>FUJI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2913385894788092</v>
+        <v>0.2817679594398612</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS MSCI AC Asia ex Japan SF UCITS ETF USD acc</t>
+          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,75 +442,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06214236304412535</v>
+        <v>0.073513738823346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.059959447692437</v>
+        <v>0.07234854227011955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04758793530526018</v>
+        <v>0.05754739444232593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04270971975018911</v>
+        <v>0.04713239385972967</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04111323530239708</v>
+        <v>0.03685147589200111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03836375004349257</v>
+        <v>0.03652565232450722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -532,105 +532,105 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03337337744601765</v>
+        <v>0.03331243415191376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>STU.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03255813318684164</v>
+        <v>0.03050242847762119</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03054640932250763</v>
+        <v>0.02893306436537024</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>ISF.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02886637486992583</v>
+        <v>0.02614505105920051</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02469774395453439</v>
+        <v>0.02393065021732954</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0234485964588913</v>
+        <v>0.02384897723079882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02232199602232554</v>
+        <v>0.02379333687815777</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02115908764883079</v>
+        <v>0.02208291779455762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -652,15 +652,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02103049470742735</v>
+        <v>0.02140187342202582</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1467137773024128</v>
+        <v>0.203296372031599</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1098218773736053</v>
+        <v>0.110989726486199</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1049678727915868</v>
+        <v>0.1088950373468507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.104840552393366</v>
+        <v>0.1064224446769408</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1001267335205629</v>
+        <v>0.1058848831564652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09692823509535575</v>
+        <v>0.08174430215217798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09683547105276391</v>
+        <v>0.07478499576288278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07880761806036296</v>
+        <v>0.06962731865830696</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07626253889853984</v>
+        <v>0.06786143661376554</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06993182381206053</v>
+        <v>0.06655441450045863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06842524027652885</v>
+        <v>0.06181838836716147</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>FUSR.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06529479970877272</v>
+        <v>0.05914788365173607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Fidelity US Equity Research Enhanced UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06097028634481427</v>
+        <v>0.05901698463826355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05966586978457289</v>
+        <v>0.05873104449903321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>500E.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05750083286944796</v>
+        <v>0.05661411162672891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi S&amp;P 500 Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4227326414131258</v>
+        <v>0.3902659841562754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,150 +969,150 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4004130215624158</v>
+        <v>0.2544839118355136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2435946819180648</v>
+        <v>0.2232904758694134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2257901958799078</v>
+        <v>0.2131781920792146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2047953363728041</v>
+        <v>0.17902811356536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1992835555382191</v>
+        <v>0.139785075570646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1401514662335637</v>
+        <v>0.1364698422663984</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1336905504800363</v>
+        <v>0.1302700104447889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1293778793760265</v>
+        <v>0.1225868666209118</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1238603464565404</v>
+        <v>0.1189189177247112</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1135470910387986</v>
+        <v>0.1083979925394898</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1105735113797188</v>
+        <v>0.1062671057569338</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1134,45 +1134,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1104170395393986</v>
+        <v>0.1002074261391126</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1075932461401907</v>
+        <v>0.09882053868461038</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1039064674815682</v>
+        <v>0.09810776111793462</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7091799547215196</v>
+        <v>0.7078698347601589</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.419362744525138</v>
+        <v>0.3769500067757123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3806567650037189</v>
+        <v>0.3621814188894821</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3419411072520102</v>
+        <v>0.3426006952156249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,30 +1270,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2981816750315358</v>
+        <v>0.2969762851945916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2784437118567888</v>
+        <v>0.260486553336589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2721509243386038</v>
+        <v>0.2177348878672016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,75 +1315,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JSOL.AS</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2644486342168031</v>
+        <v>0.2156460857640501</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21shares Jito Staked SOL ETP</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2514140984948496</v>
+        <v>0.2062231753508335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2236770258819216</v>
+        <v>0.1970389984262308</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>EQQQ.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2217810588916469</v>
+        <v>0.1969644217314108</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2141023489925802</v>
+        <v>0.1925729874696065</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2056179429324365</v>
+        <v>0.1834258980046599</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>ENAM.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2038789007635899</v>
+        <v>0.1823536982130318</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>BNP Paribas Easy MSCI USA Min TE UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SP5C.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2017211889924344</v>
+        <v>0.1809312955880749</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.118074635605292</v>
+        <v>1.130592073711649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.108404345401146</v>
+        <v>1.11685715980919</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,60 +1496,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6676745129549684</v>
+        <v>0.6897839618752057</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6494929381909189</v>
+        <v>0.6805383626425288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6493089034052404</v>
+        <v>0.6732134866764938</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6360860025645594</v>
+        <v>0.6547012948890278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5535925959438366</v>
+        <v>0.5646120848518417</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4915097818500893</v>
+        <v>0.5113710150811208</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,30 +1586,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4768475604420697</v>
+        <v>0.4775460146054551</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4708180934358979</v>
+        <v>0.4761745456279043</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4588855500075202</v>
+        <v>0.4756303488819118</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1631,60 +1631,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4448727040210707</v>
+        <v>0.4362500508626301</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4342256112206926</v>
+        <v>0.4331123283509888</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4273505126236525</v>
+        <v>0.4291906496334104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4216144052680812</v>
+        <v>0.4231351692667824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.32611234478287</v>
+        <v>2.292970532063115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.141537652053626</v>
+        <v>2.126790626648284</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.846822134313175</v>
+        <v>1.813107388111123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.820215881191338</v>
+        <v>1.784701358690267</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.799470786449954</v>
+        <v>1.720811326219517</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.535332974307702</v>
+        <v>1.539239873592737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.530090284669805</v>
+        <v>1.527742916881573</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.512022626902997</v>
+        <v>1.511658501762636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.409184083312114</v>
+        <v>1.345223542203785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.307159748158305</v>
+        <v>1.284300776708598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.258517445421214</v>
+        <v>1.265461202817198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2506113412066</v>
+        <v>1.252668503195109</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.167089339669949</v>
+        <v>1.18844248044414</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.157424877547376</v>
+        <v>1.122080901625231</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.020245018815574</v>
+        <v>1.011166171086732</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,45 +1978,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7777538839882945</v>
+        <v>0.7574775545157577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7703698485382178</v>
+        <v>0.7567000498600738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.735017962360087</v>
+        <v>0.7480758673432151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.588502378999241</v>
+        <v>0.6083946267281628</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,60 +2038,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5809445046439226</v>
+        <v>0.5827270940010865</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5684111199721826</v>
+        <v>0.554190465131658</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4335164620959513</v>
+        <v>0.4419057608956363</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4312788627526494</v>
+        <v>0.4245421419958917</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3904093392256032</v>
+        <v>0.3821821006545154</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3767970133237133</v>
+        <v>0.3765974425076088</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3703314947086611</v>
+        <v>0.3531148744922283</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3327799110125622</v>
+        <v>0.3206033883296544</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3140260599911329</v>
+        <v>0.310092244056172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>FUJI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2830621617552231</v>
+        <v>0.2750592141821235</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FUJI.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2817679594398612</v>
+        <v>0.2741343403920913</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,45 +442,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.073513738823346</v>
+        <v>0.07053800677428446</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07234854227011955</v>
+        <v>0.06700609144377268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05754739444232593</v>
+        <v>0.06305374637726824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04713239385972967</v>
+        <v>0.05698943432049153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,165 +502,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03685147589200111</v>
+        <v>0.05688303181710741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>LYINR.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03652565232450722</v>
+        <v>0.05658962613168828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03331243415191376</v>
+        <v>0.05066049256876837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STU.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03050242847762119</v>
+        <v>0.04793802242265732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02893306436537024</v>
+        <v>0.04352182395470727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ISF.L</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02614505105920051</v>
+        <v>0.04148566050023583</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>XASX.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02393065021732954</v>
+        <v>0.04023569914121028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INR.PA</t>
+          <t>ISF.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02384897723079882</v>
+        <v>0.03880246549806654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
+          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02379333687815777</v>
+        <v>0.03760421984005435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIVO.L</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02208291779455762</v>
+        <v>0.03663356162640041</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02140187342202582</v>
+        <v>0.03487900353340168</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.203296372031599</v>
+        <v>0.248561526931131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,105 +713,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.110989726486199</v>
+        <v>0.1015733286824978</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1088950373468507</v>
+        <v>0.09622234856742495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1064224446769408</v>
+        <v>0.09604150271843603</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1058848831564652</v>
+        <v>0.0856389721693831</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08174430215217798</v>
+        <v>0.08407409513752584</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07478499576288278</v>
+        <v>0.08007169811776338</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06962731865830696</v>
+        <v>0.07965668137907822</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06786143661376554</v>
+        <v>0.06995393307603304</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -833,75 +833,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06655441450045863</v>
+        <v>0.06784013019490209</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06181838836716147</v>
+        <v>0.056888127905111</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FUSR.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05914788365173607</v>
+        <v>0.05688664884188888</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fidelity US Equity Research Enhanced UCITS ETF ACC-USD</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05901698463826355</v>
+        <v>0.05181065402006357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>FUSR.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05873104449903321</v>
+        <v>0.0514410461717878</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Fidelity US Equity Research Enhanced UCITS ETF ACC-USD</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05661411162672891</v>
+        <v>0.05071156728309667</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3902659841562754</v>
+        <v>0.4358495046502751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,45 +969,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2544839118355136</v>
+        <v>0.2297989254241888</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2232904758694134</v>
+        <v>0.2281566782044306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2131781920792146</v>
+        <v>0.2233236891308525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.17902811356536</v>
+        <v>0.2086577190151981</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,150 +1029,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.139785075570646</v>
+        <v>0.1954039825270462</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1364698422663984</v>
+        <v>0.1354638746442998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1302700104447889</v>
+        <v>0.1197847252064657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1225868666209118</v>
+        <v>0.1188720323834966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1189189177247112</v>
+        <v>0.115775265464142</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1083979925394898</v>
+        <v>0.1122886441632596</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1062671057569338</v>
+        <v>0.1079286162308479</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1002074261391126</v>
+        <v>0.1063780867112809</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09882053868461038</v>
+        <v>0.1056988124998315</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09810776111793462</v>
+        <v>0.09450735540727417</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7078698347601589</v>
+        <v>0.6806669100465983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,30 +1225,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3769500067757123</v>
+        <v>0.3126092083988263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3621814188894821</v>
+        <v>0.3096966952489091</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3426006952156249</v>
+        <v>0.3016563792983373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2969762851945916</v>
+        <v>0.2612974388802878</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.260486553336589</v>
+        <v>0.2172188581582406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,15 +1300,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2177348878672016</v>
+        <v>0.2005902598576619</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2156460857640501</v>
+        <v>0.1921832791970945</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1330,105 +1330,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2062231753508335</v>
+        <v>0.18924766184317</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1970389984262308</v>
+        <v>0.1852643799323119</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EQQQ.L</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1969644217314108</v>
+        <v>0.1833085067362765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invesco EQQQ Nasdaq-100 UCITS ETF</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1925729874696065</v>
+        <v>0.1772264332226918</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1834258980046599</v>
+        <v>0.1711350689673858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENAM.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1823536982130318</v>
+        <v>0.1652666634552777</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI USA Min TE UCITS ETF</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SP5C.PA</t>
+          <t>SPEEU.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1809312955880749</v>
+        <v>0.1618131260014146</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF Acc</t>
+          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.130592073711649</v>
+        <v>0.9691855494846038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.11685715980919</v>
+        <v>0.9525204096483688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,45 +1496,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6897839618752057</v>
+        <v>0.6605776402657855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6805383626425288</v>
+        <v>0.6491221979724162</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6732134866764938</v>
+        <v>0.5751122858832074</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6547012948890278</v>
+        <v>0.5598696505487106</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5646120848518417</v>
+        <v>0.5560516985767732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5113710150811208</v>
+        <v>0.4803250279865439</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,60 +1586,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4775460146054551</v>
+        <v>0.4569257776211979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4761745456279043</v>
+        <v>0.4507654989677643</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4756303488819118</v>
+        <v>0.4180085832586249</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4362500508626301</v>
+        <v>0.4135304222142373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4331123283509888</v>
+        <v>0.4098031138599225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,30 +1661,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4291906496334104</v>
+        <v>0.4058318739951614</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4231351692667824</v>
+        <v>0.3886946647402643</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.292970532063115</v>
+        <v>2.217659893648619</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.126790626648284</v>
+        <v>2.056049793086524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,45 +1752,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.813107388111123</v>
+        <v>1.669373294749563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.784701358690267</v>
+        <v>1.669143869490644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.720811326219517</v>
+        <v>1.636400863015698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.539239873592737</v>
+        <v>1.509352646879825</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,30 +1812,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.527742916881573</v>
+        <v>1.434770056495272</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.511658501762636</v>
+        <v>1.39588500645255</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.345223542203785</v>
+        <v>1.27191917342369</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,75 +1857,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.284300776708598</v>
+        <v>1.259815737401973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.265461202817198</v>
+        <v>1.236593509038189</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.252668503195109</v>
+        <v>1.218735812707506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.18844248044414</v>
+        <v>1.155024501969108</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.122080901625231</v>
+        <v>1.154050047330971</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.011166171086732</v>
+        <v>0.9870577501284197</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7574775545157577</v>
+        <v>0.741280640173859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7567000498600738</v>
+        <v>0.6666845870087792</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7480758673432151</v>
+        <v>0.6569036807148818</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6083946267281628</v>
+        <v>0.5863138654185012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5827270940010865</v>
+        <v>0.5787373916244611</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.554190465131658</v>
+        <v>0.5025935098077707</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4419057608956363</v>
+        <v>0.4192347971203967</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4245421419958917</v>
+        <v>0.4170330569377818</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,30 +2098,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3821821006545154</v>
+        <v>0.3490414354717473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3765974425076088</v>
+        <v>0.3457470588823048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3531148744922283</v>
+        <v>0.3281689011165125</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3206033883296544</v>
+        <v>0.3175592312669431</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.310092244056172</v>
+        <v>0.3110417786962305</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FUJI.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2750592141821235</v>
+        <v>0.2741343403920913</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2741343403920913</v>
+        <v>0.2651680949927933</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,15 +442,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07053800677428446</v>
+        <v>0.05212396756387849</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06700609144377268</v>
+        <v>0.0465430204514421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,105 +472,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06305374637726824</v>
+        <v>0.04455035169516419</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05698943432049153</v>
+        <v>0.04398230299509454</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INR.PA</t>
+          <t>LYINR.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05688303181710741</v>
+        <v>0.04192946674497056</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LYINR.SW</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05658962613168828</v>
+        <v>0.04159311693016043</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05066049256876837</v>
+        <v>0.04065889908598397</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04793802242265732</v>
+        <v>0.04035273015559371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04352182395470727</v>
+        <v>0.03961727337620902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04148566050023583</v>
+        <v>0.03898067957303897</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -592,75 +592,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XASX.L</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04023569914121028</v>
+        <v>0.03654437983801606</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI UK ESG UCITS ETF 1D</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ISF.L</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03880246549806654</v>
+        <v>0.03566613265025409</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Core FTSE 100 UCITS ETF (Dist)</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03760421984005435</v>
+        <v>0.03445830315623177</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03663356162640041</v>
+        <v>0.03285907859078585</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03487900353340168</v>
+        <v>0.03225804246330699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.248561526931131</v>
+        <v>0.2774500608664119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,210 +713,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1015733286824978</v>
+        <v>0.1067556471051083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09622234856742495</v>
+        <v>0.0944443968588442</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09604150271843603</v>
+        <v>0.08512058204811646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0856389721693831</v>
+        <v>0.08267344426929024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08407409513752584</v>
+        <v>0.08242166431767983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08007169811776338</v>
+        <v>0.07692305803422883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07965668137907822</v>
+        <v>0.07313600018087363</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06995393307603304</v>
+        <v>0.07170259549603197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06784013019490209</v>
+        <v>0.06924312813159528</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.056888127905111</v>
+        <v>0.05622057169264916</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05688664884188888</v>
+        <v>0.04753524255565722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05181065402006357</v>
+        <v>0.04393881835541191</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FUSR.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0514410461717878</v>
+        <v>0.04369243728529426</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fidelity US Equity Research Enhanced UCITS ETF ACC-USD</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>500E.AS</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05071156728309667</v>
+        <v>0.04309737125183255</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Swap UCITS ETF USD Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4358495046502751</v>
+        <v>0.4414121528023265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,75 +969,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2297989254241888</v>
+        <v>0.3120992891171377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2281566782044306</v>
+        <v>0.2777586010407649</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2233236891308525</v>
+        <v>0.2365456132922381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2086577190151981</v>
+        <v>0.2068720129637496</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1954039825270462</v>
+        <v>0.2034459674755393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1354638746442998</v>
+        <v>0.1340849205259176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,120 +1059,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1197847252064657</v>
+        <v>0.1309192608594971</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1188720323834966</v>
+        <v>0.1268345883486408</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.115775265464142</v>
+        <v>0.1169049074442661</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1122886441632596</v>
+        <v>0.1168509696835933</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1079286162308479</v>
+        <v>0.105370265872117</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1063780867112809</v>
+        <v>0.1018907840771164</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1056988124998315</v>
+        <v>0.09794986532120542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09450735540727417</v>
+        <v>0.09556060657705179</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6806669100465983</v>
+        <v>0.5922641915963123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,150 +1225,150 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3126092083988263</v>
+        <v>0.3221890021924667</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3096966952489091</v>
+        <v>0.2734538371172881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3016563792983373</v>
+        <v>0.265967431466051</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2612974388802878</v>
+        <v>0.2558355682550695</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2172188581582406</v>
+        <v>0.2365754371932982</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2005902598576619</v>
+        <v>0.1962141780408362</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1921832791970945</v>
+        <v>0.1869448537418164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.18924766184317</v>
+        <v>0.1797939485803504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1852643799323119</v>
+        <v>0.1684015008360067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1833085067362765</v>
+        <v>0.1633168520323514</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1772264332226918</v>
+        <v>0.1572786034066131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1390,15 +1390,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1711350689673858</v>
+        <v>0.156431469549744</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1652666634552777</v>
+        <v>0.1525309217353097</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1618131260014146</v>
+        <v>0.141739190494371</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9691855494846038</v>
+        <v>0.8778657113975759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9525204096483688</v>
+        <v>0.8658442908660537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6605776402657855</v>
+        <v>0.6746542610094353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6491221979724162</v>
+        <v>0.6669405507414496</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,45 +1526,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5751122858832074</v>
+        <v>0.5285674848054289</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5598696505487106</v>
+        <v>0.5249960528857971</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5560516985767732</v>
+        <v>0.5095492195024574</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4803250279865439</v>
+        <v>0.5021396015965662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,90 +1586,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4569257776211979</v>
+        <v>0.4689002438288559</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4507654989677643</v>
+        <v>0.4393481608726739</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4180085832586249</v>
+        <v>0.4238708507452167</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4135304222142373</v>
+        <v>0.4124318546255097</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4098031138599225</v>
+        <v>0.3879162850128923</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4058318739951614</v>
+        <v>0.3872357212941819</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3886946647402643</v>
+        <v>0.3852203739729791</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.217659893648619</v>
+        <v>2.277801743365162</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.056049793086524</v>
+        <v>2.086316519980938</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1752,45 +1752,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.669373294749563</v>
+        <v>1.635001357446554</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.669143869490644</v>
+        <v>1.611738927882337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.636400863015698</v>
+        <v>1.608965643521013</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.509352646879825</v>
+        <v>1.548375132267088</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.434770056495272</v>
+        <v>1.427451982112104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.39588500645255</v>
+        <v>1.37075636915205</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.27191917342369</v>
+        <v>1.307754855433733</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.259815737401973</v>
+        <v>1.302255031926336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.236593509038189</v>
+        <v>1.259717509154385</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.218735812707506</v>
+        <v>1.219620894458314</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,30 +1902,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.155024501969108</v>
+        <v>1.174718681866884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.154050047330971</v>
+        <v>1.163469023407373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9870577501284197</v>
+        <v>1.006541370153803</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.741280640173859</v>
+        <v>0.7069431117443539</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6666845870087792</v>
+        <v>0.6453085145336706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6569036807148818</v>
+        <v>0.6381036337499881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5863138654185012</v>
+        <v>0.5909411281476848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5787373916244611</v>
+        <v>0.5901681862220212</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5025935098077707</v>
+        <v>0.4826645029568328</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4192347971203967</v>
+        <v>0.4300390523389175</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4170330569377818</v>
+        <v>0.4056776949614276</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3490414354717473</v>
+        <v>0.3362618954108767</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3457470588823048</v>
+        <v>0.3306357128638016</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,75 +2128,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3281689011165125</v>
+        <v>0.3262343329371677</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3175592312669431</v>
+        <v>0.3191566846873737</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3110417786962305</v>
+        <v>0.3084267600788086</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2741343403920913</v>
+        <v>0.2734614403979541</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2651680949927933</v>
+        <v>0.2644281771640726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05212396756387849</v>
+        <v>0.04262897957450651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,30 +457,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0465430204514421</v>
+        <v>0.03729022609757382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04455035169516419</v>
+        <v>0.03600215230091219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04398230299509454</v>
+        <v>0.03559323758055255</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -502,120 +502,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LYINR.SW</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04192946674497056</v>
+        <v>0.03287804538418682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04159311693016043</v>
+        <v>0.03192584963954692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INR.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04065889908598397</v>
+        <v>0.03038128569172915</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04035273015559371</v>
+        <v>0.02638284624216758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03961727337620902</v>
+        <v>0.02614103754538477</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03898067957303897</v>
+        <v>0.02539297839445265</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03654437983801606</v>
+        <v>0.02394531478360773</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03566613265025409</v>
+        <v>0.02185965093959985</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03445830315623177</v>
+        <v>0.0217544154116982</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -637,30 +637,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03285907859078585</v>
+        <v>0.01933326922510048</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>LYINR.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03225804246330699</v>
+        <v>0.01893032130463901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
         </is>
       </c>
     </row>
@@ -698,120 +698,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2774500608664119</v>
+        <v>0.1076421934687972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1067556471051083</v>
+        <v>0.1042180913833826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0944443968588442</v>
+        <v>0.1001976834932563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08512058204811646</v>
+        <v>0.08940154873384243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08267344426929024</v>
+        <v>0.08216337109599681</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08242166431767983</v>
+        <v>0.08206380160660509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07692305803422883</v>
+        <v>0.08195635864146733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07313600018087363</v>
+        <v>0.06718424691433245</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07170259549603197</v>
+        <v>0.05724402547938312</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -833,90 +833,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06924312813159528</v>
+        <v>0.04921354826612423</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05622057169264916</v>
+        <v>0.04622598819232748</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04753524255565722</v>
+        <v>0.0459770359062488</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04393881835541191</v>
+        <v>0.04552470299778255</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>EMWE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04369243728529426</v>
+        <v>0.04051711488660104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI World SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04309737125183255</v>
+        <v>0.04041327433291086</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4414121528023265</v>
+        <v>0.3955885655920861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3120992891171377</v>
+        <v>0.3028827140077377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2777586010407649</v>
+        <v>0.2890404319048949</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2365456132922381</v>
+        <v>0.2641328302912058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2068720129637496</v>
+        <v>0.2005309518459624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2034459674755393</v>
+        <v>0.1991514068074427</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1340849205259176</v>
+        <v>0.1348770973550095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,15 +1059,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1309192608594971</v>
+        <v>0.1221628567489315</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1268345883486408</v>
+        <v>0.121473579616916</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1169049074442661</v>
+        <v>0.1146683288816559</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,60 +1104,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1168509696835933</v>
+        <v>0.1141521438373851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.105370265872117</v>
+        <v>0.1022659827922952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1018907840771164</v>
+        <v>0.09794986532120542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09794986532120542</v>
+        <v>0.09598731588792275</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5922641915963123</v>
+        <v>0.5828834241351688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,30 +1225,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3221890021924667</v>
+        <v>0.3051385388610361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2734538371172881</v>
+        <v>0.303227783336848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.265967431466051</v>
+        <v>0.2987043957759752</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1270,30 +1270,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2558355682550695</v>
+        <v>0.2880091278430583</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2365754371932982</v>
+        <v>0.2272480058113153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1962141780408362</v>
+        <v>0.2089412678005922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1869448537418164</v>
+        <v>0.2028951711350302</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1797939485803504</v>
+        <v>0.1758145359151524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1345,90 +1345,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1684015008360067</v>
+        <v>0.1743414627691631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1633168520323514</v>
+        <v>0.1728625420289505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1572786034066131</v>
+        <v>0.1645913914254731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.156431469549744</v>
+        <v>0.1604849827400536</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1525309217353097</v>
+        <v>0.1503020337081473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPEEU.PA</t>
+          <t>SP5.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.141739190494371</v>
+        <v>0.1491375590324338</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy S&amp;P 500 Scored and Screened UCITS ETF EUR Acc</t>
+          <t>Amundi Core S&amp;P 500 Swap UCITS ETF EUR Dist</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8778657113975759</v>
+        <v>0.9652672328545975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8658442908660537</v>
+        <v>0.9529820336103734</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,75 +1496,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6746542610094353</v>
+        <v>0.6869982617935817</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6669405507414496</v>
+        <v>0.6781295579118971</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5285674848054289</v>
+        <v>0.6048657015785268</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5249960528857971</v>
+        <v>0.581015207782442</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5095492195024574</v>
+        <v>0.5716368749328018</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5021396015965662</v>
+        <v>0.5238987921853406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4689002438288559</v>
+        <v>0.4715779905213708</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4393481608726739</v>
+        <v>0.4580407169039149</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,45 +1616,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4238708507452167</v>
+        <v>0.4473684637145474</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4124318546255097</v>
+        <v>0.4247936920224731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3879162850128923</v>
+        <v>0.4233947896520573</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3872357212941819</v>
+        <v>0.4154171777659061</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3852203739729791</v>
+        <v>0.4081812655864838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.277801743365162</v>
+        <v>2.414005845693491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.086316519980938</v>
+        <v>2.124027137085743</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.635001357446554</v>
+        <v>1.841891410543283</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.611738927882337</v>
+        <v>1.815962246667688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.608965643521013</v>
+        <v>1.698174378196782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.548375132267088</v>
+        <v>1.623480685272479</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.427451982112104</v>
+        <v>1.50498481499575</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.37075636915205</v>
+        <v>1.458966640240129</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.307754855433733</v>
+        <v>1.398284964500011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.302255031926336</v>
+        <v>1.375941816927483</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,30 +1872,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.259717509154385</v>
+        <v>1.328984708042011</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.219620894458314</v>
+        <v>1.307831883856021</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.174718681866884</v>
+        <v>1.274432244395392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.163469023407373</v>
+        <v>1.069135017443203</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.006541370153803</v>
+        <v>1.044609987783163</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,30 +1978,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7069431117443539</v>
+        <v>0.7127664735749804</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6453085145336706</v>
+        <v>0.7095346427536504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6381036337499881</v>
+        <v>0.7061500528355054</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5909411281476848</v>
+        <v>0.6062714047163316</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5901681862220212</v>
+        <v>0.5918797889624632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4826645029568328</v>
+        <v>0.5050504642881133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4300390523389175</v>
+        <v>0.4399575356487722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4056776949614276</v>
+        <v>0.4216118116444965</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,15 +2098,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3362618954108767</v>
+        <v>0.3531479179121948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3306357128638016</v>
+        <v>0.34725812943403</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,15 +2128,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3262343329371677</v>
+        <v>0.3448481631715368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3191566846873737</v>
+        <v>0.3301012771687042</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3084267600788086</v>
+        <v>0.3168746639113087</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2734614403979541</v>
+        <v>0.3156220596030244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2644281771640726</v>
+        <v>0.2745526919654704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04262897957450651</v>
+        <v>0.05991906252139656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03729022609757382</v>
+        <v>0.05564038502558222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03600215230091219</v>
+        <v>0.05085672652466466</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03559323758055255</v>
+        <v>0.041109735427034</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03287804538418682</v>
+        <v>0.0404480771010407</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03192584963954692</v>
+        <v>0.03892012401670719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03038128569172915</v>
+        <v>0.03317635185749745</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02638284624216758</v>
+        <v>0.02587308617816042</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02614103754538477</v>
+        <v>0.0254116697478679</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02539297839445265</v>
+        <v>0.02477477953799601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02394531478360773</v>
+        <v>0.02448162984688551</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02185965093959985</v>
+        <v>0.02079838980207982</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0217544154116982</v>
+        <v>0.02078663289119764</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01933326922510048</v>
+        <v>0.02056278673704104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LYINR.SW</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01893032130463901</v>
+        <v>0.02013420300660118</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI India Swap UCITS ETF USD Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1076421934687972</v>
+        <v>0.1244175298323205</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,30 +713,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1042180913833826</v>
+        <v>0.1021753042484024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1001976834932563</v>
+        <v>0.09932966555185763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08940154873384243</v>
+        <v>0.09301583957038573</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,165 +758,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08216337109599681</v>
+        <v>0.08898411990366561</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08206380160660509</v>
+        <v>0.0802263398175278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08195635864146733</v>
+        <v>0.07466494688003533</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06718424691433245</v>
+        <v>0.07256166685424992</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05724402547938312</v>
+        <v>0.06232042388082681</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04921354826612423</v>
+        <v>0.06147991151788323</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04622598819232748</v>
+        <v>0.05621302139411077</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0459770359062488</v>
+        <v>0.05292547590862728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04552470299778255</v>
+        <v>0.05052428221576988</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMWE.PA</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04051711488660104</v>
+        <v>0.0484732029739483</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI World SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04041327433291086</v>
+        <v>0.04494617389331101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3955885655920861</v>
+        <v>0.3798478827441416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3028827140077377</v>
+        <v>0.302037525311613</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,60 +984,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2890404319048949</v>
+        <v>0.2840144208336102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2641328302912058</v>
+        <v>0.2263026534209496</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2005309518459624</v>
+        <v>0.1830271478836472</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1991514068074427</v>
+        <v>0.1809255728519403</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1348770973550095</v>
+        <v>0.1482274499923397</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,120 +1059,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1221628567489315</v>
+        <v>0.1366417219947822</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.121473579616916</v>
+        <v>0.1298538039220183</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1146683288816559</v>
+        <v>0.1131585566013724</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1141521438373851</v>
+        <v>0.1126787376911251</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1022659827922952</v>
+        <v>0.1125284386105743</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09794986532120542</v>
+        <v>0.09686123192881402</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09598731588792275</v>
+        <v>0.08859755506502909</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09556060657705179</v>
+        <v>0.0874765529965551</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5828834241351688</v>
+        <v>0.638561443777137</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3051385388610361</v>
+        <v>0.3012150947069334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.303227783336848</v>
+        <v>0.288565225352692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,90 +1255,90 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2987043957759752</v>
+        <v>0.2755140380785519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2880091278430583</v>
+        <v>0.2705386861094223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2272480058113153</v>
+        <v>0.218273819109982</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2089412678005922</v>
+        <v>0.2052244518903426</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2028951711350302</v>
+        <v>0.1922625184321103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1758145359151524</v>
+        <v>0.1823771377962904</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1743414627691631</v>
+        <v>0.1744535567586816</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,30 +1360,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1728625420289505</v>
+        <v>0.1692113714694619</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1645913914254731</v>
+        <v>0.167679612781128</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1604849827400536</v>
+        <v>0.1564899227246319</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1503020337081473</v>
+        <v>0.1511889665324311</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SP5.PA</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1491375590324338</v>
+        <v>0.1503243872221209</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core S&amp;P 500 Swap UCITS ETF EUR Dist</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9652672328545975</v>
+        <v>0.8487253357814728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9529820336103734</v>
+        <v>0.836911625566237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6869982617935817</v>
+        <v>0.6615201191475308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6781295579118971</v>
+        <v>0.6595220145722001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,45 +1526,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6048657015785268</v>
+        <v>0.5426255318795514</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.581015207782442</v>
+        <v>0.5424111997275114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5716368749328018</v>
+        <v>0.5163179393186483</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5238987921853406</v>
+        <v>0.5003708438744636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,105 +1586,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4715779905213708</v>
+        <v>0.4530979613092811</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4580407169039149</v>
+        <v>0.4380041623166735</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4473684637145474</v>
+        <v>0.4226157188683959</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BRES.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4247936920224731</v>
+        <v>0.3839490227687909</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4233947896520573</v>
+        <v>0.3768817863687712</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4154171777659061</v>
+        <v>0.3682597858751793</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4081812655864838</v>
+        <v>0.3645950545213101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.414005845693491</v>
+        <v>2.408348975304231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.124027137085743</v>
+        <v>2.11148968261806</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.841891410543283</v>
+        <v>1.75580586034388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.815962246667688</v>
+        <v>1.728366672075223</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.698174378196782</v>
+        <v>1.692210406366939</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.623480685272479</v>
+        <v>1.609457601837569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.50498481499575</v>
+        <v>1.512276603210117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.458966640240129</v>
+        <v>1.438196637597475</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,60 +1842,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.398284964500011</v>
+        <v>1.378239188740578</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.375941816927483</v>
+        <v>1.371704089404399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.328984708042011</v>
+        <v>1.307831883856021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.307831883856021</v>
+        <v>1.306319544246299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.274432244395392</v>
+        <v>1.257227320439718</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.069135017443203</v>
+        <v>1.062206368590279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.044609987783163</v>
+        <v>1.045424754406449</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1978,30 +1978,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7127664735749804</v>
+        <v>0.7710831438032999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7095346427536504</v>
+        <v>0.660883968953663</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7061500528355054</v>
+        <v>0.653077184264222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6062714047163316</v>
+        <v>0.5923240540183068</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5918797889624632</v>
+        <v>0.5808494858887536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5050504642881133</v>
+        <v>0.4840294053477618</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4399575356487722</v>
+        <v>0.4334042761635468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4216118116444965</v>
+        <v>0.4144689654806217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,15 +2098,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3531479179121948</v>
+        <v>0.3376596528442801</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.34725812943403</v>
+        <v>0.3360086216592415</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,15 +2128,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3448481631715368</v>
+        <v>0.3355472689416064</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3301012771687042</v>
+        <v>0.3204079786150182</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3168746639113087</v>
+        <v>0.3057514994885449</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,15 +2173,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3156220596030244</v>
+        <v>0.2812172487165674</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2745526919654704</v>
+        <v>0.2782628016005577</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,150 +442,150 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05991906252139656</v>
+        <v>0.07412057527470206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05564038502558222</v>
+        <v>0.04444741176663558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05085672652466466</v>
+        <v>0.04333896539845128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.041109735427034</v>
+        <v>0.036252332977738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XSMC.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0404480771010407</v>
+        <v>0.02694013733248957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03892012401670719</v>
+        <v>0.0259529348665053</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03317635185749745</v>
+        <v>0.02589225623542513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>XEWE.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02587308617816042</v>
+        <v>0.02518999391106891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers S&amp;P 500 Equal Weight Scored &amp; Screened UCITS ETF 2C - EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TELE.PA</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0254116697478679</v>
+        <v>0.02497911153047938</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02477477953799601</v>
+        <v>0.024484310599866</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02448162984688551</v>
+        <v>0.02350593056217787</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -607,60 +607,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>DDGT.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02079838980207982</v>
+        <v>0.02223564473151596</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Dimensional Global Targeted Value UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02078663289119764</v>
+        <v>0.02011555775038465</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>WLDHC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02056278673704104</v>
+        <v>0.01983146656567825</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Amundi MSCI World Swap II UCITS ETF EUR Hedged Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>CEU2.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02013420300660118</v>
+        <v>0.01961927200611058</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi Core MSCI Europe UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -698,15 +698,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1244175298323205</v>
+        <v>0.1125121523279111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1021753042484024</v>
+        <v>0.1123212824290456</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -728,30 +728,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09932966555185763</v>
+        <v>0.1083199084824309</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09301583957038573</v>
+        <v>0.1059645920697943</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08898411990366561</v>
+        <v>0.09790800053624982</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,75 +773,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0802263398175278</v>
+        <v>0.09152907945601974</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07466494688003533</v>
+        <v>0.08386963126639957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07256166685424992</v>
+        <v>0.07226077368592931</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06232042388082681</v>
+        <v>0.07124241650938501</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06147991151788323</v>
+        <v>0.06294084797634758</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05621302139411077</v>
+        <v>0.0585483895970178</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05292547590862728</v>
+        <v>0.0567409614558565</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05052428221576988</v>
+        <v>0.05299490260969963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0484732029739483</v>
+        <v>0.04588675644310114</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04494617389331101</v>
+        <v>0.04541935207078596</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3798478827441416</v>
+        <v>0.409526282277008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.302037525311613</v>
+        <v>0.3707722770091897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -984,30 +984,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2840144208336102</v>
+        <v>0.2955149721619035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2263026534209496</v>
+        <v>0.294503468722378</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1830271478836472</v>
+        <v>0.1761107913464515</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1809255728519403</v>
+        <v>0.1712564543889845</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1044,15 +1044,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1482274499923397</v>
+        <v>0.1372286494913268</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1366417219947822</v>
+        <v>0.1307957910871671</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,105 +1074,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1298538039220183</v>
+        <v>0.1278142786339376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1131585566013724</v>
+        <v>0.1081636480773589</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1126787376911251</v>
+        <v>0.1067207845461375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1125284386105743</v>
+        <v>0.105530485824948</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09686123192881402</v>
+        <v>0.1018222608345654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08859755506502909</v>
+        <v>0.09610930972633458</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0874765529965551</v>
+        <v>0.08916782561707004</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.638561443777137</v>
+        <v>0.6550210126311873</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3012150947069334</v>
+        <v>0.3001178332608812</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.288565225352692</v>
+        <v>0.2770284504275851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2755140380785519</v>
+        <v>0.2729495553645975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2705386861094223</v>
+        <v>0.2607299034254245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,150 +1285,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.218273819109982</v>
+        <v>0.2437629640887042</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2052244518903426</v>
+        <v>0.2145029298386092</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1922625184321103</v>
+        <v>0.204462557594048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1823771377962904</v>
+        <v>0.1984854079428475</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1744535567586816</v>
+        <v>0.1859053399547763</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1692113714694619</v>
+        <v>0.1813235905231321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.167679612781128</v>
+        <v>0.1733444487255642</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1564899227246319</v>
+        <v>0.1714522515448991</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1511889665324311</v>
+        <v>0.1694664106802513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>AJASE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1503243872221209</v>
+        <v>0.1595844200640426</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8487253357814728</v>
+        <v>0.9027983365052512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.836911625566237</v>
+        <v>0.8880297079405046</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,30 +1496,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6615201191475308</v>
+        <v>0.6666667164953533</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6595220145722001</v>
+        <v>0.6661702275714509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5426255318795514</v>
+        <v>0.5633723319090655</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,30 +1541,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5424111997275114</v>
+        <v>0.5414620856578058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5163179393186483</v>
+        <v>0.5380334261971511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5003708438744636</v>
+        <v>0.5086103378504714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,30 +1586,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4530979613092811</v>
+        <v>0.4611127961354138</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4380041623166735</v>
+        <v>0.4558434366968482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4226157188683959</v>
+        <v>0.4052443779790198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3839490227687909</v>
+        <v>0.3950150746680929</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3768817863687712</v>
+        <v>0.3910710869715317</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,15 +1661,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3682597858751793</v>
+        <v>0.3876196979967166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3645950545213101</v>
+        <v>0.3773353304164158</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.408348975304231</v>
+        <v>2.486840041341469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.11148968261806</v>
+        <v>2.158613655133188</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.75580586034388</v>
+        <v>1.804463087820987</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.728366672075223</v>
+        <v>1.773949178351541</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.692210406366939</v>
+        <v>1.742635007736947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.609457601837569</v>
+        <v>1.635945615304912</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.512276603210117</v>
+        <v>1.547020539256077</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.438196637597475</v>
+        <v>1.474417517074587</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.378239188740578</v>
+        <v>1.441646875134743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1857,45 +1857,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.371704089404399</v>
+        <v>1.335349382208215</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.307831883856021</v>
+        <v>1.335065641649629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.306319544246299</v>
+        <v>1.330546573731431</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.257227320439718</v>
+        <v>1.320124041403369</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,30 +1917,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.062206368590279</v>
+        <v>1.069052520279227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.045424754406449</v>
+        <v>1.064096104944089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7710831438032999</v>
+        <v>0.7903034766635546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.660883968953663</v>
+        <v>0.6902089697649956</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.653077184264222</v>
+        <v>0.6806949534952353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5923240540183068</v>
+        <v>0.6081005654636134</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5808494858887536</v>
+        <v>0.5970429247886027</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4840294053477618</v>
+        <v>0.499590464194386</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4334042761635468</v>
+        <v>0.4507616219557924</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4144689654806217</v>
+        <v>0.4155678218958319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3376596528442801</v>
+        <v>0.3512379332019722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3360086216592415</v>
+        <v>0.3497767084538224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2128,30 +2128,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3355472689416064</v>
+        <v>0.3335698264758629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3204079786150182</v>
+        <v>0.3308427393486437</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3057514994885449</v>
+        <v>0.3251492244138965</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,30 +2173,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2812172487165674</v>
+        <v>0.2959407439783956</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2782628016005577</v>
+        <v>0.2688877305142465</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07412057527470206</v>
+        <v>0.04152151469497078</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04444741176663558</v>
+        <v>0.04065530386839744</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04333896539845128</v>
+        <v>0.03252957061812567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.036252332977738</v>
+        <v>0.0248375520892099</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XSMC.SW</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02694013733248957</v>
+        <v>0.02393731698296242</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers Swiss Large Cap UCITS ETF 1C</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0259529348665053</v>
+        <v>0.02262773766180137</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02589225623542513</v>
+        <v>0.02246535566966945</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XEWE.MI</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02518999391106891</v>
+        <v>0.02125966768443521</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers S&amp;P 500 Equal Weight Scored &amp; Screened UCITS ETF 2C - EUR Hedged</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02497911153047938</v>
+        <v>0.02104490423538063</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>MIVO.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.024484310599866</v>
+        <v>0.0197936994703094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02350593056217787</v>
+        <v>0.01941333007812496</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DDGT.L</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02223564473151596</v>
+        <v>0.01878613049892452</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dimensional Global Targeted Value UCITS ETF USD (Acc)</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02011555775038465</v>
+        <v>0.01732127483287327</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WLDHC.PA</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01983146656567825</v>
+        <v>0.01647630775234199</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Swap II UCITS ETF EUR Hedged Acc</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEU2.AS</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01961927200611058</v>
+        <v>0.01574286651361101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Core MSCI Europe UCITS ETF Acc</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -698,195 +698,195 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1125121523279111</v>
+        <v>0.1572199139835024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1123212824290456</v>
+        <v>0.1043358929647229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1083199084824309</v>
+        <v>0.09717254699478728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1059645920697943</v>
+        <v>0.09263917867551474</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09790800053624982</v>
+        <v>0.08239913928609499</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09152907945601974</v>
+        <v>0.07864057984908834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08386963126639957</v>
+        <v>0.07856655363080667</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07226077368592931</v>
+        <v>0.07819485222996048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07124241650938501</v>
+        <v>0.07814409040692727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06294084797634758</v>
+        <v>0.07607246563011527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0585483895970178</v>
+        <v>0.06342491125003291</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0567409614558565</v>
+        <v>0.06294084797634758</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05299490260969963</v>
+        <v>0.05502011486834957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04588675644310114</v>
+        <v>0.05281690274386408</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -908,15 +908,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04541935207078596</v>
+        <v>0.05046512721584806</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.409526282277008</v>
+        <v>0.3986876840469433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3707722770091897</v>
+        <v>0.2922050977808368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2955149721619035</v>
+        <v>0.2701544166791101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.294503468722378</v>
+        <v>0.2562345010269911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,45 +1014,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1761107913464515</v>
+        <v>0.1345992940803382</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1712564543889845</v>
+        <v>0.1332403273834248</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1372286494913268</v>
+        <v>0.1290911609391583</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1307957910871671</v>
+        <v>0.1260669544492148</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1074,75 +1074,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1278142786339376</v>
+        <v>0.1201122843674689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1081636480773589</v>
+        <v>0.1175128406017256</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1067207845461375</v>
+        <v>0.1034077932966579</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.105530485824948</v>
+        <v>0.1002817046037128</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1018222608345654</v>
+        <v>0.09842599111275629</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09610930972633458</v>
+        <v>0.09085188972995173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08916782561707004</v>
+        <v>0.08688728947040314</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6550210126311873</v>
+        <v>0.6516393915167153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3001178332608812</v>
+        <v>0.2836323515071282</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2770284504275851</v>
+        <v>0.2459118317997282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,180 +1255,180 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2729495553645975</v>
+        <v>0.2403652212237573</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2607299034254245</v>
+        <v>0.2386638750590195</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2437629640887042</v>
+        <v>0.2155826794676607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2145029298386092</v>
+        <v>0.1863091108045474</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.204462557594048</v>
+        <v>0.1862262785079585</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1984854079428475</v>
+        <v>0.1800415672325342</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1859053399547763</v>
+        <v>0.1665316143237403</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1813235905231321</v>
+        <v>0.159390721634596</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1733444487255642</v>
+        <v>0.1569440189932136</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1714522515448991</v>
+        <v>0.1451595054432979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1694664106802513</v>
+        <v>0.1435411324770417</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AJASE.PA</t>
+          <t>AUSSE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1595844200640426</v>
+        <v>0.1435305920665022</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced Japan UCITS ETF EUR Acc</t>
+          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9027983365052512</v>
+        <v>0.8221511776015999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8880297079405046</v>
+        <v>0.8098659235382064</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,75 +1496,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6666667164953533</v>
+        <v>0.638544455345641</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6661702275714509</v>
+        <v>0.6293436827986387</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5633723319090655</v>
+        <v>0.6167075073681101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5414620856578058</v>
+        <v>0.5418944545709075</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5380334261971511</v>
+        <v>0.5085567515775</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5086103378504714</v>
+        <v>0.4631703528239024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,105 +1586,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4611127961354138</v>
+        <v>0.4229860429527472</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4558434366968482</v>
+        <v>0.410188477052843</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4052443779790198</v>
+        <v>0.3889603863268087</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRES.PA</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3950150746680929</v>
+        <v>0.3728195983721183</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Basic Resources UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3910710869715317</v>
+        <v>0.3681578807850623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3876196979967166</v>
+        <v>0.3664988061054375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3773353304164158</v>
+        <v>0.3580195540690794</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.486840041341469</v>
+        <v>2.264490973836441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.158613655133188</v>
+        <v>2.017687622048094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.804463087820987</v>
+        <v>1.701126996689721</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.773949178351541</v>
+        <v>1.676275463593143</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.742635007736947</v>
+        <v>1.638969085618846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.635945615304912</v>
+        <v>1.593373789352291</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.547020539256077</v>
+        <v>1.443386589298362</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.474417517074587</v>
+        <v>1.436406138332264</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.441646875134743</v>
+        <v>1.394528537703097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.335349382208215</v>
+        <v>1.284763328295555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.335065641649629</v>
+        <v>1.263085060340308</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.330546573731431</v>
+        <v>1.225113795619592</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.320124041403369</v>
+        <v>1.212426646082462</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,30 +1917,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.069052520279227</v>
+        <v>1.042895774896129</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.064096104944089</v>
+        <v>1.003144339952811</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7903034766635546</v>
+        <v>0.7406329118877397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6902089697649956</v>
+        <v>0.6272625114856827</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6806949534952353</v>
+        <v>0.6203017811753282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6081005654636134</v>
+        <v>0.5846045588720314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5970429247886027</v>
+        <v>0.5753062551503554</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.499590464194386</v>
+        <v>0.4438984111677005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4507616219557924</v>
+        <v>0.4231314165256255</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4155678218958319</v>
+        <v>0.4047618881270827</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3512379332019722</v>
+        <v>0.3254791299199919</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2113,30 +2113,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3497767084538224</v>
+        <v>0.3189180063963797</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3335698264758629</v>
+        <v>0.3116626567018337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3308427393486437</v>
+        <v>0.2992943944586122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3251492244138965</v>
+        <v>0.2992403308913476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,15 +2173,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2959407439783956</v>
+        <v>0.2930702877054632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,15 +442,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>INDO.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04152151469497078</v>
+        <v>0.06590944718859904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04065530386839744</v>
+        <v>0.05311918858160558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03252957061812567</v>
+        <v>0.04529456564669898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0248375520892099</v>
+        <v>0.04124340037676877</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02393731698296242</v>
+        <v>0.03956050741244765</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02262773766180137</v>
+        <v>0.03894374159629943</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>DSD.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02246535566966945</v>
+        <v>0.03845354501758247</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02125966768443521</v>
+        <v>0.03793932528838062</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02104490423538063</v>
+        <v>0.03406121715479138</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MIVO.L</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0197936994703094</v>
+        <v>0.0277906108607362</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01941333007812496</v>
+        <v>0.0267876242782803</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>BSX.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01878613049892452</v>
+        <v>0.02380605192907437</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>SHC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01732127483287327</v>
+        <v>0.02331233915929154</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01647630775234199</v>
+        <v>0.02219937754444179</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>MIVO.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01574286651361101</v>
+        <v>0.02139671034290491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1572199139835024</v>
+        <v>0.1466038780297358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,15 +713,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1043358929647229</v>
+        <v>0.1321473116563736</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09717254699478728</v>
+        <v>0.1209613265582981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -743,75 +743,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09263917867551474</v>
+        <v>0.09695118000469249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08239913928609499</v>
+        <v>0.0846341977327012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07864057984908834</v>
+        <v>0.08344794770244057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07856655363080667</v>
+        <v>0.07802664713716134</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07819485222996048</v>
+        <v>0.07780722975106391</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07814409040692727</v>
+        <v>0.07714628247930522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -833,90 +833,90 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>BERMIB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07607246563011527</v>
+        <v>0.07359673062709771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06342491125003291</v>
+        <v>0.0699945535865949</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06294084797634758</v>
+        <v>0.06897683019318124</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05502011486834957</v>
+        <v>0.06882900724924035</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05281690274386408</v>
+        <v>0.06254772463559055</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05046512721584806</v>
+        <v>0.06233334011501745</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3986876840469433</v>
+        <v>0.4428068765644204</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,30 +969,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2922050977808368</v>
+        <v>0.347094863560836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2701544166791101</v>
+        <v>0.3132123220354799</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2562345010269911</v>
+        <v>0.2560088533068967</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1345992940803382</v>
+        <v>0.1986045218784454</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1029,60 +1029,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1332403273834248</v>
+        <v>0.1934904172605449</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1290911609391583</v>
+        <v>0.1404682154239481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1260669544492148</v>
+        <v>0.1373214119774533</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ALAT.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1201122843674689</v>
+        <v>0.1106932824659208</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1175128406017256</v>
+        <v>0.1068287933202761</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,75 +1104,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1034077932966579</v>
+        <v>0.1020698397381108</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1002817046037128</v>
+        <v>0.09301524839072206</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>ALAU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09842599111275629</v>
+        <v>0.09188521030143115</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09085188972995173</v>
+        <v>0.08786224243898744</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08688728947040314</v>
+        <v>0.08588261203652037</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6516393915167153</v>
+        <v>0.6428127770660561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,30 +1225,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2836323515071282</v>
+        <v>0.3083215945121776</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2459118317997282</v>
+        <v>0.2856625640670922</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2403652212237573</v>
+        <v>0.2466928636800314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2386638750590195</v>
+        <v>0.2395891353716046</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1285,60 +1285,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2155826794676607</v>
+        <v>0.2349640590359698</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1863091108045474</v>
+        <v>0.2282579139985459</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1862262785079585</v>
+        <v>0.1980719977644616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1800415672325342</v>
+        <v>0.1835362531136775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1665316143237403</v>
+        <v>0.1592630177026153</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.159390721634596</v>
+        <v>0.1514860227151085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1569440189932136</v>
+        <v>0.15108940411852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1451595054432979</v>
+        <v>0.1488418608583406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>JPN.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1435411324770417</v>
+        <v>0.1485997299607644</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AUSSE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1435305920665022</v>
+        <v>0.1481845077001787</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy ESG Enhanced US UCITS ETF EUR Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8221511776015999</v>
+        <v>0.8386566928231858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8098659235382064</v>
+        <v>0.8283993204152489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1496,15 +1496,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.638544455345641</v>
+        <v>0.665073930735848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6293436827986387</v>
+        <v>0.6563969133896517</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1526,15 +1526,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6167075073681101</v>
+        <v>0.5922621332041249</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5418944545709075</v>
+        <v>0.5165412333694812</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1556,30 +1556,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5085567515775</v>
+        <v>0.509200205269819</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4631703528239024</v>
+        <v>0.5026008507584814</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4229860429527472</v>
+        <v>0.4185716183195967</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,30 +1601,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.410188477052843</v>
+        <v>0.3898875986884545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3889603863268087</v>
+        <v>0.3834575149312813</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3728195983721183</v>
+        <v>0.3688560252604172</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3681578807850623</v>
+        <v>0.3610666910807292</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3664988061054375</v>
+        <v>0.3585958815626207</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3580195540690794</v>
+        <v>0.3467233925838076</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.264490973836441</v>
+        <v>2.291942812906139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.017687622048094</v>
+        <v>2.053934579767034</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.701126996689721</v>
+        <v>1.689260365978789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.676275463593143</v>
+        <v>1.66482720339068</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1782,60 +1782,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.638969085618846</v>
+        <v>1.572070513069233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.593373789352291</v>
+        <v>1.547930801512051</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.443386589298362</v>
+        <v>1.388726237430447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.436406138332264</v>
+        <v>1.362412171696898</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.394528537703097</v>
+        <v>1.327680546511726</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.284763328295555</v>
+        <v>1.280164014036511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.263085060340308</v>
+        <v>1.26446612305907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.225113795619592</v>
+        <v>1.236391268306162</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.212426646082462</v>
+        <v>1.168901195278865</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.042895774896129</v>
+        <v>1.027248591005314</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.003144339952811</v>
+        <v>1.010746104924728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7406329118877397</v>
+        <v>0.7153655360358329</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1993,90 +1993,90 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6272625114856827</v>
+        <v>0.6528983283371932</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6203017811753282</v>
+        <v>0.6504980943023324</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5846045588720314</v>
+        <v>0.6442344413459007</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5753062551503554</v>
+        <v>0.6367726232749129</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4438984111677005</v>
+        <v>0.4890187255289464</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4231314165256255</v>
+        <v>0.4589133788812825</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4047618881270827</v>
+        <v>0.417216106518647</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3189180063963797</v>
+        <v>0.3231967161893321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3116626567018337</v>
+        <v>0.3165318753133652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2992943944586122</v>
+        <v>0.3078732673794122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,30 +2158,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2992403308913476</v>
+        <v>0.2971883497949579</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2930702877054632</v>
+        <v>0.2841833505336229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06590944718859904</v>
+        <v>0.1056881291589562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,210 +457,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05311918858160558</v>
+        <v>0.04966278611588737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04529456564669898</v>
+        <v>0.04407443423457313</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04124340037676877</v>
+        <v>0.03575043875223582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03956050741244765</v>
+        <v>0.03333332160302205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03894374159629943</v>
+        <v>0.0303611396752701</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSD.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03845354501758247</v>
+        <v>0.02992774312000246</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi ShortDAX Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03793932528838062</v>
+        <v>0.02851201414892302</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03406121715479138</v>
+        <v>0.02842855583653114</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0277906108607362</v>
+        <v>0.02809181664229432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>UINC.L</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0267876242782803</v>
+        <v>0.02778696658948054</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>First Trust US Equity Income UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BSX.PA</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02380605192907437</v>
+        <v>0.02599448063323684</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHC.PA</t>
+          <t>STU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02331233915929154</v>
+        <v>0.02535595804657498</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi CAC 40 Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>EPRU.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02219937754444179</v>
+        <v>0.02512757593149306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIVO.L</t>
+          <t>IPRP.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02139671034290491</v>
+        <v>0.02467267196129375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
+          <t>iShares European Property Yield UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -698,45 +698,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1466038780297358</v>
+        <v>0.1420635510650234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1321473116563736</v>
+        <v>0.1078338132455781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1209613265582981</v>
+        <v>0.1074048629475928</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09695118000469249</v>
+        <v>0.1022184199872809</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0846341977327012</v>
+        <v>0.09445022061793895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -773,150 +773,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08344794770244057</v>
+        <v>0.08643127939034478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07802664713716134</v>
+        <v>0.08591733068190521</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07780722975106391</v>
+        <v>0.07686384235405375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07714628247930522</v>
+        <v>0.07243241952536161</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BERMIB.MI</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07359673062709771</v>
+        <v>0.06918867209031099</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0699945535865949</v>
+        <v>0.06462176523955598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06897683019318124</v>
+        <v>0.0631118254692038</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06882900724924035</v>
+        <v>0.06193272161039287</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>BXX.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06254772463559055</v>
+        <v>0.05910851495927805</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06233334011501745</v>
+        <v>0.05745223508398833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4428068765644204</v>
+        <v>0.3781233657046859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,120 +969,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.347094863560836</v>
+        <v>0.351525575602069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3132123220354799</v>
+        <v>0.3122599501213692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2560088533068967</v>
+        <v>0.2848691659072247</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1986045218784454</v>
+        <v>0.2153706119796823</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1934904172605449</v>
+        <v>0.2120054580082591</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1404682154239481</v>
+        <v>0.162637684935534</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1373214119774533</v>
+        <v>0.1193525681893883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1106932824659208</v>
+        <v>0.1128903403463684</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1068287933202761</v>
+        <v>0.1070500274530803</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1104,75 +1104,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1020698397381108</v>
+        <v>0.1049585481572592</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09301524839072206</v>
+        <v>0.1026020356108768</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09188521030143115</v>
+        <v>0.1025568332984916</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08786224243898744</v>
+        <v>0.1024848824107421</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08588261203652037</v>
+        <v>0.09324302964733322</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6428127770660561</v>
+        <v>0.684437729375335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3083215945121776</v>
+        <v>0.3014076125890801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2856625640670922</v>
+        <v>0.2813890787319904</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,30 +1255,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2466928636800314</v>
+        <v>0.2532759124496242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2395891353716046</v>
+        <v>0.2468536538247339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2349640590359698</v>
+        <v>0.2303627872578629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,30 +1300,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2282579139985459</v>
+        <v>0.2113274604188866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1980719977644616</v>
+        <v>0.199605891703394</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1835362531136775</v>
+        <v>0.177936735717996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1592630177026153</v>
+        <v>0.1663933972907443</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,30 +1360,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1514860227151085</v>
+        <v>0.1653047126210081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.15108940411852</v>
+        <v>0.1605813473683408</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1488418608583406</v>
+        <v>0.1568146441701339</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1405,30 +1405,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JPN.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1485997299607644</v>
+        <v>0.1548824888957945</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Dist</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1481845077001787</v>
+        <v>0.1516081132021854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1466,30 +1466,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8386566928231858</v>
+        <v>0.8404796454951988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8283993204152489</v>
+        <v>0.8158205830431939</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.665073930735848</v>
+        <v>0.666523910397165</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1511,30 +1511,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6563969133896517</v>
+        <v>0.643580267458945</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5922621332041249</v>
+        <v>0.6429914288097125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5165412333694812</v>
+        <v>0.5236876929731129</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.509200205269819</v>
+        <v>0.5081231807234692</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5026008507584814</v>
+        <v>0.4887470114860872</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,60 +1586,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4185716183195967</v>
+        <v>0.4136436721243779</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3898875986884545</v>
+        <v>0.3975047111733379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3834575149312813</v>
+        <v>0.3645652519129992</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAU.PA</t>
+          <t>USRI.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3688560252604172</v>
+        <v>0.3631948212751632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF USD</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3585958815626207</v>
+        <v>0.3549571334025012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>WSRI.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3467233925838076</v>
+        <v>0.338291142806143</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World SRI Climate Paris Aligned UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.291942812906139</v>
+        <v>2.438988479013539</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.053934579767034</v>
+        <v>2.06643364052516</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.689260365978789</v>
+        <v>1.838597947670183</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.66482720339068</v>
+        <v>1.812648974362975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.572070513069233</v>
+        <v>1.710965308743961</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.547930801512051</v>
+        <v>1.595454545454545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,15 +1812,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.388726237430447</v>
+        <v>1.436124628908277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.362412171696898</v>
+        <v>1.409774727138738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,15 +1842,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.327680546511726</v>
+        <v>1.339233110821831</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.280164014036511</v>
+        <v>1.330421418522509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.26446612305907</v>
+        <v>1.319199590215397</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,60 +1887,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.236391268306162</v>
+        <v>1.256860034596662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.168901195278865</v>
+        <v>1.207775628695665</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.027248591005314</v>
+        <v>1.055174414085531</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.010746104924728</v>
+        <v>1.022361914311544</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7153655360358329</v>
+        <v>0.7706512562942405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1993,15 +1993,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6528983283371932</v>
+        <v>0.6535796812167824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6504980943023324</v>
+        <v>0.651935381033933</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6442344413459007</v>
+        <v>0.6475868612536453</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6367726232749129</v>
+        <v>0.6395211583644556</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4890187255289464</v>
+        <v>0.4879561032792479</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4589133788812825</v>
+        <v>0.4772043726864352</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.417216106518647</v>
+        <v>0.4216118116444965</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,30 +2098,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3254791299199919</v>
+        <v>0.3458129035627779</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3231967161893321</v>
+        <v>0.3368609125474591</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3165318753133652</v>
+        <v>0.3130057878255059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,60 +2143,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALAT.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3078732673794122</v>
+        <v>0.2917874244356073</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Latin America UCITS ETF EUR (C)</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2971883497949579</v>
+        <v>0.2908301965055469</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2841833505336229</v>
+        <v>0.2625918787174411</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>TPXE.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2688877305142465</v>
+        <v>0.246922554542168</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi Japan Topix UCITS ETF EUR</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDO.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1056881291589562</v>
+        <v>0.04828678187197855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Indonesia UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04966278611588737</v>
+        <v>0.04686215229178892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04407443423457313</v>
+        <v>0.03533909348034658</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03575043875223582</v>
+        <v>0.03463204977077328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03333332160302205</v>
+        <v>0.03377265983029853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0303611396752701</v>
+        <v>0.03219428886089792</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02992774312000246</v>
+        <v>0.03109433398998385</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02851201414892302</v>
+        <v>0.03007378930357074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02842855583653114</v>
+        <v>0.02979065082819932</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02809181664229432</v>
+        <v>0.02497520824881949</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UINC.L</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02778696658948054</v>
+        <v>0.024436613138894</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>First Trust US Equity Income UCITS ETF Dist</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>USRIH.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02599448063323684</v>
+        <v>0.02359984633345147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STU.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02535595804657498</v>
+        <v>0.02341939801015469</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EPRU.AS</t>
+          <t>EMWE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02512757593149306</v>
+        <v>0.02298422516376886</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE EPRA NAREIT Global UCITS ETF Acc</t>
+          <t>BNP Paribas Easy MSCI World SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IPRP.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02467267196129375</v>
+        <v>0.02274930838311029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares European Property Yield UCITS ETF</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1420635510650234</v>
+        <v>0.1249011609831845</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,90 +713,90 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1078338132455781</v>
+        <v>0.09521283630053157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1074048629475928</v>
+        <v>0.0915841038297367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1022184199872809</v>
+        <v>0.09059186426620447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09445022061793895</v>
+        <v>0.08966401389141199</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08643127939034478</v>
+        <v>0.08872582550094599</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08591733068190521</v>
+        <v>0.08642562973358814</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07686384235405375</v>
+        <v>0.07840416149854379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07243241952536161</v>
+        <v>0.0761167146681776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06918867209031099</v>
+        <v>0.06762635327885169</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -848,75 +848,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06462176523955598</v>
+        <v>0.06144553139963804</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0631118254692038</v>
+        <v>0.06084153538961812</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06193272161039287</v>
+        <v>0.05629223202733047</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BXX.PA</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05910851495927805</v>
+        <v>0.05599820112523357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05745223508398833</v>
+        <v>0.05534793889233658</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -954,45 +954,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3781233657046859</v>
+        <v>0.472932477573385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.351525575602069</v>
+        <v>0.409575365524337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3122599501213692</v>
+        <v>0.4022429708559141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2848691659072247</v>
+        <v>0.3448812034141613</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2153706119796823</v>
+        <v>0.2148274083270267</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2120054580082591</v>
+        <v>0.2063742668312041</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.162637684935534</v>
+        <v>0.1980902594206086</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,45 +1059,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1193525681893883</v>
+        <v>0.1420770724163249</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1128903403463684</v>
+        <v>0.1384066524563827</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1070500274530803</v>
+        <v>0.1240918476227431</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1049585481572592</v>
+        <v>0.1197380639047196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1026020356108768</v>
+        <v>0.1183413413216261</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1134,45 +1134,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1025568332984916</v>
+        <v>0.1106882217637215</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1024848824107421</v>
+        <v>0.1014530294377034</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09324302964733322</v>
+        <v>0.09587714203570807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.684437729375335</v>
+        <v>0.7987237385389976</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,180 +1225,180 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3014076125890801</v>
+        <v>0.2911172084465312</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2813890787319904</v>
+        <v>0.284934186771894</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2532759124496242</v>
+        <v>0.2714139039617891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2468536538247339</v>
+        <v>0.2581517201883368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2303627872578629</v>
+        <v>0.2484907965823755</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2113274604188866</v>
+        <v>0.2481345061426676</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.199605891703394</v>
+        <v>0.2180526873974535</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.177936735717996</v>
+        <v>0.2067606252757117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1663933972907443</v>
+        <v>0.2003249532266811</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1653047126210081</v>
+        <v>0.1964500268201035</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1605813473683408</v>
+        <v>0.1857043787813568</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1568146441701339</v>
+        <v>0.1819288152987006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1548824888957945</v>
+        <v>0.1802001540944871</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1420,15 +1420,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>CU2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1516081132021854</v>
+        <v>0.1772186861885325</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
         </is>
       </c>
     </row>
@@ -1466,60 +1466,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8404796454951988</v>
+        <v>0.8276646631304927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8158205830431939</v>
+        <v>0.8137678547193707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.666523910397165</v>
+        <v>0.7401073778838854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.643580267458945</v>
+        <v>0.6565461937258878</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6429914288097125</v>
+        <v>0.6135185250537023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5236876929731129</v>
+        <v>0.5295792526810776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5081231807234692</v>
+        <v>0.5147789782348811</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4887470114860872</v>
+        <v>0.4939369981308137</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,60 +1586,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4136436721243779</v>
+        <v>0.4115764186029842</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3975047111733379</v>
+        <v>0.3920062479719473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3645652519129992</v>
+        <v>0.3692924202312853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USRI.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3631948212751632</v>
+        <v>0.3598624558188368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3610666910807292</v>
+        <v>0.3499543547134523</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1661,30 +1661,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3549571334025012</v>
+        <v>0.3470764268494071</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WSRI.AS</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.338291142806143</v>
+        <v>0.3451637578764539</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI World SRI Climate Paris Aligned UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.438988479013539</v>
+        <v>2.501580281087487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1737,120 +1737,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BNKE.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.06643364052516</v>
+        <v>1.936881252975891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi Euro Stoxx Banks UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.838597947670183</v>
+        <v>1.90609154545029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.812648974362975</v>
+        <v>1.762795825952423</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.710965308743961</v>
+        <v>1.657272616299716</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.595454545454545</v>
+        <v>1.465031810606039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.436124628908277</v>
+        <v>1.463541600952283</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.409774727138738</v>
+        <v>1.385938958467624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.339233110821831</v>
+        <v>1.356391269758417</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.330421418522509</v>
+        <v>1.333486505851892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,75 +1872,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.319199590215397</v>
+        <v>1.291372093249119</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.256860034596662</v>
+        <v>1.286806885224697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>MIB.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.207775628695665</v>
+        <v>1.073549581595922</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi FTSE MIB UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MIB.PA</t>
+          <t>GOLD.AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.055174414085531</v>
+        <v>1.042436900580476</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB UCITS ETF Dist</t>
+          <t>Amundi Physical Gold ETC (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>JPNH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.022361914311544</v>
+        <v>1.001071111277044</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7706512562942405</v>
+        <v>0.8566030492452679</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6535796812167824</v>
+        <v>0.7108330434936538</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2008,30 +2008,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.651935381033933</v>
+        <v>0.7023234294527003</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6475868612536453</v>
+        <v>0.6271108786033486</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6395211583644556</v>
+        <v>0.6078384552275766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2053,30 +2053,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4879561032792479</v>
+        <v>0.513513509995225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4772043726864352</v>
+        <v>0.4840594838740191</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4216118116444965</v>
+        <v>0.4168498676244119</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,30 +2098,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3458129035627779</v>
+        <v>0.3624201450133346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3368609125474591</v>
+        <v>0.3571209389564518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3130057878255059</v>
+        <v>0.3413815304546817</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,60 +2143,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2917874244356073</v>
+        <v>0.3166033091618554</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2908301965055469</v>
+        <v>0.3142625303477296</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2625918787174411</v>
+        <v>0.2699694561953971</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TPXE.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.246922554542168</v>
+        <v>0.2625918787174411</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan Topix UCITS ETF EUR</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04828678187197855</v>
+        <v>0.09927623136438135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,210 +457,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04686215229178892</v>
+        <v>0.06335380853844219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03533909348034658</v>
+        <v>0.06088329329941855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03463204977077328</v>
+        <v>0.04147881260755715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03377265983029853</v>
+        <v>0.03052130392695873</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>MIVO.L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03219428886089792</v>
+        <v>0.02690270420964591</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03109433398998385</v>
+        <v>0.02677099446683462</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03007378930357074</v>
+        <v>0.0247603398249201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02979065082819932</v>
+        <v>0.02387191223641905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02497520824881949</v>
+        <v>0.02284815476012603</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.024436613138894</v>
+        <v>0.02031199284232854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USRIH.MI</t>
+          <t>DHYE.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02359984633345147</v>
+        <v>0.01959771018918177</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA SRI Climate Paris Aligned UCITS ETF Acc EUR Hedged</t>
+          <t>iShares USD High Yield Corporate Bond ESG SRI UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>STU.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02341939801015469</v>
+        <v>0.01957024552597209</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMWE.PA</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02298422516376886</v>
+        <v>0.01896283932757981</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI World SRI S-Series PAB 5% Capped UCITS ETF EUR Acc</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>AASI.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02274930838311029</v>
+        <v>0.01752509637022537</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1249011609831845</v>
+        <v>0.1267327086797325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,30 +713,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09521283630053157</v>
+        <v>0.09495393223642434</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0915841038297367</v>
+        <v>0.0935762906391957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09059186426620447</v>
+        <v>0.08805023291959557</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,60 +758,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08966401389141199</v>
+        <v>0.0829869197581794</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08872582550094599</v>
+        <v>0.08298228021683363</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08642562973358814</v>
+        <v>0.08138757541413844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07840416149854379</v>
+        <v>0.08064516437343583</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0761167146681776</v>
+        <v>0.07350584296794715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06762635327885169</v>
+        <v>0.06705408778390565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -848,75 +848,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>STU.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06144553139963804</v>
+        <v>0.06429008092506461</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>WELE.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06084153538961812</v>
+        <v>0.06109418319543036</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05629223202733047</v>
+        <v>0.06103208035155649</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSP5.PA</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05599820112523357</v>
+        <v>0.06083804381338176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05534793889233658</v>
+        <v>0.06037893137007599</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.472932477573385</v>
+        <v>0.484685548889831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.409575365524337</v>
+        <v>0.4780005502795293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4022429708559141</v>
+        <v>0.4183534705522722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3448812034141613</v>
+        <v>0.3723275457457589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,135 +1014,135 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2148274083270267</v>
+        <v>0.2371134534544763</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2063742668312041</v>
+        <v>0.1999139977696645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1980902594206086</v>
+        <v>0.1734398983750596</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1420770724163249</v>
+        <v>0.1734295032962292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1384066524563827</v>
+        <v>0.1731674787565669</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1240918476227431</v>
+        <v>0.1672280733867682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1197380639047196</v>
+        <v>0.1484897554222224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1183413413216261</v>
+        <v>0.148178588118502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1106882217637215</v>
+        <v>0.1373690034060748</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1014530294377034</v>
+        <v>0.1192457564356189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1164,15 +1164,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09587714203570807</v>
+        <v>0.1102878003720771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7987237385389976</v>
+        <v>0.9654912430727998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2911172084465312</v>
+        <v>0.2904069520807413</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.284934186771894</v>
+        <v>0.2797530154775778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1255,165 +1255,165 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2714139039617891</v>
+        <v>0.2678926436956899</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2581517201883368</v>
+        <v>0.25695619855549</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2484907965823755</v>
+        <v>0.2557112231938097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2481345061426676</v>
+        <v>0.2544201391329994</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2180526873974535</v>
+        <v>0.250118897219354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2067606252757117</v>
+        <v>0.2496096910798855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2003249532266811</v>
+        <v>0.2049265738859249</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1964500268201035</v>
+        <v>0.1918825139653497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1857043787813568</v>
+        <v>0.1846367422489588</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1819288152987006</v>
+        <v>0.1818756452878136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1802001540944871</v>
+        <v>0.1778102346315229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1772186861885325</v>
+        <v>0.1725446196332916</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8276646631304927</v>
+        <v>0.9245312858570685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8137678547193707</v>
+        <v>0.9106562608265063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7401073778838854</v>
+        <v>0.8596062135469631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6565461937258878</v>
+        <v>0.6859769547170196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6135185250537023</v>
+        <v>0.6325998477803174</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5295792526810776</v>
+        <v>0.5560968991282509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5147789782348811</v>
+        <v>0.5387841038977386</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4939369981308137</v>
+        <v>0.4925093957842901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,75 +1586,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4115764186029842</v>
+        <v>0.4444270714813547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3920062479719473</v>
+        <v>0.3882505912918046</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3692924202312853</v>
+        <v>0.3881154245182705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3598624558188368</v>
+        <v>0.3635301322717204</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3499543547134523</v>
+        <v>0.3597528741742098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3470764268494071</v>
+        <v>0.3539258343889111</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1676,15 +1676,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3451637578764539</v>
+        <v>0.33365836617881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.501580281087487</v>
+        <v>2.529319752652128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.936881252975891</v>
+        <v>2.078128667656936</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.90609154545029</v>
+        <v>2.05094164798799</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.762795825952423</v>
+        <v>1.769274447520725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.657272616299716</v>
+        <v>1.66454551003196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.465031810606039</v>
+        <v>1.483215153838946</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.463541600952283</v>
+        <v>1.464388464845711</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.385938958467624</v>
+        <v>1.37733525956164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.356391269758417</v>
+        <v>1.359166717663872</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.333486505851892</v>
+        <v>1.32643682837943</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.291372093249119</v>
+        <v>1.297595607540475</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.286806885224697</v>
+        <v>1.277459053394254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.073549581595922</v>
+        <v>1.080491439621256</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.042436900580476</v>
+        <v>1.033415787597196</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.001071111277044</v>
+        <v>0.986521034196904</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8566030492452679</v>
+        <v>0.9680380588252619</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7108330434936538</v>
+        <v>0.7931144582085057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7023234294527003</v>
+        <v>0.7871733797904985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6271108786033486</v>
+        <v>0.6407642926390547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6078384552275766</v>
+        <v>0.619572789722717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.513513509995225</v>
+        <v>0.52306847761508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4840594838740191</v>
+        <v>0.4950407583450727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4168498676244119</v>
+        <v>0.4271062334530515</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,30 +2098,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3624201450133346</v>
+        <v>0.4119804107374863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3571209389564518</v>
+        <v>0.365614953856485</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3413815304546817</v>
+        <v>0.3593472062488328</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,30 +2143,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3166033091618554</v>
+        <v>0.3321285122970141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3142625303477296</v>
+        <v>0.3118556359615625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2699694561953971</v>
+        <v>0.2704060192628901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,15 +2188,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCCMA.SW</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2625918787174411</v>
+        <v>0.2627403786637372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -442,225 +442,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09927623136438135</v>
+        <v>0.1729032454952117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06335380853844219</v>
+        <v>0.1576922881236908</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06088329329941855</v>
+        <v>0.07197866495700533</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04147881260755715</v>
+        <v>0.0708957016630356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03052130392695873</v>
+        <v>0.06726452248594117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MIVO.L</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02690270420964591</v>
+        <v>0.05804945853088173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe Minimum Volatility Factor UCITS ETF EUR (C)</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02677099446683462</v>
+        <v>0.05701039457475798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0247603398249201</v>
+        <v>0.05270236986387244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02387191223641905</v>
+        <v>0.04990666216594097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02284815476012603</v>
+        <v>0.04600391121734426</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02031199284232854</v>
+        <v>0.04123965061331458</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DHYE.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01959771018918177</v>
+        <v>0.04046128698068685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares USD High Yield Corporate Bond ESG SRI UCITS ETF USD (Acc)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STU.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01957024552597209</v>
+        <v>0.03471160285243546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>CN1.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01896283932757981</v>
+        <v>0.03445844549545707</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>Amundi MSCI Nordic UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AASI.PA</t>
+          <t>AEJ.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01752509637022537</v>
+        <v>0.03368882384373872</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Markets Asia UCITS ETF EUR (C)</t>
+          <t>Amundi MSCI AC Asia Pacific Ex Japan UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1267327086797325</v>
+        <v>0.1274349823854959</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,30 +713,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09495393223642434</v>
+        <v>0.1172889201578757</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0935762906391957</v>
+        <v>0.1099999968629133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08805023291959557</v>
+        <v>0.1091349816882199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -758,90 +758,90 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0829869197581794</v>
+        <v>0.09761753615070368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08298228021683363</v>
+        <v>0.0975351057260172</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XBRMIB.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08138757541413844</v>
+        <v>0.09457598714251425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08064516437343583</v>
+        <v>0.08692980665722083</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07350584296794715</v>
+        <v>0.08105263157894727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06705408778390565</v>
+        <v>0.08019338695723999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06429008092506461</v>
+        <v>0.07197278526992079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -863,60 +863,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WELE.MI</t>
+          <t>UTI.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06109418319543036</v>
+        <v>0.06968291011714611</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06103208035155649</v>
+        <v>0.06836746584507902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06083804381338176</v>
+        <v>0.068172571531675</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>SPEQ.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06037893137007599</v>
+        <v>0.06794426602783066</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Invesco S&amp;P 500 Equal Weight UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.484685548889831</v>
+        <v>0.6802218870553427</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYPE.SW</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4780005502795293</v>
+        <v>0.5037873396928017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21shares Hyperliquid ETP</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4183534705522722</v>
+        <v>0.4250747092421596</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3723275457457589</v>
+        <v>0.308727389088151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2371134534544763</v>
+        <v>0.2426693431445754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1999139977696645</v>
+        <v>0.2186366688739434</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1734398983750596</v>
+        <v>0.1870956057390916</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1059,105 +1059,105 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1734295032962292</v>
+        <v>0.1524472702709765</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKI.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1731674787565669</v>
+        <v>0.1377410266273491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1672280733867682</v>
+        <v>0.137644834842465</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1484897554222224</v>
+        <v>0.130225028928695</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.148178588118502</v>
+        <v>0.1289124804243804</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>LQQ.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1373690034060748</v>
+        <v>0.1192427541999428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1192457564356189</v>
+        <v>0.1188593023097484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1102878003720771</v>
+        <v>0.09064983821247741</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9654912430727998</v>
+        <v>0.9640076763657681</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2904069520807413</v>
+        <v>0.3039691340335489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1240,105 +1240,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2797530154775778</v>
+        <v>0.2662054857348246</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2678926436956899</v>
+        <v>0.2634618943928</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25695619855549</v>
+        <v>0.2548649874320597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2557112231938097</v>
+        <v>0.2473162025950768</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2544201391329994</v>
+        <v>0.2466308735924805</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.250118897219354</v>
+        <v>0.2247539125991267</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2496096910798855</v>
+        <v>0.2246577272924555</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2049265738859249</v>
+        <v>0.2204479876176604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1360,75 +1360,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1918825139653497</v>
+        <v>0.1928841463374955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1846367422489588</v>
+        <v>0.1846755295883642</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1818756452878136</v>
+        <v>0.177905808307016</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LWLD.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1778102346315229</v>
+        <v>0.1638969698950741</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CU2.PA</t>
+          <t>WELE.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1725446196332916</v>
+        <v>0.1567456654589339</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi PEA MSCI USA ESG Selection UCITS ETF - EUR</t>
+          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1466,45 +1466,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9245312858570685</v>
+        <v>0.8994403072180577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9106562608265063</v>
+        <v>0.8037379205779884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8596062135469631</v>
+        <v>0.7924113370573729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6859769547170196</v>
+        <v>0.6588568456146013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6325998477803174</v>
+        <v>0.6311110825566519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1541,30 +1541,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COMO.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5560968991282509</v>
+        <v>0.5268777782236889</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>COMO.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5387841038977386</v>
+        <v>0.5139883051775938</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi Bloomberg Equal-weight Commodity ex-Agriculture UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4925093957842901</v>
+        <v>0.4579414328486426</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,90 +1586,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4444270714813547</v>
+        <v>0.4005722373215346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3882505912918046</v>
+        <v>0.377703000777029</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3881154245182705</v>
+        <v>0.3630966636585917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3635301322717204</v>
+        <v>0.3523312371867149</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3597528741742098</v>
+        <v>0.3504823632711214</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3539258343889111</v>
+        <v>0.3163383736260845</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.33365836617881</v>
+        <v>0.315677073225755</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.529319752652128</v>
+        <v>2.553292545729434</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.078128667656936</v>
+        <v>1.97184402794682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.05094164798799</v>
+        <v>1.947232607393778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.769274447520725</v>
+        <v>1.767303230528974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.66454551003196</v>
+        <v>1.685745095975405</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.483215153838946</v>
+        <v>1.547951489838165</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.464388464845711</v>
+        <v>1.501157179416717</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.37733525956164</v>
+        <v>1.38141571569881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.359166717663872</v>
+        <v>1.332291893176019</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.32643682837943</v>
+        <v>1.325638076753501</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.297595607540475</v>
+        <v>1.320879661763869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.277459053394254</v>
+        <v>1.314926623854727</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.080491439621256</v>
+        <v>1.087979101736015</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,30 +1917,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLD.AS</t>
+          <t>XMK9.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.033415787597196</v>
+        <v>1.00533332824707</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi Physical Gold ETC (C)</t>
+          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JPNH.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.986521034196904</v>
+        <v>1.004143965481624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi Japan TOPIX II UCITS ETF EUR Hedged Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9680380588252619</v>
+        <v>1.01511729854672</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7931144582085057</v>
+        <v>0.7426284290274139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7871733797904985</v>
+        <v>0.7369289402117862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6407642926390547</v>
+        <v>0.6364702600439966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.619572789722717</v>
+        <v>0.6258042996117956</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.52306847761508</v>
+        <v>0.5023203991529144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4950407583450727</v>
+        <v>0.4941551553479071</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4271062334530515</v>
+        <v>0.4014651791489481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,45 +2098,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VAPU.SW</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4119804107374863</v>
+        <v>0.354033448068779</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.365614953856485</v>
+        <v>0.3398704599029563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3593472062488328</v>
+        <v>0.3279978283340723</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3321285122970141</v>
+        <v>0.3157514251141216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2158,45 +2158,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3118556359615625</v>
+        <v>0.2843737479381632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2704060192628901</v>
+        <v>0.2788462420187086</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>EJAP.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2627403786637372</v>
+        <v>0.2505881699283039</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
         </is>
       </c>
     </row>

--- a/data/results/etf/returns_ranking.xlsx
+++ b/data/results/etf/returns_ranking.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1729032454952117</v>
+        <v>0.1851494120387969</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1576922881236908</v>
+        <v>0.08573583905271787</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,195 +472,195 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>LVD.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07197866495700533</v>
+        <v>0.05209558516558843</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0708957016630356</v>
+        <v>0.04775520660372878</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06726452248594117</v>
+        <v>0.04741381243259446</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05804945853088173</v>
+        <v>0.04239559689530537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05701039457475798</v>
+        <v>0.03880411019880681</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LVD.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05270236986387244</v>
+        <v>0.03814662102495658</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi LevDax Daily (2x) leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>CN1.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04990666216594097</v>
+        <v>0.03421569610714825</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Nordic UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>INR.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04600391121734426</v>
+        <v>0.03317536886150507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi MSCI India Swap UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04123965061331458</v>
+        <v>0.03279240418716545</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04046128698068685</v>
+        <v>0.03213838600518759</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>TELE.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03471160285243546</v>
+        <v>0.03186255770836888</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi STOXX Europe 600 Telecommunications UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CN1.PA</t>
+          <t>ITAMID.MI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03445844549545707</v>
+        <v>0.02907340246608325</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI Nordic UCITS ETF EUR (C)</t>
+          <t>Amundi FTSE Italia PMI PIR 2020 UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AEJ.PA</t>
+          <t>INDEP.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03368882384373872</v>
+        <v>0.02883770707977007</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI AC Asia Pacific Ex Japan UCITS ETF Acc</t>
+          <t>Amundi European Strategic Autonomy UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1274349823854959</v>
+        <v>0.145352016857657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -713,210 +713,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1172889201578757</v>
+        <v>0.1394373440380112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1099999968629133</v>
+        <v>0.1380591017040074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLT.PA</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1091349816882199</v>
+        <v>0.1274238357823365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XDWU.MI</t>
+          <t>XDWS.MI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09761753615070368</v>
+        <v>0.1208160947066383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
+          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>ESIH.L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0975351057260172</v>
+        <v>0.1106632961098735</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XDWS.MI</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09457598714251425</v>
+        <v>0.1106234662542149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Consumer Staples UCITS ETF 1C</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UTIW.MI</t>
+          <t>CD9.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08692980665722083</v>
+        <v>0.09716947847624335</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
+          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CD9.PA</t>
+          <t>XDWU.MI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08105263157894727</v>
+        <v>0.0962744409717724</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI Europe High Dividend Factor UCITS ETF EUR (C)</t>
+          <t>Xtrackers MSCI World Utilities UCITS ETF 1C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESIH.L</t>
+          <t>DSP5.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08019338695723999</v>
+        <v>0.09510343734748594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares MSCI Europe Health Care Sector UCITS ETF EUR (Acc)</t>
+          <t>Amundi MSCI USA Daily (-1x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STU.PA</t>
+          <t>UTIW.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07197278526992079</v>
+        <v>0.09174594017208126</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Utilities UCITS ETF EUR</t>
+          <t>Amundi S&amp;P Global Utilities ESG UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UTI.PA</t>
+          <t>HYPE.SW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06968291011714611</v>
+        <v>0.08441173329072837</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amundi STOXX Europe 600 Utilities UCITS ETF Acc</t>
+          <t>21shares Hyperliquid ETP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XDEB.MI</t>
+          <t>MVEU.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06836746584507902</v>
+        <v>0.07903358922595394</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
+          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MVEU.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.068172571531675</v>
+        <v>0.07551482128368692</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Edge MSCI Europe Minimum Volatility UCITS ETF</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPEQ.MI</t>
+          <t>XDEB.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06794426602783066</v>
+        <v>0.0749218319270577</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invesco S&amp;P 500 Equal Weight UCITS ETF Acc</t>
+          <t>Xtrackers MSCI World Minimum Volatility UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6802218870553427</v>
+        <v>0.6638086275163273</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -969,135 +969,135 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARKG.MI</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5037873396928017</v>
+        <v>0.4051907382957323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>ARKG.MI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4250747092421596</v>
+        <v>0.3986376500759143</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>ARK Genomic Revolution UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.308727389088151</v>
+        <v>0.3567957337671803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2426693431445754</v>
+        <v>0.2275288431531521</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2186366688739434</v>
+        <v>0.1849361167745813</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1870956057390916</v>
+        <v>0.1767750967993507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1524472702709765</v>
+        <v>0.1574879751473843</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARKI.MI</t>
+          <t>XUHC.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1377410266273491</v>
+        <v>0.1489281331984966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARK Artificial Intelligence &amp; Robotics UCITS ETF USD Accumulating</t>
+          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.137644834842465</v>
+        <v>0.1393862520283617</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.130225028928695</v>
+        <v>0.1350597202112143</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1119,45 +1119,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>XBRMIB.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1289124804243804</v>
+        <v>0.1096076195545985</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi FTSE MIB Daily (-2x) Inverse UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LQQ.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1192427541999428</v>
+        <v>0.09872833845864148</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi Nasdaq-100 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XUHC.SW</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1188593023097484</v>
+        <v>0.09586372281321043</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI USA Health Care UCITS ETF 1D</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09064983821247741</v>
+        <v>0.08662765407822004</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9640076763657681</v>
+        <v>0.8151967432553535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1225,210 +1225,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLNC.PA</t>
+          <t>HLTW.PA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3039691340335489</v>
+        <v>0.2850982038796521</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoinShares Physical Staked Solana</t>
+          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLTW.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2662054857348246</v>
+        <v>0.2609977914437227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amundi MSCI World Health Care UCITS ETF EUR Acc</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>ABCH.AS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2634618943928</v>
+        <v>0.2592142067928744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>21shares Bitcoin Cash ETP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2548649874320597</v>
+        <v>0.2490650049204339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABCH.AS</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2473162025950768</v>
+        <v>0.2234023831232728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21shares Bitcoin Cash ETP</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARKK.MI</t>
+          <t>SLNC.PA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2466308735924805</v>
+        <v>0.216001010987368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARK Innovation UCITS ETF USD Accumulating</t>
+          <t>CoinShares Physical Staked Solana</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2247539125991267</v>
+        <v>0.212152583538715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>STN.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2246577272924555</v>
+        <v>0.1974176300149466</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>CEC.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2204479876176604</v>
+        <v>0.1672962520773529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEC.PA</t>
+          <t>WELE.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1928841463374955</v>
+        <v>0.1543897888698105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi MSCI Eastern Europe Ex Russia UCITS ETF Acc</t>
+          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STN.PA</t>
+          <t>ARKK.MI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1846755295883642</v>
+        <v>0.1527314733114222</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Energy UCITS ETF EUR</t>
+          <t>ARK Innovation UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.177905808307016</v>
+        <v>0.1509958080566851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LWLD.PA</t>
+          <t>HLT.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1638969698950741</v>
+        <v>0.1487749161550946</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amundi MSCI World (2x) Leveraged UCITS ETF Acc</t>
+          <t>Amundi STOXX Europe 600 Healthcare UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WELE.MI</t>
+          <t>VMIG.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1567456654589339</v>
+        <v>0.147527568610629</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P 500 Equal Weight ESG UCITS ETF Acc</t>
+          <t>Vanguard FTSE 250 UCITS ETF (GBP) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8994403072180577</v>
+        <v>0.7569520737145434</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8037379205779884</v>
+        <v>0.7295864811391932</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7924113370573729</v>
+        <v>0.7158962317584665</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6588568456146013</v>
+        <v>0.6745398963309366</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6311110825566519</v>
+        <v>0.642507522181073</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5268777782236889</v>
+        <v>0.5314460059440176</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5139883051775938</v>
+        <v>0.4946409128554889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,15 +1571,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4579414328486426</v>
+        <v>0.3943662076932959</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4005722373215346</v>
+        <v>0.3782189628479999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,30 +1601,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.377703000777029</v>
+        <v>0.3707924539413916</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEVMIB.MI</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3630966636585917</v>
+        <v>0.3697778814146335</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3523312371867149</v>
+        <v>0.3530953337631029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>LEVMIB.MI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3504823632711214</v>
+        <v>0.3378587234872406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi FTSE MIB Daily (2x) Leveraged UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EMEH.PA</t>
+          <t>BCCMA.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3163383736260845</v>
+        <v>0.3183323686004296</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
+          <t>UBS BBG Commodity CMCI SF UCITS ETF USD acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>EMEH.PA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.315677073225755</v>
+        <v>0.3129315743752399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>BNP Paribas Easy Energy &amp; Metals Enhanced Roll UCITS ETF EUR</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.553292545729434</v>
+        <v>2.381179091635749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.97184402794682</v>
+        <v>1.861067703086706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.947232607393778</v>
+        <v>1.83173185415329</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.767303230528974</v>
+        <v>1.629345000045828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1782,15 +1782,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCHN.MI</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.685745095975405</v>
+        <v>1.479535796527556</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.547951489838165</v>
+        <v>1.478774497882906</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1812,15 +1812,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BCHN.MI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.501157179416717</v>
+        <v>1.461835390764149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>Invesco CoinShares Global Blockchain UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.38141571569881</v>
+        <v>1.315687829953572</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1842,60 +1842,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WITS.AS</t>
+          <t>STZ.PA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.332291893176019</v>
+        <v>1.290936639768355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
+          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STZ.PA</t>
+          <t>WITS.AS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.325638076753501</v>
+        <v>1.230868420853023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Street SPDR MSCI Europe Financials UCITS ETF EUR</t>
+          <t>iShares MSCI World Information Technology Sector Advanced UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LVE.PA</t>
+          <t>COPX.MI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.320879661763869</v>
+        <v>1.215438227691341</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COPX.MI</t>
+          <t>LVE.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.314926623854727</v>
+        <v>1.214542508406678</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global X Copper Miners UCITS ETF USD Accumulating</t>
+          <t>Amundi EURO STOXX 50 Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.087979101736015</v>
+        <v>1.033307552537404</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,30 +1917,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XMK9.MI</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.00533332824707</v>
+        <v>1.02117211081299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI Japan UCITS ETF 4C - EUR Hedged</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>XDWF.MI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.004143965481624</v>
+        <v>0.9646839163539012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Xtrackers MSCI World Financials UCITS ETF 1C</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.01511729854672</v>
+        <v>0.8624338395499802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1993,30 +1993,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KRW.PA</t>
+          <t>SXLE.AS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7426284290274139</v>
+        <v>0.6580761527715555</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amundi MSCI Korea UCITS ETF Acc</t>
+          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IKRA.AS</t>
+          <t>KRW.PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7369289402117862</v>
+        <v>0.6555131112981092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
+          <t>Amundi MSCI Korea UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6364702600439966</v>
+        <v>0.6540717617867071</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2038,45 +2038,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SXLE.AS</t>
+          <t>IKRA.AS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6258042996117956</v>
+        <v>0.6477532692960661</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Street SPDR S&amp;P U.S. Energy Select Sector UCITS ETF USD</t>
+          <t>iShares MSCI Korea UCITS ETF (Dist)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AINF.AS</t>
+          <t>NRGW.PA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5023203991529144</v>
+        <v>0.5138151027150835</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
+          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NRGW.PA</t>
+          <t>AINF.AS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4941551553479071</v>
+        <v>0.4119573520398945</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S&amp;P Global Energy Carbon Reduced UCITS ETF DR EUR (A)</t>
+          <t>iShares AI Infrastructure UCITS ETF USD (Acc)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4014651791489481</v>
+        <v>0.3945055222984433</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2098,30 +2098,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CL2.PA</t>
+          <t>VAPU.SW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.354033448068779</v>
+        <v>0.3477994140849063</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
+          <t>Vanguard FTSE Developed Asia Pacific ex Japan UCITS ETF (USD) Accumulating</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EMXC.PA</t>
+          <t>CL2.PA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3398704599029563</v>
+        <v>0.3111022616096133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
+          <t>Amundi MSCI USA Daily (2x) Leveraged UCITS ETF Acc</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3279978283340723</v>
+        <v>0.2995116856408009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2143,60 +2143,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXCD.AS</t>
+          <t>EMXC.PA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3157514251141216</v>
+        <v>0.2967192501113831</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
+          <t>Amundi MSCI Emerging Ex China UCITS ETF Acc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRE.PA</t>
+          <t>BTEC.SW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2843737479381632</v>
+        <v>0.2850962477499246</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amundi MSCI Greece UCITS ETF Dist</t>
+          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTEC.SW</t>
+          <t>GRE.PA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2788462420187086</v>
+        <v>0.2756438394655094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>iShares Nasdaq US Biotechnology UCITS ETF</t>
+          <t>Amundi MSCI Greece UCITS ETF Dist</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EJAP.PA</t>
+          <t>EXCD.AS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2505881699283039</v>
+        <v>0.2733036500956822</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNP Paribas Easy MSCI Japan Min TE UCITS ETF</t>
+          <t>iShares MSCI EM ex-China UCITS ETF USD (Dist)</t>
         </is>
       </c>
     </row>
